--- a/tame_output/ON/bt/strategyON_20240702.xlsx
+++ b/tame_output/ON/bt/strategyON_20240702.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>43.2%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>78.1%</t>
+          <t>76.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>41.2%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-73.2%</t>
+          <t>-73.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.2%</t>
+          <t>123.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.5%</t>
+          <t>-49.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>452.0%</t>
+          <t>451.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-523.4%</t>
+          <t>-522.8%</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.1%</t>
+          <t>-37.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-50.6%</t>
+          <t>-50.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-163.5%</t>
+          <t>-163.3%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-209.8%</t>
+          <t>-209.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,12 +1456,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.6%</t>
+          <t>-27.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>-17.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-73.9%</t>
+          <t>-93.9%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2011"/>
+  <dimension ref="A1:G2013"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390433</v>
+        <v>3.763182248390432</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105957</v>
+        <v>3.784718794105956</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960992</v>
+        <v>3.753882571960991</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607651</v>
+        <v>3.69293185560765</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.77042258398791</v>
+        <v>3.770422583987909</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -46240,10 +46240,10 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.520963718201717</v>
+        <v>-4.513453150235263</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.005176791157031</v>
+        <v>1.008181018343612</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.3267691687105896</v>
@@ -46263,10 +46263,10 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.566270537600697</v>
+        <v>-4.558759969634242</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9788298388419643</v>
+        <v>0.9818340660285461</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.3675793317198204</v>
@@ -46286,10 +46286,10 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.595303642302998</v>
+        <v>-4.587793074336544</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9677684699941453</v>
+        <v>0.9707726971807271</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.3675793317198204</v>
@@ -46309,10 +46309,10 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.502493160852138</v>
+        <v>-4.494982592885684</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.934165354465855</v>
+        <v>0.9371695816524366</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.2747688502689611</v>
@@ -46332,10 +46332,10 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.546882630181566</v>
+        <v>-4.539372062215111</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9182830426586848</v>
+        <v>0.9212872698452665</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.3191583195983888</v>
@@ -46355,10 +46355,10 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.434211411945316</v>
+        <v>-4.426700843978861</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9584272384649077</v>
+        <v>0.9614314656514895</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.2064871013621385</v>
@@ -46378,10 +46378,10 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.321834410762643</v>
+        <v>-4.314323842796188</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.008869334768644</v>
+        <v>1.011873561955226</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.2064871013621385</v>
@@ -46401,10 +46401,10 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.349614808663995</v>
+        <v>-4.342104240697541</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.009254377376642</v>
+        <v>1.012258604563224</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.2342674992634916</v>
@@ -46424,10 +46424,10 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.432616089689274</v>
+        <v>-4.42510552172282</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.814409584967184</v>
+        <v>0.8174138121537657</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.2528383837906654</v>
@@ -46447,10 +46447,10 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.541230168132605</v>
+        <v>-4.533719600166151</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8911136143090572</v>
+        <v>0.8941178414956388</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.2528383837906654</v>
@@ -46470,10 +46470,10 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.505821129884462</v>
+        <v>-4.498310561918008</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9197902557106372</v>
+        <v>0.922794482897219</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.2528383837906654</v>
@@ -46493,10 +46493,10 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.467437467326311</v>
+        <v>-4.459926899359857</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9325631620762664</v>
+        <v>0.935567389262848</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.2144547212325142</v>
@@ -46516,10 +46516,10 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.290321137291145</v>
+        <v>-4.282810569324691</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.000138722935635</v>
+        <v>1.003142950122216</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.2144547212325142</v>
@@ -46539,10 +46539,10 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.335413382124691</v>
+        <v>-4.327902814158237</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9827852167641296</v>
+        <v>0.9857894439507113</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.276350764401904</v>
@@ -46562,10 +46562,10 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.156037960885923</v>
+        <v>-4.148527392919469</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.048322360566051</v>
+        <v>1.051326587752633</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.1195740062311853</v>
@@ -46585,10 +46585,10 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.201052174406529</v>
+        <v>-4.193541606440075</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.011124130489399</v>
+        <v>1.01412835767598</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.1499229015457899</v>
@@ -46608,10 +46608,10 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.468056684678964</v>
+        <v>-4.46054611671251</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9100138887193703</v>
+        <v>0.9130181159059518</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.3442859395887385</v>
@@ -46631,10 +46631,10 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.569254466116137</v>
+        <v>-4.561743898149683</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8687386980410026</v>
+        <v>0.8717429252275841</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.4126947531340577</v>
@@ -46654,10 +46654,10 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.562743499501824</v>
+        <v>-4.55523293153537</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8689430462410443</v>
+        <v>0.8719472734276259</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.4126947531340577</v>
@@ -46677,10 +46677,10 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.543705371794527</v>
+        <v>-4.536194803828073</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8730830165322081</v>
+        <v>0.8760872437187899</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.4708783644652522</v>
@@ -46700,10 +46700,10 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.574832002945145</v>
+        <v>-4.567321434978691</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.038214233010641</v>
+        <v>1.041218460197223</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.4708783644652522</v>
@@ -46723,10 +46723,10 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.588698764279063</v>
+        <v>-4.581188196312609</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.033500857463208</v>
+        <v>1.036505084649789</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.5087362811990752</v>
@@ -46746,10 +46746,10 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.543894592739133</v>
+        <v>-4.536384024772679</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.057431056476106</v>
+        <v>1.060435283662687</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.5087362811990752</v>
@@ -46769,10 +46769,10 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.396151622504131</v>
+        <v>-4.388641054537676</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.195680892362128</v>
+        <v>1.19868511954871</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.3409289239641921</v>
@@ -46792,10 +46792,10 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.498166305035352</v>
+        <v>-4.490655737068898</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.157668640881121</v>
+        <v>1.160672868067703</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.3409289239641921</v>
@@ -46815,10 +46815,10 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.492013598982568</v>
+        <v>-4.484503031016113</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.160792071693893</v>
+        <v>1.163796298880475</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.3347762179114078</v>
@@ -46838,10 +46838,10 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.508822897133069</v>
+        <v>-4.501312329166615</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.153148829173803</v>
+        <v>1.156153056360384</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.3515855160619094</v>
@@ -46861,10 +46861,10 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.446524898356947</v>
+        <v>-4.439014330390493</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.244403582481072</v>
+        <v>1.247407809667654</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.3515855160619094</v>
@@ -46884,10 +46884,10 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.244734700691789</v>
+        <v>-4.237224132725335</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.033700533936534</v>
+        <v>1.036704761123115</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.153567323892755</v>
@@ -46907,10 +46907,10 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.171356603603053</v>
+        <v>-4.163846035636599</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.133342005094203</v>
+        <v>1.136346232280785</v>
       </c>
       <c r="F1972" t="n">
         <v>-0.08018922680401847</v>
@@ -46930,10 +46930,10 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.269097148228028</v>
+        <v>-4.261586580261573</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.108873523360257</v>
+        <v>1.111877750546839</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.09607850493699865</v>
@@ -46953,10 +46953,10 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.445434908350957</v>
+        <v>-4.437924340384503</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.036874400135757</v>
+        <v>1.039878627322339</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.2724162650599281</v>
@@ -46976,10 +46976,10 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.36901286191903</v>
+        <v>-4.361502293952576</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.065934836748456</v>
+        <v>1.068939063935038</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.2724162650599281</v>
@@ -46999,10 +46999,10 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.324639730280461</v>
+        <v>-4.317129162314007</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.08354695683932</v>
+        <v>1.086551184025902</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.2280431334213595</v>
@@ -47022,10 +47022,10 @@
         <v>2.808153067403842</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.201805509393294</v>
+        <v>-4.19429494142684</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.127074439332778</v>
+        <v>1.130078666519359</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.2280431334213595</v>
@@ -47045,10 +47045,10 @@
         <v>2.814534824431647</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.154149778832238</v>
+        <v>-4.146639210865784</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.152518488585004</v>
+        <v>1.155522715771586</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.1803874028603038</v>
@@ -47068,10 +47068,10 @@
         <v>2.819427197806371</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.053631620333483</v>
+        <v>-4.046121052367029</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.197618125359231</v>
+        <v>1.200622352545812</v>
       </c>
       <c r="F1979" t="n">
         <v>-0.07986924436154924</v>
@@ -47091,10 +47091,10 @@
         <v>2.806181870282244</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.114298210735873</v>
+        <v>-4.106787642769419</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.160106161674147</v>
+        <v>1.163110388860729</v>
       </c>
       <c r="F1980" t="n">
         <v>-0.1615675610800829</v>
@@ -47114,10 +47114,10 @@
         <v>2.810279572892872</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.069459809127475</v>
+        <v>-4.06194924116102</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.182139224928135</v>
+        <v>1.185143452114717</v>
       </c>
       <c r="F1981" t="n">
         <v>-0.1570241281352134</v>
@@ -47137,10 +47137,10 @@
         <v>2.81444051252395</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.170218444884473</v>
+        <v>-4.162707876918018</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.145996710256414</v>
+        <v>1.149000937442996</v>
       </c>
       <c r="F1982" t="n">
         <v>-0.2458496968622189</v>
@@ -47160,10 +47160,10 @@
         <v>2.820320115051787</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.126015607798572</v>
+        <v>-4.118505039832118</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.169557447618611</v>
+        <v>1.172561674805193</v>
       </c>
       <c r="F1983" t="n">
         <v>-0.2016468597763184</v>
@@ -47183,10 +47183,10 @@
         <v>2.818730115521035</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.162994635462015</v>
+        <v>-4.155484067495561</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.153175837022482</v>
+        <v>1.156180064209063</v>
       </c>
       <c r="F1984" t="n">
         <v>-0.1646729579849879</v>
@@ -47206,10 +47206,10 @@
         <v>2.869977880704075</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.183052714326855</v>
+        <v>-4.175542146360401</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.196400370659585</v>
+        <v>1.199404597846167</v>
       </c>
       <c r="F1985" t="n">
         <v>-0.1646729579849879</v>
@@ -47229,10 +47229,10 @@
         <v>2.868418585298328</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.143122041148965</v>
+        <v>-4.135611473182511</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.210813344524994</v>
+        <v>1.213817571711576</v>
       </c>
       <c r="F1986" t="n">
         <v>-0.1247422848070975</v>
@@ -47252,10 +47252,10 @@
         <v>2.863366813536598</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.092089948426437</v>
+        <v>-4.084579380459983</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.226174409852276</v>
+        <v>1.229178637038857</v>
       </c>
       <c r="F1987" t="n">
         <v>-0.07371019208456958</v>
@@ -47275,10 +47275,10 @@
         <v>2.880554217629303</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.026865767299232</v>
+        <v>-4.019355199332778</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.269451486395863</v>
+        <v>1.272455713582444</v>
       </c>
       <c r="F1988" t="n">
         <v>-0.008486010957363954</v>
@@ -47298,10 +47298,10 @@
         <v>2.876515189928583</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.989438747228098</v>
+        <v>-3.981928179261644</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.280383266723596</v>
+        <v>1.283387493910178</v>
       </c>
       <c r="F1989" t="n">
         <v>-0.003234472928182297</v>
@@ -47321,10 +47321,10 @@
         <v>2.877771982259823</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.009550403262806</v>
+        <v>-4.002039835296353</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.273595396640954</v>
+        <v>1.276599623827535</v>
       </c>
       <c r="F1990" t="n">
         <v>0.0077928720692369</v>
@@ -47344,10 +47344,10 @@
         <v>3.038329753281034</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.955805588835601</v>
+        <v>-3.948295020869148</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.455651093433046</v>
+        <v>1.458655320619628</v>
       </c>
       <c r="F1991" t="n">
         <v>0.01785618150969887</v>
@@ -47367,10 +47367,10 @@
         <v>3.158442662498851</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.932014020229459</v>
+        <v>-3.924503452263006</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.58528063009332</v>
+        <v>1.588284857279902</v>
       </c>
       <c r="F1992" t="n">
         <v>0.04164775011584115</v>
@@ -47390,10 +47390,10 @@
         <v>3.15015063851271</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.905929935965651</v>
+        <v>-3.898419367999198</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.587422239812702</v>
+        <v>1.590426466999284</v>
       </c>
       <c r="F1993" t="n">
         <v>0.04164775011584115</v>
@@ -47413,10 +47413,10 @@
         <v>3.14834383409649</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.775637405036041</v>
+        <v>-3.768126837069588</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.637732447768326</v>
+        <v>1.640736674954907</v>
       </c>
       <c r="F1994" t="n">
         <v>0.278183374643576</v>
@@ -47436,10 +47436,10 @@
         <v>3.165898239823281</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.766744943642758</v>
+        <v>-3.759234375676305</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.658843838052431</v>
+        <v>1.661848065239012</v>
       </c>
       <c r="F1995" t="n">
         <v>0.278183374643576</v>
@@ -47459,10 +47459,10 @@
         <v>3.157753287227865</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.935221060612636</v>
+        <v>-3.927710492646183</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.583308438669063</v>
+        <v>1.586312665855645</v>
       </c>
       <c r="F1996" t="n">
         <v>0.2502355389269952</v>
@@ -47482,10 +47482,10 @@
         <v>3.139022984415727</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.237421531751052</v>
+        <v>-3.2299109637846</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.843697947401559</v>
+        <v>1.84670217458814</v>
       </c>
       <c r="F1997" t="n">
         <v>0.1798874795565845</v>
@@ -47505,10 +47505,10 @@
         <v>3.129687006912631</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.2147004280679</v>
+        <v>-3.207189860101447</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.843450411371724</v>
+        <v>1.846454638558306</v>
       </c>
       <c r="F1998" t="n">
         <v>0.1798874795565845</v>
@@ -47528,10 +47528,10 @@
         <v>3.2885931327638</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.212975384777856</v>
+        <v>-3.205464816811403</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.003046554538911</v>
+        <v>2.006050781725492</v>
       </c>
       <c r="F1999" t="n">
         <v>0.1816125228466282</v>
@@ -47551,10 +47551,10 @@
         <v>3.325670955257447</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.367756391556111</v>
+        <v>-3.360245823589658</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.978211974321256</v>
+        <v>1.981216201507837</v>
       </c>
       <c r="F2000" t="n">
         <v>0.1482448487921521</v>
@@ -47574,10 +47574,10 @@
         <v>3.322346311246992</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.316321058171452</v>
+        <v>-3.308810490204999</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.995461463664665</v>
+        <v>1.998465690851246</v>
       </c>
       <c r="F2001" t="n">
         <v>0.1996801821768118</v>
@@ -47597,10 +47597,10 @@
         <v>3.332352464891734</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.289369833844964</v>
+        <v>-3.281859265878511</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.016248107040001</v>
+        <v>2.019252334226582</v>
       </c>
       <c r="F2002" t="n">
         <v>0.2145605282045309</v>
@@ -47620,10 +47620,10 @@
         <v>3.516455597036694</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.42532284190128</v>
+        <v>-3.417812273934827</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.145970035962434</v>
+        <v>2.148974263149015</v>
       </c>
       <c r="F2003" t="n">
         <v>0.2145605282045309</v>
@@ -47643,10 +47643,10 @@
         <v>3.508572291939687</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.447730959706152</v>
+        <v>-3.440220391739699</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.129123483743479</v>
+        <v>2.13212771093006</v>
       </c>
       <c r="F2004" t="n">
         <v>0.2145605282045309</v>
@@ -47666,10 +47666,10 @@
         <v>3.510626291489324</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.595736727185551</v>
+        <v>-3.588226159219098</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.071975176301356</v>
+        <v>2.074979403487938</v>
       </c>
       <c r="F2005" t="n">
         <v>0.1278335193409895</v>
@@ -47689,10 +47689,10 @@
         <v>3.566880009211171</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.605177653074081</v>
+        <v>-3.597667085107628</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.124452523667792</v>
+        <v>2.127456750854373</v>
       </c>
       <c r="F2006" t="n">
         <v>0.2502606368843809</v>
@@ -47712,10 +47712,10 @@
         <v>3.569771103756472</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.603890889534525</v>
+        <v>-3.596380321568072</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.127858323628915</v>
+        <v>2.130862550815496</v>
       </c>
       <c r="F2007" t="n">
         <v>0.2515474004239375</v>
@@ -47735,10 +47735,10 @@
         <v>3.567882916650247</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.605447943523816</v>
+        <v>-3.597937375557363</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.125347314926973</v>
+        <v>2.128351542113555</v>
       </c>
       <c r="F2008" t="n">
         <v>0.2515474004239375</v>
@@ -47758,10 +47758,10 @@
         <v>3.56270314625311</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.612719829047281</v>
+        <v>-3.605209261080828</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.11725879032045</v>
+        <v>2.120263017507031</v>
       </c>
       <c r="F2009" t="n">
         <v>0.2442755149004727</v>
@@ -47781,10 +47781,10 @@
         <v>3.561137156463262</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.61087880998903</v>
+        <v>-3.603368242022577</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.116429208153903</v>
+        <v>2.119433435340484</v>
       </c>
       <c r="F2010" t="n">
         <v>0.2455437415719411</v>
@@ -47804,16 +47804,62 @@
         <v>3.574210563329181</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.61778751548871</v>
+        <v>-3.610276947522257</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.126739132819949</v>
+        <v>2.129743360006531</v>
       </c>
       <c r="F2011" t="n">
         <v>0.2455437415719411</v>
       </c>
       <c r="G2011" t="n">
         <v>3.721536808272345</v>
+      </c>
+    </row>
+    <row r="2012">
+      <c r="A2012" s="2" t="n">
+        <v>45474</v>
+      </c>
+      <c r="B2012" t="n">
+        <v>3.749896851763537</v>
+      </c>
+      <c r="C2012" t="n">
+        <v>3.574210563329181</v>
+      </c>
+      <c r="D2012" t="n">
+        <v>-3.611838590337117</v>
+      </c>
+      <c r="E2012" t="n">
+        <v>2.129118702880587</v>
+      </c>
+      <c r="F2012" t="n">
+        <v>0.2455437415719411</v>
+      </c>
+      <c r="G2012" t="n">
+        <v>3.721536808272345</v>
+      </c>
+    </row>
+    <row r="2013">
+      <c r="A2013" s="2" t="n">
+        <v>45475</v>
+      </c>
+      <c r="B2013" t="n">
+        <v>3.712856324467116</v>
+      </c>
+      <c r="C2013" t="n">
+        <v>3.528414014102369</v>
+      </c>
+      <c r="D2013" t="n">
+        <v>-3.611838590337117</v>
+      </c>
+      <c r="E2013" t="n">
+        <v>2.129118702880587</v>
+      </c>
+      <c r="F2013" t="n">
+        <v>0.2455437415719411</v>
+      </c>
+      <c r="G2013" t="n">
+        <v>3.521477811088737</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240702.xlsx
+++ b/tame_output/ON/bt/strategyON_20240702.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>61.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>55.1%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>76.5%</t>
+          <t>78.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,27 +819,27 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-21.1%</t>
+          <t>-33.6%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>62.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>48.6%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-73.1%</t>
+          <t>-73.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-68.7%</t>
+          <t>-68.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>451.5%</t>
+          <t>452.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-522.8%</t>
+          <t>-523.5%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-50.5%</t>
+          <t>-25.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>70.5%</t>
+          <t>-34.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-163.3%</t>
+          <t>-176.3%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-12.6%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-209.6%</t>
+          <t>-209.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-170.2%</t>
+          <t>-169.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>61.4%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.9%</t>
+          <t>-28.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-93.9%</t>
+          <t>-86.4%</t>
         </is>
       </c>
     </row>
@@ -43681,7 +43681,7 @@
         <v>45294</v>
       </c>
       <c r="B1832" t="n">
-        <v>3.301413393085799</v>
+        <v>3.301413393085798</v>
       </c>
       <c r="C1832" t="n">
         <v>3.130069279090508</v>
@@ -43704,7 +43704,7 @@
         <v>45295</v>
       </c>
       <c r="B1833" t="n">
-        <v>3.311607601705545</v>
+        <v>3.311607601705544</v>
       </c>
       <c r="C1833" t="n">
         <v>3.12694133299222</v>
@@ -43727,7 +43727,7 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045692</v>
+        <v>3.317575502045691</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.311888301355689</v>
+        <v>3.311888301355688</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279813</v>
+        <v>3.385382209279812</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511403</v>
+        <v>3.367379938511402</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998559</v>
+        <v>3.367370539998558</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082123</v>
+        <v>3.299560092082122</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757921</v>
+        <v>3.29349053375792</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760739</v>
+        <v>3.293766719760738</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296836</v>
+        <v>3.299918119296835</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201487</v>
+        <v>3.295507330201486</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153006</v>
+        <v>3.258791981153005</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537426</v>
+        <v>3.271168579537425</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382192</v>
+        <v>3.272760131382191</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074623</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911641</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213498</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416047</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.23598197738233</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347056</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130018</v>
+        <v>3.287377576130017</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207813</v>
+        <v>3.305316798207812</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309425</v>
+        <v>3.311086391309424</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970906</v>
+        <v>3.304715716970905</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191738</v>
+        <v>3.302618194191737</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.30502326510864</v>
+        <v>3.305023265108639</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097822</v>
+        <v>3.341378723097821</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094117</v>
+        <v>3.374439043094116</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199287</v>
+        <v>3.405960511199286</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969594</v>
+        <v>3.424633354969593</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923087</v>
+        <v>3.419979433923086</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.45810009129775</v>
+        <v>3.458100091297749</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317619</v>
+        <v>3.447750501317618</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737172</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341315</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539466</v>
+        <v>3.501052558539465</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937501</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141704</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729893</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440636</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608602</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410273</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764398</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390587</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297401</v>
+        <v>3.492101641297399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322546</v>
+        <v>3.573674025322544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158924</v>
+        <v>3.600038265158922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940722</v>
+        <v>3.69157173394072</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770583</v>
+        <v>3.676841549770582</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615287</v>
+        <v>3.685161381615285</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812106</v>
+        <v>3.684843823812105</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646221</v>
+        <v>3.710935533646219</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611572</v>
+        <v>3.768951674611571</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955332</v>
+        <v>3.72857792995533</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232417</v>
+        <v>3.747702660232416</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436234</v>
+        <v>3.766317079436232</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311954</v>
+        <v>3.784684521311952</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.80082935409725</v>
+        <v>3.800829354097248</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017778</v>
+        <v>3.789311112017776</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.83325274783973</v>
+        <v>3.833252747839729</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388735</v>
+        <v>3.839374447388733</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626481</v>
+        <v>3.856161751626479</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291817</v>
+        <v>3.787330429291815</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785793</v>
+        <v>3.801637122785792</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.155859013848905</v>
+        <v>3.028522268475006</v>
       </c>
       <c r="D1904" t="n">
         <v>-8.112838733526406</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.08963290387540512</v>
+        <v>-0.2169696492493034</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.726345126766282</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.120051937789135</v>
+        <v>1.992715192415237</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390432</v>
+        <v>3.763182248390431</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.151226500595932</v>
+        <v>3.023889755222033</v>
       </c>
       <c r="D1905" t="n">
         <v>-7.980563259895519</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.04135522767602362</v>
+        <v>-0.1686919730499219</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.594069653135396</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.194784708714694</v>
+        <v>2.067447963340796</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105956</v>
+        <v>3.784718794105955</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.154041561283568</v>
+        <v>3.02670481590967</v>
       </c>
       <c r="D1906" t="n">
         <v>-7.824824927335778</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.0237551660355102</v>
+        <v>-0.1035815793383881</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.438331320575654</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.291042768938176</v>
+        <v>2.163706023564278</v>
       </c>
     </row>
     <row r="1907">
@@ -45409,19 +45409,19 @@
         <v>3.753882571960991</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.166947902507227</v>
+        <v>3.039611157133329</v>
       </c>
       <c r="D1907" t="n">
         <v>-7.575825128652196</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.136261426732601</v>
+        <v>0.008924681358702724</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.438331320575654</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.303949110161835</v>
+        <v>2.176612364787937</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.69293185560765</v>
+        <v>3.692931855607649</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.038971972908008</v>
+        <v>2.91163522753411</v>
       </c>
       <c r="D1908" t="n">
         <v>-7.681415118425301</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.03395049877585921</v>
+        <v>-0.1612872441497575</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.543921310348759</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.112619186698754</v>
+        <v>1.985282441324856</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987909</v>
+        <v>3.770422583987908</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.087516314785095</v>
+        <v>2.960179569411197</v>
       </c>
       <c r="D1909" t="n">
         <v>-7.700150020543898</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.007099882253788437</v>
+        <v>-0.1202368631201098</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.54951732000889</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.157805922779761</v>
+        <v>2.030469177405863</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710817</v>
+        <v>3.760333686710815</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.967637392096927</v>
+        <v>2.840300646723029</v>
       </c>
       <c r="D1910" t="n">
         <v>-7.552209979136299</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.05360302387133942</v>
+        <v>-0.1809397692452377</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.529196404100332</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.050119549636728</v>
+        <v>1.92278280426283</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.72356622940921</v>
+        <v>3.723566229409208</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.958923405843449</v>
+        <v>2.831586660469551</v>
       </c>
       <c r="D1911" t="n">
         <v>-7.49924045688231</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.04112920122322228</v>
+        <v>-0.1684659465971206</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.476226881846344</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.073187276735643</v>
+        <v>1.945850531361745</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098115</v>
+        <v>3.729969716098113</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.951962793748356</v>
+        <v>2.824626048374458</v>
       </c>
       <c r="D1912" t="n">
         <v>-7.45569205011162</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.03067045061003926</v>
+        <v>-0.1580071959839375</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.476226881846344</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.06622666464055</v>
+        <v>1.938889919266652</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493426</v>
+        <v>3.782922533493424</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.966425148129499</v>
+        <v>2.839088402755601</v>
       </c>
       <c r="D1913" t="n">
         <v>-7.213543656657762</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.08065126115264709</v>
+        <v>-0.04668548422125118</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.476226881846344</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.080689019021693</v>
+        <v>1.953352273647795</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722822</v>
+        <v>3.82855148672282</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.960957268588694</v>
+        <v>2.833620523214796</v>
       </c>
       <c r="D1914" t="n">
         <v>-7.10528451953524</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1184870364608508</v>
+        <v>-0.008849708913047483</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.476226881846344</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.075221139480888</v>
+        <v>1.94788439410699</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792051</v>
+        <v>3.828052928792049</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.958455362599271</v>
+        <v>2.831118617225373</v>
       </c>
       <c r="D1915" t="n">
         <v>-6.981993384718109</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1653015843982799</v>
+        <v>0.03796483902438164</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.352935747029213</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.146693914381743</v>
+        <v>2.019357169007845</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919913</v>
+        <v>3.812453678919911</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.966156340836596</v>
+        <v>2.838819595462698</v>
       </c>
       <c r="D1916" t="n">
         <v>-6.960844185814666</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1814622421969823</v>
+        <v>0.05412549682308399</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.33178654812577</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.167084411961135</v>
+        <v>2.039747666587236</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318099</v>
+        <v>3.748328408318097</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.961937049183647</v>
+        <v>2.834600303809748</v>
       </c>
       <c r="D1917" t="n">
         <v>-6.717078743831221</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2747491273374107</v>
+        <v>0.1474123819635125</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.33178654812577</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.162865120308185</v>
+        <v>2.035528374934287</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057532</v>
+        <v>3.82431123305753</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.964061363103663</v>
+        <v>2.836724617729764</v>
       </c>
       <c r="D1918" t="n">
         <v>-6.615315923553927</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3175785693683446</v>
+        <v>0.1902418239944463</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.318567479733341</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.172920875263658</v>
+        <v>2.04558412988976</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279192</v>
+        <v>3.82635497427919</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.956803438087365</v>
+        <v>2.829466692713467</v>
       </c>
       <c r="D1919" t="n">
         <v>-6.365465529604852</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4102608019316767</v>
+        <v>0.2829240565577784</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.318567479733341</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.165662950247361</v>
+        <v>2.038326204873462</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011505</v>
+        <v>3.835957987011503</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.960402561608014</v>
+        <v>2.833065816234115</v>
       </c>
       <c r="D1920" t="n">
         <v>-6.189573437137419</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4842167624392988</v>
+        <v>0.3568800170654005</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.318567479733341</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.169262073768009</v>
+        <v>2.041925328394111</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392994</v>
+        <v>3.780933911392992</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.973730067662567</v>
+        <v>2.846393322288669</v>
       </c>
       <c r="D1921" t="n">
         <v>-6.018126974114955</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5661228537028378</v>
+        <v>0.4387861083289395</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.147121016710878</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.285457457636041</v>
+        <v>2.158120712262143</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632789</v>
+        <v>3.773765222632787</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.972750545278864</v>
+        <v>2.845413799904966</v>
       </c>
       <c r="D1922" t="n">
         <v>-5.943837408376616</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5948591576144704</v>
+        <v>0.4675224122405721</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.072831450972539</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.329051674695342</v>
+        <v>2.201714929321443</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883081</v>
+        <v>3.76461787988308</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.977445346333182</v>
+        <v>2.850108600959283</v>
       </c>
       <c r="D1923" t="n">
         <v>-5.880201666142682</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6250082555623617</v>
+        <v>0.4976715101884635</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.009195708738604</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.37192792109002</v>
+        <v>2.244591175716121</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074792</v>
+        <v>3.79881477107479</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.958639605116977</v>
+        <v>2.831302859743079</v>
       </c>
       <c r="D1924" t="n">
         <v>-5.768774906816762</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6507732180765253</v>
+        <v>0.5234364727026271</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.009195708738604</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.353122179873815</v>
+        <v>2.225785434499917</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242303</v>
+        <v>3.797694884242302</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.960382681741855</v>
+        <v>2.833045936367956</v>
       </c>
       <c r="D1925" t="n">
         <v>-5.528344410011901</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7486884934233466</v>
+        <v>0.6213517480494484</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.7687652119337436</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.499123554581609</v>
+        <v>2.37178680920771</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367694</v>
+        <v>3.821593509367692</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.964311995576675</v>
+        <v>2.836975250202777</v>
       </c>
       <c r="D1926" t="n">
         <v>-5.456101841840707</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7815148345266447</v>
+        <v>0.6541780891527464</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.7687652119337436</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.503052868416429</v>
+        <v>2.375716123042531</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879975</v>
+        <v>3.822326997879973</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.964990579494015</v>
+        <v>2.837653834120117</v>
       </c>
       <c r="D1927" t="n">
         <v>-5.403103519559319</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8033927473565399</v>
+        <v>0.6760560019826416</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.7134289529318047</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.536933207734932</v>
+        <v>2.409596462361034</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502347</v>
+        <v>3.848616626502345</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.961988650714008</v>
+        <v>2.83465190534011</v>
       </c>
       <c r="D1928" t="n">
         <v>-5.294298634079592</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8439127727684244</v>
+        <v>0.7165760273945261</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.7134289529318047</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.533931278954926</v>
+        <v>2.406594533581027</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675948</v>
+        <v>3.818668951675947</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.963567687724622</v>
+        <v>2.836230942350724</v>
       </c>
       <c r="D1929" t="n">
         <v>-5.074277836042581</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9335001289938427</v>
+        <v>0.8061633836199444</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.5722091078638245</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.620242223006328</v>
+        <v>2.49290547763243</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539959</v>
+        <v>3.843274527539958</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.979461870526446</v>
+        <v>2.852125125152547</v>
       </c>
       <c r="D1930" t="n">
         <v>-4.941410146979304</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.002541387420977</v>
+        <v>0.8752046420470787</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.5722091078638245</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.636136405808151</v>
+        <v>2.508799660434253</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496268</v>
+        <v>3.845047386496266</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.980607714966748</v>
+        <v>2.853270969592849</v>
       </c>
       <c r="D1931" t="n">
         <v>-4.821237063614805</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.051756465207078</v>
+        <v>0.9244197198331801</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.4520360244993256</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.709386100267153</v>
+        <v>2.582049354893254</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577005</v>
+        <v>3.791273551577003</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.990695817528187</v>
+        <v>2.863359072154289</v>
       </c>
       <c r="D1932" t="n">
         <v>-4.676564918515068</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.119713425808413</v>
+        <v>0.9923766804345149</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.3073638793995881</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.806277489888435</v>
+        <v>2.678940744514537</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.73583922294211</v>
+        <v>3.735839222942108</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.976733308929613</v>
+        <v>2.849396563555715</v>
       </c>
       <c r="D1933" t="n">
         <v>-4.73643974587276</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.081800986266762</v>
+        <v>0.9544642408928639</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.3672387067572803</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.756390084875245</v>
+        <v>2.629053339501347</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674522</v>
+        <v>3.76264747767452</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.999133802252179</v>
+        <v>2.871797056878281</v>
       </c>
       <c r="D1934" t="n">
         <v>-4.649640248093752</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.138921278700932</v>
+        <v>1.011584533327033</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.3672387067572803</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.778790578197811</v>
+        <v>2.651453832823913</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430701</v>
+        <v>3.729146398430699</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.999206203625592</v>
+        <v>2.871869458251693</v>
       </c>
       <c r="D1935" t="n">
         <v>-4.652109954555558</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.138005797489621</v>
+        <v>1.010669052115723</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.3697084132190864</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.77738115569414</v>
+        <v>2.650044410320242</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.74322019600361</v>
+        <v>3.743220196003608</v>
       </c>
       <c r="C1936" t="n">
-        <v>3.010213126100294</v>
+        <v>2.882876380726395</v>
       </c>
       <c r="D1936" t="n">
         <v>-4.720480140879568</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.121664645434719</v>
+        <v>0.9943279000608209</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.3604327141828715</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.793953497590571</v>
+        <v>2.666616752216672</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508378</v>
+        <v>3.714179139508376</v>
       </c>
       <c r="C1937" t="n">
-        <v>3.000649834732185</v>
+        <v>2.873313089358287</v>
       </c>
       <c r="D1937" t="n">
         <v>-4.734268193726614</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.106586132927792</v>
+        <v>0.9792493875538935</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.3604327141828715</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.784390206222462</v>
+        <v>2.657053460848564</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417713</v>
+        <v>3.710906731417711</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.825359399772572</v>
+        <v>2.698022654398673</v>
       </c>
       <c r="D1938" t="n">
         <v>-4.76526135305532</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9188984342366964</v>
+        <v>0.7915616888627981</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.3604327141828715</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.609099771262849</v>
+        <v>2.48176302588895</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205908</v>
+        <v>3.746042526205906</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.829926631764359</v>
+        <v>2.702589886390461</v>
       </c>
       <c r="D1939" t="n">
         <v>-4.589787093262851</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9936553701454718</v>
+        <v>0.8663186247715735</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.3604327141828715</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.613667003254637</v>
+        <v>2.486330257880739</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225453</v>
+        <v>3.765024323225451</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.805668660525567</v>
+        <v>2.678331915151668</v>
       </c>
       <c r="D1940" t="n">
         <v>-4.7007233459041</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9250228978501793</v>
+        <v>0.7976861524762811</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.3604327141828715</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.589409032015844</v>
+        <v>2.462072286641946</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111302</v>
+        <v>3.7732102971113</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.808800045745472</v>
+        <v>2.681463300371574</v>
       </c>
       <c r="D1941" t="n">
         <v>-4.667059800431818</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9416197012589977</v>
+        <v>0.8142829558850995</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.3267691687105896</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.612738544519118</v>
+        <v>2.48540179914522</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264171</v>
+        <v>3.78434395226417</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.818972432177604</v>
+        <v>2.691635686803706</v>
       </c>
       <c r="D1942" t="n">
         <v>-4.607207181228095</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9757331353726193</v>
+        <v>0.848396389998721</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.3267691687105896</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.622910930951251</v>
+        <v>2.495574185577353</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742308</v>
+        <v>3.786949957742306</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.813918702751465</v>
+        <v>2.686581957377566</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.513453150235263</v>
+        <v>-4.520963718201717</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.008181018343612</v>
+        <v>0.8778400457831324</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.3267691687105896</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.617857201525111</v>
+        <v>2.490520456151213</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316054</v>
+        <v>3.752027499316053</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.80569447819599</v>
+        <v>2.678357732822092</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.558759969634242</v>
+        <v>-4.566270537600697</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9818340660285461</v>
+        <v>0.851493093468066</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.3675793317198204</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.585146879164098</v>
+        <v>2.4578101337902</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.7535711658032</v>
+        <v>3.753571165803198</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.806246351229092</v>
+        <v>2.678909605855194</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.587793074336544</v>
+        <v>-4.595303642302998</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9707726971807271</v>
+        <v>0.8404317246202471</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.3675793317198204</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.5856987521972</v>
+        <v>2.458362006823302</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809506</v>
+        <v>3.733390600809504</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.735519043120457</v>
+        <v>2.608182297746559</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.494982592885684</v>
+        <v>-4.502493160852138</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9371695816524366</v>
+        <v>0.8068286090919567</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.2747688502689611</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.570657732959081</v>
+        <v>2.443320987585183</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560433</v>
+        <v>3.748285816560431</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.737392519045058</v>
+        <v>2.61005577367116</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.539372062215111</v>
+        <v>-4.546882630181566</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9212872698452665</v>
+        <v>0.7909462972847865</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.3191583195983888</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.545897527286025</v>
+        <v>2.418560781912127</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472746</v>
+        <v>3.721077195472744</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.732468227556781</v>
+        <v>2.605131482182883</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.426700843978861</v>
+        <v>-4.434211411945316</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9614314656514895</v>
+        <v>0.8310904930910095</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.2064871013621385</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.608575966739498</v>
+        <v>2.4812392213656</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798545</v>
+        <v>3.743047603798543</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.737959523387449</v>
+        <v>2.61062277801355</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.314323842796188</v>
+        <v>-4.321834410762643</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.011873561955226</v>
+        <v>0.8815325893947459</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.2064871013621385</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.614067262570166</v>
+        <v>2.486730517196267</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498873</v>
+        <v>3.689597840498871</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.749456725155988</v>
+        <v>2.622119979782089</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.342104240697541</v>
+        <v>-4.349614808663995</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.012258604563224</v>
+        <v>0.881917632002744</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.2342674992634916</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.608896225597893</v>
+        <v>2.481559480223995</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705334</v>
+        <v>3.643069621705332</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.587812445156641</v>
+        <v>2.460475699782743</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.42510552172282</v>
+        <v>-4.432616089689274</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8174138121537657</v>
+        <v>0.6870728395932857</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.2528383837906654</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.436109414882242</v>
+        <v>2.308772669508344</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729278</v>
+        <v>3.682716310729277</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.707962105875847</v>
+        <v>2.580625360501948</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.533719600166151</v>
+        <v>-4.541230168132605</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8941178414956388</v>
+        <v>0.7637768689351589</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.2528383837906654</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.556259075601448</v>
+        <v>2.428922330227549</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190778</v>
+        <v>3.733012441190776</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.722475131978169</v>
+        <v>2.595138386604271</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.498310561918008</v>
+        <v>-4.505821129884462</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.922794482897219</v>
+        <v>0.7924535103367389</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.2528383837906654</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.570772101703771</v>
+        <v>2.443435356329872</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913435</v>
+        <v>3.741174069913433</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.719894573320538</v>
+        <v>2.59255782794664</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.459926899359857</v>
+        <v>-4.467437467326311</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.935567389262848</v>
+        <v>0.8052264167023682</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.2144547212325142</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.59122174058103</v>
+        <v>2.463884995207132</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532496</v>
+        <v>3.751147197532494</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.71662360216584</v>
+        <v>2.589286856791942</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.282810569324691</v>
+        <v>-4.290321137291145</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.003142950122216</v>
+        <v>0.8728019775617364</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.2144547212325142</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.587950769426332</v>
+        <v>2.460614024052433</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793913</v>
+        <v>3.741328448793912</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.717306993927753</v>
+        <v>2.589970248553855</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.327902814158237</v>
+        <v>-4.335413382124691</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9857894439507113</v>
+        <v>0.8554484713902313</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.276350764401904</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.551496535286611</v>
+        <v>2.424159789912713</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011246</v>
+        <v>3.750729377011244</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.711093969234168</v>
+        <v>2.583757223860269</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.148527392919469</v>
+        <v>-4.156037960885923</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.051326587752633</v>
+        <v>0.9209856151921527</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.1195740062311853</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.639349565495456</v>
+        <v>2.512012820121558</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898224</v>
+        <v>3.716991718982238</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.691901424565757</v>
+        <v>2.564564679191859</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.193541606440075</v>
+        <v>-4.201052174406529</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.01412835767598</v>
+        <v>0.8837873851155003</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.1499229015457899</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.601947683638284</v>
+        <v>2.474610938264385</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509549</v>
+        <v>3.737026608509547</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.697592986904703</v>
+        <v>2.570256241530805</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.46054611671251</v>
+        <v>-4.468056684678964</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9130181159059518</v>
+        <v>0.782677143345472</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.3442859395887385</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.49102142315146</v>
+        <v>2.363684677777562</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476082</v>
+        <v>3.702309454760818</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.696796908801204</v>
+        <v>2.569460163427306</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.561743898149683</v>
+        <v>-4.569254466116137</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8717429252275841</v>
+        <v>0.7414019526671043</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.4126947531340577</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.44918005692077</v>
+        <v>2.321843311546872</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815464</v>
+        <v>3.705571661815463</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.694396870355521</v>
+        <v>2.567060124981623</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.55523293153537</v>
+        <v>-4.562743499501824</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8719472734276259</v>
+        <v>0.7416063008671461</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.4126947531340577</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.446780018475087</v>
+        <v>2.319443273101188</v>
       </c>
     </row>
     <row r="1962">
@@ -46674,19 +46674,19 @@
         <v>3.709510443378107</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.690921589563766</v>
+        <v>2.563584844189868</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.536194803828073</v>
+        <v>-4.543705371794527</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8760872437187899</v>
+        <v>0.7457462711583098</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.4708783644652522</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.408394570884615</v>
+        <v>2.281057825510717</v>
       </c>
     </row>
     <row r="1963">
@@ -46697,19 +46697,19 @@
         <v>3.731064473131259</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.868503458502447</v>
+        <v>2.741166713128548</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.567321434978691</v>
+        <v>-4.574832002945145</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.041218460197223</v>
+        <v>0.9108774876367431</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.4708783644652522</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.585976439823296</v>
+        <v>2.458639694449397</v>
       </c>
     </row>
     <row r="1964">
@@ -46720,19 +46720,19 @@
         <v>3.722447362067875</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.86933678748858</v>
+        <v>2.742000042114682</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.581188196312609</v>
+        <v>-4.588698764279063</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.036505084649789</v>
+        <v>0.9061641120893094</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.5087362811990752</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.564095018769136</v>
+        <v>2.436758273395237</v>
       </c>
     </row>
     <row r="1965">
@@ -46743,19 +46743,19 @@
         <v>3.787425580789131</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.875345317885506</v>
+        <v>2.748008572511608</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.536384024772679</v>
+        <v>-4.543894592739133</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.060435283662687</v>
+        <v>0.9300943111022073</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.5087362811990752</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.570103549166062</v>
+        <v>2.442766803792163</v>
       </c>
     </row>
     <row r="1966">
@@ -46766,19 +46766,19 @@
         <v>3.781501250519918</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.954497965677528</v>
+        <v>2.82716122030363</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.388641054537676</v>
+        <v>-4.396151622504131</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.19868511954871</v>
+        <v>1.06834414698823</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.3409289239641921</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.749940611299013</v>
+        <v>2.622603865925115</v>
       </c>
     </row>
     <row r="1967">
@@ -46789,19 +46789,19 @@
         <v>3.80224592918118</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.957291587209009</v>
+        <v>2.829954841835111</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.490655737068898</v>
+        <v>-4.498166305035352</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.160672868067703</v>
+        <v>1.030331895507223</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.3409289239641921</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.752734232830494</v>
+        <v>2.625397487456596</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.80560898539474</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.957953935600667</v>
+        <v>2.830617190226769</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.484503031016113</v>
+        <v>-4.492013598982568</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.163796298880475</v>
+        <v>1.033455326319995</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.3347762179114078</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.757088204853823</v>
+        <v>2.629751459479925</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890617</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.957034412340778</v>
+        <v>2.829697666966879</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.501312329166615</v>
+        <v>-4.508822897133069</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.156153056360384</v>
+        <v>1.025812083799904</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.3515855160619094</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.746083102703632</v>
+        <v>2.618746357329734</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798434</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.023369966137599</v>
+        <v>2.8960332207637</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.439014330390493</v>
+        <v>-4.446524898356947</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.247407809667654</v>
+        <v>1.117066837107174</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.3515855160619094</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.812418656500453</v>
+        <v>2.685081911126555</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992201</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.731950838526997</v>
+        <v>2.604614093153098</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.237224132725335</v>
+        <v>-4.244734700691789</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.036704761123115</v>
+        <v>0.9063637885626354</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.153567323892755</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.639810444191344</v>
+        <v>2.512473698817446</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852431</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.802241070849172</v>
+        <v>2.674904325475274</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.163846035636599</v>
+        <v>-4.171356603603053</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.136346232280785</v>
+        <v>1.006005259720305</v>
       </c>
       <c r="F1972" t="n">
         <v>-0.08018922680401847</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.754127534766761</v>
+        <v>2.626790789392863</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319556</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.816868806965215</v>
+        <v>2.689532061591317</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.261586580261573</v>
+        <v>-4.269097148228028</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.111877750546839</v>
+        <v>0.9815367779863589</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.09607850493699865</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.759221704003016</v>
+        <v>2.631884958629118</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489395</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.815404787789887</v>
+        <v>2.688068042415989</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.437924340384503</v>
+        <v>-4.445434908350957</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.039878627322339</v>
+        <v>0.9095376547618588</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.2724162650599281</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.65195502875393</v>
+        <v>2.524618283380032</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397804</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.813896405829816</v>
+        <v>2.686559660455917</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.361502293952576</v>
+        <v>-4.36901286191903</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.068939063935038</v>
+        <v>0.9385980913745582</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.2724162650599281</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.650446646793859</v>
+        <v>2.523109901419961</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.833513460316259</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.813759273265252</v>
+        <v>2.686422527891354</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.317129162314007</v>
+        <v>-4.324639730280461</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.086551184025902</v>
+        <v>0.9562102114654218</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.2280431334213595</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.676933393212436</v>
+        <v>2.549596647838538</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821562117105973</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.808153067403842</v>
+        <v>2.680816322029944</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.19429494142684</v>
+        <v>-4.201805509393294</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.130078666519359</v>
+        <v>0.9997376939588793</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.2280431334213595</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.671327187351027</v>
+        <v>2.543990441977129</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833011148190332</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.814534824431647</v>
+        <v>2.687198079057748</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.146639210865784</v>
+        <v>-4.154149778832238</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.155522715771586</v>
+        <v>1.025181743211106</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.1803874028603038</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.706302382715465</v>
+        <v>2.578965637341566</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822678210569624</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.819427197806371</v>
+        <v>2.692090452432473</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.046121052367029</v>
+        <v>-4.053631620333483</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.200622352545812</v>
+        <v>1.070281379985333</v>
       </c>
       <c r="F1979" t="n">
         <v>-0.07986924436154924</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.771505651189442</v>
+        <v>2.644168905815544</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828808877557299</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.806181870282244</v>
+        <v>2.678845124908345</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.106787642769419</v>
+        <v>-4.114298210735873</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.163110388860729</v>
+        <v>1.032769416300249</v>
       </c>
       <c r="F1980" t="n">
         <v>-0.1615675610800829</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.709241333634194</v>
+        <v>2.581904588260296</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816837033932774</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.810279572892872</v>
+        <v>2.682942827518974</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.06194924116102</v>
+        <v>-4.069459809127475</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.185143452114717</v>
+        <v>1.054802479554237</v>
       </c>
       <c r="F1981" t="n">
         <v>-0.1570241281352134</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.716065096011744</v>
+        <v>2.588728350637846</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817932354917058</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.81444051252395</v>
+        <v>2.687103767150052</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.162707876918018</v>
+        <v>-4.170218444884473</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.149000937442996</v>
+        <v>1.018659964882516</v>
       </c>
       <c r="F1982" t="n">
         <v>-0.2458496968622189</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.666930694406619</v>
+        <v>2.539593949032721</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.826684745405967</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.820320115051787</v>
+        <v>2.692983369677889</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.118505039832118</v>
+        <v>-4.126015607798572</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.172561674805193</v>
+        <v>1.042220702244713</v>
       </c>
       <c r="F1983" t="n">
         <v>-0.2016468597763184</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.699331999185997</v>
+        <v>2.571995253812098</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838199629265652</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.818730115521035</v>
+        <v>2.691393370147137</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.155484067495561</v>
+        <v>-4.162994635462015</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.156180064209063</v>
+        <v>1.025839091648583</v>
       </c>
       <c r="F1984" t="n">
         <v>-0.1646729579849879</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.719926340730042</v>
+        <v>2.592589595356144</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47203,19 @@
         <v>3.863895080284887</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.869977880704075</v>
+        <v>2.742641135330176</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.175542146360401</v>
+        <v>-4.183052714326855</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.199404597846167</v>
+        <v>1.069063625285687</v>
       </c>
       <c r="F1985" t="n">
         <v>-0.1646729579849879</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.771174105913082</v>
+        <v>2.643837360539184</v>
       </c>
     </row>
     <row r="1986">
@@ -47226,19 +47226,19 @@
         <v>3.865338681321029</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.868418585298328</v>
+        <v>2.741081839924429</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.135611473182511</v>
+        <v>-4.143122041148965</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.213817571711576</v>
+        <v>1.083476599151096</v>
       </c>
       <c r="F1986" t="n">
         <v>-0.1247422848070975</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.793573214414069</v>
+        <v>2.666236469040171</v>
       </c>
     </row>
     <row r="1987">
@@ -47249,19 +47249,19 @@
         <v>3.864489842475146</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.863366813536598</v>
+        <v>2.736030068162699</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.084579380459983</v>
+        <v>-4.092089948426437</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.229178637038857</v>
+        <v>1.098837664478377</v>
       </c>
       <c r="F1987" t="n">
         <v>-0.07371019208456958</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.819140698285856</v>
+        <v>2.691803952911958</v>
       </c>
     </row>
     <row r="1988">
@@ -47272,19 +47272,19 @@
         <v>3.842547360404862</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.880554217629303</v>
+        <v>2.753217472255404</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.019355199332778</v>
+        <v>-4.026865767299232</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.272455713582444</v>
+        <v>1.142114741021964</v>
       </c>
       <c r="F1988" t="n">
         <v>-0.008486010957363954</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.875462611054885</v>
+        <v>2.748125865680986</v>
       </c>
     </row>
     <row r="1989">
@@ -47295,19 +47295,19 @@
         <v>3.840061186882566</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.876515189928583</v>
+        <v>2.749178444554685</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.981928179261644</v>
+        <v>-3.989438747228098</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.283387493910178</v>
+        <v>1.153046521349698</v>
       </c>
       <c r="F1989" t="n">
         <v>-0.003234472928182297</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.874574506171674</v>
+        <v>2.747237760797776</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47318,19 @@
         <v>3.84516980899267</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.877771982259823</v>
+        <v>2.750435236885925</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.002039835296353</v>
+        <v>-4.009550403262806</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.276599623827535</v>
+        <v>1.146258651267055</v>
       </c>
       <c r="F1990" t="n">
         <v>0.0077928720692369</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.882447705501366</v>
+        <v>2.755110960127467</v>
       </c>
     </row>
     <row r="1991">
@@ -47341,19 +47341,19 @@
         <v>3.828661445636296</v>
       </c>
       <c r="C1991" t="n">
-        <v>3.038329753281034</v>
+        <v>2.910993007907136</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.948295020869148</v>
+        <v>-3.955805588835601</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.458655320619628</v>
+        <v>1.328314348059148</v>
       </c>
       <c r="F1991" t="n">
         <v>0.01785618150969887</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.049043462186853</v>
+        <v>2.921706716812955</v>
       </c>
     </row>
     <row r="1992">
@@ -47364,19 +47364,19 @@
         <v>3.813222820957634</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.158442662498851</v>
+        <v>3.031105917124953</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.924503452263006</v>
+        <v>-3.932014020229459</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.588284857279902</v>
+        <v>1.457943884719422</v>
       </c>
       <c r="F1992" t="n">
         <v>0.04164775011584115</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.183431312568356</v>
+        <v>3.056094567194458</v>
       </c>
     </row>
     <row r="1993">
@@ -47387,19 +47387,19 @@
         <v>3.81423072799876</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.15015063851271</v>
+        <v>3.022813893138812</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.898419367999198</v>
+        <v>-3.905929935965651</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.590426466999284</v>
+        <v>1.460085494438804</v>
       </c>
       <c r="F1993" t="n">
         <v>0.04164775011584115</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.175139288582215</v>
+        <v>3.047802543208317</v>
       </c>
     </row>
     <row r="1994">
@@ -47410,19 +47410,19 @@
         <v>3.803397818896934</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.14834383409649</v>
+        <v>3.021007088722591</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.768126837069588</v>
+        <v>-3.775637405036041</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.640736674954907</v>
+        <v>1.510395702394428</v>
       </c>
       <c r="F1994" t="n">
         <v>0.278183374643576</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.315253858882635</v>
+        <v>3.187917113508737</v>
       </c>
     </row>
     <row r="1995">
@@ -47433,19 +47433,19 @@
         <v>3.796264143959863</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.165898239823281</v>
+        <v>3.038561494449383</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.759234375676305</v>
+        <v>-3.766744943642758</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.661848065239012</v>
+        <v>1.531507092678532</v>
       </c>
       <c r="F1995" t="n">
         <v>0.278183374643576</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.332808264609427</v>
+        <v>3.205471519235529</v>
       </c>
     </row>
     <row r="1996">
@@ -47456,19 +47456,19 @@
         <v>3.794424941945373</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.157753287227865</v>
+        <v>3.030416541853967</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.927710492646183</v>
+        <v>-3.935221060612636</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.586312665855645</v>
+        <v>1.455971693295165</v>
       </c>
       <c r="F1996" t="n">
         <v>0.2502355389269952</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.307894610584063</v>
+        <v>3.180557865210164</v>
       </c>
     </row>
     <row r="1997">
@@ -47479,19 +47479,19 @@
         <v>3.795574066782715</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.139022984415727</v>
+        <v>3.011686239041829</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.2299109637846</v>
+        <v>-3.237421531751052</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.84670217458814</v>
+        <v>1.71636120202766</v>
       </c>
       <c r="F1997" t="n">
         <v>0.1798874795565845</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.246955472149678</v>
+        <v>3.11961872677578</v>
       </c>
     </row>
     <row r="1998">
@@ -47502,19 +47502,19 @@
         <v>3.784671345632645</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.129687006912631</v>
+        <v>3.002350261538733</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.207189860101447</v>
+        <v>-3.2147004280679</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.846454638558306</v>
+        <v>1.716113665997826</v>
       </c>
       <c r="F1998" t="n">
         <v>0.1798874795565845</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.237619494646582</v>
+        <v>3.110282749272684</v>
       </c>
     </row>
     <row r="1999">
@@ -47525,19 +47525,19 @@
         <v>3.783205696777682</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.2885931327638</v>
+        <v>3.161256387389902</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.205464816811403</v>
+        <v>-3.212975384777856</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.006050781725492</v>
+        <v>1.875709809165013</v>
       </c>
       <c r="F1999" t="n">
         <v>0.1816125228466282</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.397560646471778</v>
+        <v>3.27022390109788</v>
       </c>
     </row>
     <row r="2000">
@@ -47548,19 +47548,19 @@
         <v>3.779933725644421</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.325670955257447</v>
+        <v>3.198334209883549</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.360245823589658</v>
+        <v>-3.367756391556111</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.981216201507837</v>
+        <v>1.850875228947357</v>
       </c>
       <c r="F2000" t="n">
         <v>0.1482448487921521</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.414617864532739</v>
+        <v>3.28728111915884</v>
       </c>
     </row>
     <row r="2001">
@@ -47571,19 +47571,19 @@
         <v>3.769443619799969</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.322346311246992</v>
+        <v>3.195009565873094</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.308810490204999</v>
+        <v>-3.316321058171452</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.998465690851246</v>
+        <v>1.868124718290766</v>
       </c>
       <c r="F2001" t="n">
         <v>0.1996801821768118</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.442154420553079</v>
+        <v>3.314817675179181</v>
       </c>
     </row>
     <row r="2002">
@@ -47594,19 +47594,19 @@
         <v>3.766673496331124</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.332352464891734</v>
+        <v>3.205015719517835</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.281859265878511</v>
+        <v>-3.289369833844964</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.019252334226582</v>
+        <v>1.888911361666103</v>
       </c>
       <c r="F2002" t="n">
         <v>0.2145605282045309</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.461088781814452</v>
+        <v>3.333752036440554</v>
       </c>
     </row>
     <row r="2003">
@@ -47617,19 +47617,19 @@
         <v>3.768052067784117</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.516455597036694</v>
+        <v>3.389118851662795</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.417812273934827</v>
+        <v>-3.42532284190128</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.148974263149015</v>
+        <v>2.018633290588536</v>
       </c>
       <c r="F2003" t="n">
         <v>0.2145605282045309</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.645191913959412</v>
+        <v>3.517855168585514</v>
       </c>
     </row>
     <row r="2004">
@@ -47640,19 +47640,19 @@
         <v>3.74392550571443</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.508572291939687</v>
+        <v>3.381235546565788</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.440220391739699</v>
+        <v>-3.447730959706152</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.13212771093006</v>
+        <v>2.001786738369581</v>
       </c>
       <c r="F2004" t="n">
         <v>0.2145605282045309</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.637308608862405</v>
+        <v>3.509971863488507</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155041</v>
+        <v>3.719118627155042</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.510626291489324</v>
+        <v>3.383289546115426</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.588226159219098</v>
+        <v>-3.595736727185551</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.074979403487938</v>
+        <v>1.944638430927458</v>
       </c>
       <c r="F2005" t="n">
         <v>0.1278335193409895</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.587326403093918</v>
+        <v>3.45998965772002</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161986</v>
+        <v>3.729452285161987</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.566880009211171</v>
+        <v>3.439543263837273</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.597667085107628</v>
+        <v>-3.605177653074081</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.127456750854373</v>
+        <v>1.997115778293893</v>
       </c>
       <c r="F2006" t="n">
         <v>0.2502606368843809</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.7170363913418</v>
+        <v>3.589699645967902</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321643</v>
+        <v>3.714941193321644</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.569771103756472</v>
+        <v>3.442434358382574</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.596380321568072</v>
+        <v>-3.603890889534525</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.130862550815496</v>
+        <v>2.000521578255016</v>
       </c>
       <c r="F2007" t="n">
         <v>0.2515474004239375</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.720699544010835</v>
+        <v>3.593362798636937</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347711</v>
+        <v>3.727898186347712</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.567882916650247</v>
+        <v>3.440546171276349</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.597937375557363</v>
+        <v>-3.605447943523816</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.128351542113555</v>
+        <v>1.998010569553075</v>
       </c>
       <c r="F2008" t="n">
         <v>0.2515474004239375</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.71881135690461</v>
+        <v>3.591474611530712</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887755</v>
+        <v>3.710654104887756</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.56270314625311</v>
+        <v>3.435366400879211</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.605209261080828</v>
+        <v>-3.612719829047281</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.120263017507031</v>
+        <v>1.989922044946552</v>
       </c>
       <c r="F2009" t="n">
         <v>0.2442755149004727</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.709268455193393</v>
+        <v>3.581931709819495</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343073</v>
+        <v>3.712897612343074</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.561137156463262</v>
+        <v>3.433800411089364</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.603368242022577</v>
+        <v>-3.61087880998903</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.119433435340484</v>
+        <v>1.989092462780004</v>
       </c>
       <c r="F2010" t="n">
         <v>0.2455437415719411</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.708463401406427</v>
+        <v>3.581126656032529</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647114</v>
+        <v>3.754911907647115</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.574210563329181</v>
+        <v>3.446873817955282</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.610276947522257</v>
+        <v>-3.61778751548871</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.129743360006531</v>
+        <v>1.999402387446051</v>
       </c>
       <c r="F2011" t="n">
         <v>0.2455437415719411</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.721536808272345</v>
+        <v>3.594200062898447</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763537</v>
+        <v>3.749896851763538</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.574210563329181</v>
+        <v>3.446873817955282</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.611838590337117</v>
+        <v>-3.61934915830357</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.129118702880587</v>
+        <v>1.998777730320107</v>
       </c>
       <c r="F2012" t="n">
         <v>0.2455437415719411</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.721536808272345</v>
+        <v>3.594200062898447</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.712856324467116</v>
+        <v>3.831785640062565</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.528414014102369</v>
+        <v>3.602751568594131</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.611838590337117</v>
+        <v>-3.61934915830357</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.129118702880587</v>
+        <v>1.998777730320107</v>
       </c>
       <c r="F2013" t="n">
         <v>0.2455437415719411</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.521477811088737</v>
+        <v>3.595815365580499</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240702.xlsx
+++ b/tame_output/ON/bt/strategyON_20240702.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -671,17 +671,17 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>28.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>78.3%</t>
+          <t>72.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>62.2%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>31.0%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-73.2%</t>
+          <t>-74.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.9%</t>
+          <t>109.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.1%</t>
+          <t>123.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,12 +982,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.6%</t>
+          <t>-50.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-68.6%</t>
+          <t>-70.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>452.0%</t>
+          <t>449.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-523.5%</t>
+          <t>-543.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,22 +1140,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-8.5%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-37.2%</t>
+          <t>-37.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-25.3%</t>
+          <t>-24.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-34.1%</t>
+          <t>-37.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-176.3%</t>
+          <t>-178.9%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-12.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-209.8%</t>
+          <t>-40.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-169.9%</t>
+          <t>-171.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-199.4%</t>
+          <t>-197.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.6%</t>
+          <t>-28.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.4%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-86.4%</t>
+          <t>-104.1%</t>
         </is>
       </c>
     </row>
@@ -43681,7 +43681,7 @@
         <v>45294</v>
       </c>
       <c r="B1832" t="n">
-        <v>3.301413393085798</v>
+        <v>3.301413393085799</v>
       </c>
       <c r="C1832" t="n">
         <v>3.130069279090508</v>
@@ -43704,7 +43704,7 @@
         <v>45295</v>
       </c>
       <c r="B1833" t="n">
-        <v>3.311607601705544</v>
+        <v>3.311607601705545</v>
       </c>
       <c r="C1833" t="n">
         <v>3.12694133299222</v>
@@ -43727,7 +43727,7 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045691</v>
+        <v>3.317575502045693</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.311888301355688</v>
+        <v>3.311888301355689</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279812</v>
+        <v>3.385382209279813</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511402</v>
+        <v>3.367379938511403</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998558</v>
+        <v>3.36737053999856</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082122</v>
+        <v>3.299560092082124</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.29349053375792</v>
+        <v>3.293490533757923</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760738</v>
+        <v>3.293766719760741</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706668</v>
+        <v>3.298730590706669</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296835</v>
+        <v>3.299918119296836</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201486</v>
+        <v>3.295507330201487</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153005</v>
+        <v>3.258791981153006</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537425</v>
+        <v>3.271168579537426</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382191</v>
+        <v>3.272760131382192</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074623</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347054</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130017</v>
+        <v>3.287377576130016</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178244</v>
+        <v>3.315884374178243</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207812</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310981</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006533</v>
+        <v>3.305849539006532</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309424</v>
+        <v>3.311086391309423</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970905</v>
+        <v>3.304715716970904</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330523</v>
+        <v>3.300815818330522</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191737</v>
+        <v>3.302618194191736</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108639</v>
+        <v>3.305023265108638</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097821</v>
+        <v>3.34137872309782</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199286</v>
+        <v>3.405960511199285</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969593</v>
+        <v>3.424633354969592</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297749</v>
+        <v>3.458100091297748</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317618</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341315</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539465</v>
+        <v>3.501052558539464</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390587</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297399</v>
+        <v>3.4921016412974</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322544</v>
+        <v>3.573674025322545</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158922</v>
+        <v>3.600038265158923</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.69157173394072</v>
+        <v>3.691571733940721</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812105</v>
+        <v>3.684843823812104</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646219</v>
+        <v>3.710935533646218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611571</v>
+        <v>3.76895167461157</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.72857792995533</v>
+        <v>3.728577929955329</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232416</v>
+        <v>3.747702660232415</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436232</v>
+        <v>3.766317079436231</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311952</v>
+        <v>3.784684521311951</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097248</v>
+        <v>3.800829354097247</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017776</v>
+        <v>3.789311112017775</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839729</v>
+        <v>3.833252747839728</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388733</v>
+        <v>3.839374447388732</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626479</v>
+        <v>3.856161751626478</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291815</v>
+        <v>3.787330429291814</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785792</v>
+        <v>3.80163712278579</v>
       </c>
       <c r="C1904" t="n">
         <v>3.028522268475006</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.112838733526406</v>
+        <v>-8.108044911132819</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.2169696492493034</v>
+        <v>-0.2150521202918685</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.726345126766282</v>
+        <v>-1.706313558251827</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.992715192415237</v>
+        <v>2.004734133523911</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390431</v>
+        <v>3.76318224839043</v>
       </c>
       <c r="C1905" t="n">
         <v>3.023889755222033</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.980563259895519</v>
+        <v>-7.975769437501932</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.1686919730499219</v>
+        <v>-0.166774444092487</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.594069653135396</v>
+        <v>-1.57403808462094</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.067447963340796</v>
+        <v>2.07946690444947</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.02670481590967</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.824824927335778</v>
+        <v>-7.82003110494219</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1035815793383881</v>
+        <v>-0.1016640503809532</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.438331320575654</v>
+        <v>-1.418299752061198</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.163706023564278</v>
+        <v>2.175724964672952</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960991</v>
+        <v>3.75388257196099</v>
       </c>
       <c r="C1907" t="n">
         <v>3.039611157133329</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.575825128652196</v>
+        <v>-7.571031306258609</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.008924681358702724</v>
+        <v>0.01084221031613763</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.438331320575654</v>
+        <v>-1.418299752061198</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.176612364787937</v>
+        <v>2.18863130589661</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607649</v>
+        <v>3.692931855607648</v>
       </c>
       <c r="C1908" t="n">
         <v>2.91163522753411</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.681415118425301</v>
+        <v>-7.676621296031714</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.1612872441497575</v>
+        <v>-0.1593697151923226</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.543921310348759</v>
+        <v>-1.523889741834303</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.985282441324856</v>
+        <v>1.997301382433529</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987908</v>
+        <v>3.770422583987906</v>
       </c>
       <c r="C1909" t="n">
         <v>2.960179569411197</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.700150020543898</v>
+        <v>-7.695356198150311</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1202368631201098</v>
+        <v>-0.1183193341626749</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.54951732000889</v>
+        <v>-1.529485751494434</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.030469177405863</v>
+        <v>2.042488118514536</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.840300646723029</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.552209979136299</v>
+        <v>-7.547416156742711</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1809397692452377</v>
+        <v>-0.1790222402878028</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.529196404100332</v>
+        <v>-1.509164835585876</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.92278280426283</v>
+        <v>1.934801745371503</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409208</v>
+        <v>3.723566229409207</v>
       </c>
       <c r="C1911" t="n">
         <v>2.831586660469551</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.49924045688231</v>
+        <v>-7.494446634488723</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1684659465971206</v>
+        <v>-0.1665484176396856</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.476226881846344</v>
+        <v>-1.456195313331888</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.945850531361745</v>
+        <v>1.957869472470418</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098113</v>
+        <v>3.729969716098111</v>
       </c>
       <c r="C1912" t="n">
         <v>2.824626048374458</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.45569205011162</v>
+        <v>-7.450898227718032</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1580071959839375</v>
+        <v>-0.1560896670265026</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.476226881846344</v>
+        <v>-1.456195313331888</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.938889919266652</v>
+        <v>1.950908860375325</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493424</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.839088402755601</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.213543656657762</v>
+        <v>-7.208749834264174</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.04668548422125118</v>
+        <v>-0.04476795526381627</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.476226881846344</v>
+        <v>-1.456195313331888</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.953352273647795</v>
+        <v>1.965371214756468</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.82855148672282</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.833620523214796</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.10528451953524</v>
+        <v>-7.100490697141653</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.008849708913047483</v>
+        <v>-0.006932179955612572</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.476226881846344</v>
+        <v>-1.456195313331888</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.94788439410699</v>
+        <v>1.959903335215663</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792049</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.831118617225373</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.981993384718109</v>
+        <v>-6.977199562324522</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.03796483902438164</v>
+        <v>0.03988236798181655</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.352935747029213</v>
+        <v>-1.332904178514757</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.019357169007845</v>
+        <v>2.031376110116518</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919911</v>
+        <v>3.812453678919908</v>
       </c>
       <c r="C1916" t="n">
         <v>2.838819595462698</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.960844185814666</v>
+        <v>-6.956050363421078</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.05412549682308399</v>
+        <v>0.0560430257805189</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.33178654812577</v>
+        <v>-1.311754979611314</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.039747666587236</v>
+        <v>2.05176660769591</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318097</v>
+        <v>3.748328408318094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.834600303809748</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.717078743831221</v>
+        <v>-6.712284921437634</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1474123819635125</v>
+        <v>0.1493299109209474</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.33178654812577</v>
+        <v>-1.311754979611314</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.035528374934287</v>
+        <v>2.04754731604296</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.82431123305753</v>
+        <v>3.824311233057527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.836724617729764</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.615315923553927</v>
+        <v>-6.610522101160339</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1902418239944463</v>
+        <v>0.1921593529518812</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.318567479733341</v>
+        <v>-1.298535911218885</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.04558412988976</v>
+        <v>2.057603070998434</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.82635497427919</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.829466692713467</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.365465529604852</v>
+        <v>-6.360671707211265</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2829240565577784</v>
+        <v>0.2848415855152133</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.318567479733341</v>
+        <v>-1.298535911218885</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.038326204873462</v>
+        <v>2.050345145982136</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011503</v>
+        <v>3.835957987011499</v>
       </c>
       <c r="C1920" t="n">
         <v>2.833065816234115</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.189573437137419</v>
+        <v>-6.184779614743832</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3568800170654005</v>
+        <v>0.3587975460228354</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.318567479733341</v>
+        <v>-1.298535911218885</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.041925328394111</v>
+        <v>2.053944269502785</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392992</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.846393322288669</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.018126974114955</v>
+        <v>-6.013333151721368</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4387861083289395</v>
+        <v>0.4407036372863744</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.147121016710878</v>
+        <v>-1.127089448196422</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.158120712262143</v>
+        <v>2.170139653370816</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632787</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.845413799904966</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.943837408376616</v>
+        <v>-5.939043585983029</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4675224122405721</v>
+        <v>0.469439941198007</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.072831450972539</v>
+        <v>-1.052799882458083</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.201714929321443</v>
+        <v>2.213733870430117</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.76461787988308</v>
+        <v>3.764617879883074</v>
       </c>
       <c r="C1923" t="n">
         <v>2.850108600959283</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.880201666142682</v>
+        <v>-5.875407843749095</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4976715101884635</v>
+        <v>0.4995890391458984</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.009195708738604</v>
+        <v>-0.9891641402241481</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.244591175716121</v>
+        <v>2.256610116824795</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107479</v>
+        <v>3.798814771074785</v>
       </c>
       <c r="C1924" t="n">
         <v>2.831302859743079</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.768774906816762</v>
+        <v>-5.763981084423174</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5234364727026271</v>
+        <v>0.525354001660062</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.009195708738604</v>
+        <v>-0.9891641402241481</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.225785434499917</v>
+        <v>2.23780437560859</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242302</v>
+        <v>3.797694884242296</v>
       </c>
       <c r="C1925" t="n">
         <v>2.833045936367956</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.528344410011901</v>
+        <v>-5.523550587618314</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6213517480494484</v>
+        <v>0.6232692770068833</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.7687652119337436</v>
+        <v>-0.7487336434192878</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.37178680920771</v>
+        <v>2.383805750316384</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367692</v>
+        <v>3.821593509367687</v>
       </c>
       <c r="C1926" t="n">
         <v>2.836975250202777</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.456101841840707</v>
+        <v>-5.45130801944712</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6541780891527464</v>
+        <v>0.6560956181101814</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.7687652119337436</v>
+        <v>-0.7487336434192878</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.375716123042531</v>
+        <v>2.387735064151204</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879973</v>
+        <v>3.822326997879967</v>
       </c>
       <c r="C1927" t="n">
         <v>2.837653834120117</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.403103519559319</v>
+        <v>-5.398309697165732</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6760560019826416</v>
+        <v>0.6779735309400765</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7134289529318047</v>
+        <v>-0.693397384417349</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.409596462361034</v>
+        <v>2.421615403469707</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502345</v>
+        <v>3.84861662650234</v>
       </c>
       <c r="C1928" t="n">
         <v>2.83465190534011</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.294298634079592</v>
+        <v>-5.289504811686005</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7165760273945261</v>
+        <v>0.718493556351961</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7134289529318047</v>
+        <v>-0.693397384417349</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.406594533581027</v>
+        <v>2.418613474689701</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675947</v>
+        <v>3.818668951675941</v>
       </c>
       <c r="C1929" t="n">
         <v>2.836230942350724</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.074277836042581</v>
+        <v>-5.069484013648994</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8061633836199444</v>
+        <v>0.8080809125773794</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.5722091078638245</v>
+        <v>-0.5521775393493688</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.49290547763243</v>
+        <v>2.504924418741103</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539958</v>
+        <v>3.843274527539952</v>
       </c>
       <c r="C1930" t="n">
         <v>2.852125125152547</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.941410146979304</v>
+        <v>-4.936616324585716</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8752046420470787</v>
+        <v>0.8771221710045136</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.5722091078638245</v>
+        <v>-0.5521775393493688</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.508799660434253</v>
+        <v>2.520818601542926</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496266</v>
+        <v>3.845047386496262</v>
       </c>
       <c r="C1931" t="n">
         <v>2.853270969592849</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.821237063614805</v>
+        <v>-4.816443241221218</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9244197198331801</v>
+        <v>0.926337248790615</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4520360244993256</v>
+        <v>-0.4320044559848698</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.582049354893254</v>
+        <v>2.594068296001928</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577003</v>
+        <v>3.791273551576999</v>
       </c>
       <c r="C1932" t="n">
         <v>2.863359072154289</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.676564918515068</v>
+        <v>-4.67177109612148</v>
       </c>
       <c r="E1932" t="n">
-        <v>0.9923766804345149</v>
+        <v>0.9942942093919498</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3073638793995881</v>
+        <v>-0.2873323108851324</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.678940744514537</v>
+        <v>2.69095968562321</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942108</v>
+        <v>3.735839222942104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.849396563555715</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.73643974587276</v>
+        <v>-4.731645923479173</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9544642408928639</v>
+        <v>0.9563817698502988</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.3672387067572803</v>
+        <v>-0.3472071382428245</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.629053339501347</v>
+        <v>2.64107228061002</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.76264747767452</v>
+        <v>3.762647477674516</v>
       </c>
       <c r="C1934" t="n">
         <v>2.871797056878281</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.649640248093752</v>
+        <v>-4.644846425700164</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.011584533327033</v>
+        <v>1.013502062284468</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.3672387067572803</v>
+        <v>-0.3472071382428245</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.651453832823913</v>
+        <v>2.663472773932587</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430699</v>
+        <v>3.729146398430696</v>
       </c>
       <c r="C1935" t="n">
         <v>2.871869458251693</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.652109954555558</v>
+        <v>-4.64731613216197</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.010669052115723</v>
+        <v>1.012586581073158</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3697084132190864</v>
+        <v>-0.3496768447046307</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.650044410320242</v>
+        <v>2.662063351428915</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003608</v>
+        <v>3.743220196003604</v>
       </c>
       <c r="C1936" t="n">
         <v>2.882876380726395</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.720480140879568</v>
+        <v>-4.715686318485981</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.9943279000608209</v>
+        <v>0.9962454290182559</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3604327141828715</v>
+        <v>-0.3404011456684157</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.666616752216672</v>
+        <v>2.678635693325346</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508376</v>
+        <v>3.714179139508372</v>
       </c>
       <c r="C1937" t="n">
         <v>2.873313089358287</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.734268193726614</v>
+        <v>-4.729474371333027</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9792493875538935</v>
+        <v>0.9811669165113284</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3604327141828715</v>
+        <v>-0.3404011456684157</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.657053460848564</v>
+        <v>2.669072401957237</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417711</v>
+        <v>3.710906731417706</v>
       </c>
       <c r="C1938" t="n">
         <v>2.698022654398673</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.76526135305532</v>
+        <v>-4.760467530661733</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.7915616888627981</v>
+        <v>0.793479217820233</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3604327141828715</v>
+        <v>-0.3404011456684157</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.48176302588895</v>
+        <v>2.493781966997624</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205906</v>
+        <v>3.746042526205903</v>
       </c>
       <c r="C1939" t="n">
         <v>2.702589886390461</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.589787093262851</v>
+        <v>-4.584993270869264</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.8663186247715735</v>
+        <v>0.8682361537290084</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.3604327141828715</v>
+        <v>-0.3404011456684157</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.486330257880739</v>
+        <v>2.498349198989412</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225451</v>
+        <v>3.765024323225448</v>
       </c>
       <c r="C1940" t="n">
         <v>2.678331915151668</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.7007233459041</v>
+        <v>-4.695929523510513</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.7976861524762811</v>
+        <v>0.799603681433716</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.3604327141828715</v>
+        <v>-0.3404011456684157</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.462072286641946</v>
+        <v>2.474091227750619</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.7732102971113</v>
+        <v>3.773210297111296</v>
       </c>
       <c r="C1941" t="n">
         <v>2.681463300371574</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.667059800431818</v>
+        <v>-4.662265978038231</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8142829558850995</v>
+        <v>0.8162004848425344</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.3267691687105896</v>
+        <v>-0.3067376001961339</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.48540179914522</v>
+        <v>2.497420740253894</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.78434395226417</v>
+        <v>3.784343952264165</v>
       </c>
       <c r="C1942" t="n">
         <v>2.691635686803706</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.607207181228095</v>
+        <v>-4.602413358834507</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.848396389998721</v>
+        <v>0.8503139189561559</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.3267691687105896</v>
+        <v>-0.3067376001961339</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.495574185577353</v>
+        <v>2.507593126686026</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742306</v>
+        <v>3.786949957742301</v>
       </c>
       <c r="C1943" t="n">
         <v>2.686581957377566</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.520963718201717</v>
+        <v>-4.51616989580813</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8778400457831324</v>
+        <v>0.8797575747405673</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.3267691687105896</v>
+        <v>-0.3067376001961339</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.490520456151213</v>
+        <v>2.502539397259886</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316053</v>
+        <v>3.752027499316048</v>
       </c>
       <c r="C1944" t="n">
         <v>2.678357732822092</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.566270537600697</v>
+        <v>-4.561476715207109</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.851493093468066</v>
+        <v>0.8534106224255009</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.3675793317198204</v>
+        <v>-0.3475477632053647</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.4578101337902</v>
+        <v>2.469829074898874</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803198</v>
+        <v>3.753571165803193</v>
       </c>
       <c r="C1945" t="n">
         <v>2.678909605855194</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.595303642302998</v>
+        <v>-4.590509819909411</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8404317246202471</v>
+        <v>0.842349253577682</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.3675793317198204</v>
+        <v>-0.3475477632053647</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.458362006823302</v>
+        <v>2.470380947931975</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809504</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
         <v>2.608182297746559</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.502493160852138</v>
+        <v>-4.497699338458551</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8068286090919567</v>
+        <v>0.8087461380493917</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.2747688502689611</v>
+        <v>-0.2547372817545053</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.443320987585183</v>
+        <v>2.455339928693856</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560431</v>
+        <v>3.748285816560428</v>
       </c>
       <c r="C1947" t="n">
         <v>2.61005577367116</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.546882630181566</v>
+        <v>-4.542088807787978</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.7909462972847865</v>
+        <v>0.7928638262422214</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.3191583195983888</v>
+        <v>-0.299126751083933</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.418560781912127</v>
+        <v>2.4305797230208</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472744</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
         <v>2.605131482182883</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.434211411945316</v>
+        <v>-4.429417589551728</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8310904930910095</v>
+        <v>0.8330080220484444</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.2064871013621385</v>
+        <v>-0.1864555328476828</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.4812392213656</v>
+        <v>2.493258162474274</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798543</v>
+        <v>3.74304760379854</v>
       </c>
       <c r="C1949" t="n">
         <v>2.61062277801355</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.321834410762643</v>
+        <v>-4.317040588369055</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.8815325893947459</v>
+        <v>0.8834501183521808</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.2064871013621385</v>
+        <v>-0.1864555328476828</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.486730517196267</v>
+        <v>2.498749458304941</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498871</v>
+        <v>3.689597840498867</v>
       </c>
       <c r="C1950" t="n">
         <v>2.622119979782089</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.349614808663995</v>
+        <v>-4.344820986270408</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.881917632002744</v>
+        <v>0.8838351609601789</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.2342674992634916</v>
+        <v>-0.2142359307490359</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.481559480223995</v>
+        <v>2.493578421332668</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705332</v>
+        <v>3.643069621705328</v>
       </c>
       <c r="C1951" t="n">
         <v>2.460475699782743</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.432616089689274</v>
+        <v>-4.427822267295687</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6870728395932857</v>
+        <v>0.6889903685507206</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2528383837906654</v>
+        <v>-0.2328068152762096</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.308772669508344</v>
+        <v>2.320791610617017</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729277</v>
+        <v>3.682716310729272</v>
       </c>
       <c r="C1952" t="n">
         <v>2.580625360501948</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.541230168132605</v>
+        <v>-4.536436345739018</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7637768689351589</v>
+        <v>0.7656943978925939</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2528383837906654</v>
+        <v>-0.2328068152762096</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.428922330227549</v>
+        <v>2.440941271336223</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190776</v>
+        <v>3.733012441190771</v>
       </c>
       <c r="C1953" t="n">
         <v>2.595138386604271</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.505821129884462</v>
+        <v>-4.501027307490875</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7924535103367389</v>
+        <v>0.7943710392941739</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2528383837906654</v>
+        <v>-0.2328068152762096</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.443435356329872</v>
+        <v>2.455454297438546</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913433</v>
+        <v>3.741174069913429</v>
       </c>
       <c r="C1954" t="n">
         <v>2.59255782794664</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.467437467326311</v>
+        <v>-4.462643644932724</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8052264167023682</v>
+        <v>0.8071439456598031</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.2144547212325142</v>
+        <v>-0.1944231527180584</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.463884995207132</v>
+        <v>2.475903936315805</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532494</v>
+        <v>3.751147197532489</v>
       </c>
       <c r="C1955" t="n">
         <v>2.589286856791942</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.290321137291145</v>
+        <v>-4.285527314897558</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8728019775617364</v>
+        <v>0.8747195065191713</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.2144547212325142</v>
+        <v>-0.1944231527180584</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.460614024052433</v>
+        <v>2.472632965161107</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793912</v>
+        <v>3.741328448793907</v>
       </c>
       <c r="C1956" t="n">
         <v>2.589970248553855</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.335413382124691</v>
+        <v>-4.330619559731104</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8554484713902313</v>
+        <v>0.8573660003476662</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.276350764401904</v>
+        <v>-0.2563191958874482</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.424159789912713</v>
+        <v>2.436178731021386</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011244</v>
+        <v>3.75072937701124</v>
       </c>
       <c r="C1957" t="n">
         <v>2.583757223860269</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.156037960885923</v>
+        <v>-4.151244138492336</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9209856151921527</v>
+        <v>0.9229031441495876</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.1195740062311853</v>
+        <v>-0.09954243771672955</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.512012820121558</v>
+        <v>2.524031761230232</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982238</v>
+        <v>3.716991718982234</v>
       </c>
       <c r="C1958" t="n">
         <v>2.564564679191859</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.201052174406529</v>
+        <v>-4.196258352012942</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8837873851155003</v>
+        <v>0.8857049140729352</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.1499229015457899</v>
+        <v>-0.1298913330313342</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.474610938264385</v>
+        <v>2.486629879373059</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509547</v>
+        <v>3.737026608509542</v>
       </c>
       <c r="C1959" t="n">
         <v>2.570256241530805</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.468056684678964</v>
+        <v>-4.463262862285377</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.782677143345472</v>
+        <v>0.7845946723029069</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.3442859395887385</v>
+        <v>-0.3242543710742827</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.363684677777562</v>
+        <v>2.375703618886235</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760818</v>
+        <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
         <v>2.569460163427306</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.569254466116137</v>
+        <v>-4.564460643722549</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7414019526671043</v>
+        <v>0.7433194816245392</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.4126947531340577</v>
+        <v>-0.3926631846196019</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.321843311546872</v>
+        <v>2.333862252655545</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815463</v>
+        <v>3.705571661815458</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.567060124981623</v>
+        <v>2.620583061980939</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.562743499501824</v>
+        <v>-4.557949677108237</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7416063008671461</v>
+        <v>0.7970467668238974</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.4126947531340577</v>
+        <v>-0.3926631846196019</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.319443273101188</v>
+        <v>2.384985151209178</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378107</v>
+        <v>3.709510443378104</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.563584844189868</v>
+        <v>2.617107781189184</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.543705371794527</v>
+        <v>-4.53891154940094</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7457462711583098</v>
+        <v>0.8011867371150612</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4708783644652522</v>
+        <v>-0.4508467959507965</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.281057825510717</v>
+        <v>2.346599703618707</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131259</v>
+        <v>3.731064473131254</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.741166713128548</v>
+        <v>2.794689650127865</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.574832002945145</v>
+        <v>-4.570038180551558</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9108774876367431</v>
+        <v>0.9663179535934945</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4708783644652522</v>
+        <v>-0.4508467959507965</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.458639694449397</v>
+        <v>2.524181572557387</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067875</v>
+        <v>3.72244736206787</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.742000042114682</v>
+        <v>2.795522979113998</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.588698764279063</v>
+        <v>-4.583904941885476</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9061641120893094</v>
+        <v>0.9616045780460607</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.5087362811990752</v>
+        <v>-0.4887047126846194</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.436758273395237</v>
+        <v>2.502300151503227</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789131</v>
+        <v>3.787425580789126</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.748008572511608</v>
+        <v>2.801531509510924</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.543894592739133</v>
+        <v>-4.539100770345546</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9300943111022073</v>
+        <v>0.9855347770589586</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.5087362811990752</v>
+        <v>-0.4887047126846194</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.442766803792163</v>
+        <v>2.508308681900153</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519918</v>
+        <v>3.781501250519913</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.82716122030363</v>
+        <v>2.880684157302946</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.396151622504131</v>
+        <v>-4.391357800110543</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.06834414698823</v>
+        <v>1.123784612944982</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.3409289239641921</v>
+        <v>-0.3208973554497362</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.622603865925115</v>
+        <v>2.688145744033105</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918118</v>
+        <v>3.802245929181175</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.829954841835111</v>
+        <v>2.883477778834427</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.498166305035352</v>
+        <v>-4.493372482641765</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.030331895507223</v>
+        <v>1.085772361463974</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.3409289239641921</v>
+        <v>-0.3208973554497362</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.625397487456596</v>
+        <v>2.690939365564586</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560898539474</v>
+        <v>3.805608985394735</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.830617190226769</v>
+        <v>2.884140127226086</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.492013598982568</v>
+        <v>-4.48721977658898</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.033455326319995</v>
+        <v>1.088895792276746</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.3347762179114078</v>
+        <v>-0.314744649396952</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.629751459479925</v>
+        <v>2.695293337587915</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890617</v>
+        <v>3.798239794890614</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.829697666966879</v>
+        <v>2.883220603966196</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.508822897133069</v>
+        <v>-4.504029074739482</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.025812083799904</v>
+        <v>1.081252549756656</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.3515855160619094</v>
+        <v>-0.3315539475474536</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.618746357329734</v>
+        <v>2.684288235437724</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798434</v>
+        <v>3.867362636798429</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.8960332207637</v>
+        <v>2.949556157763017</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.446524898356947</v>
+        <v>-4.44173107596336</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.117066837107174</v>
+        <v>1.172507303063925</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.3515855160619094</v>
+        <v>-0.3315539475474536</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.685081911126555</v>
+        <v>2.750623789234545</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992201</v>
+        <v>3.848729139992196</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.604614093153098</v>
+        <v>2.658137030152415</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.244734700691789</v>
+        <v>-4.239940878298202</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9063637885626354</v>
+        <v>0.9618042545193868</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.153567323892755</v>
+        <v>-0.1335357553782992</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.512473698817446</v>
+        <v>2.578015576925436</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852431</v>
+        <v>3.841444817852426</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.674904325475274</v>
+        <v>2.72842726247459</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.171356603603053</v>
+        <v>-4.166562781209466</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.006005259720305</v>
+        <v>1.061445725677056</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.08018922680401847</v>
+        <v>-0.06015765828956265</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.626790789392863</v>
+        <v>2.692332667500853</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319556</v>
+        <v>3.81906330031955</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.689532061591317</v>
+        <v>2.743054998590634</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.269097148228028</v>
+        <v>-4.26430332583444</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9815367779863589</v>
+        <v>1.03697724394311</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.09607850493699865</v>
+        <v>-0.07604693642254284</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.631884958629118</v>
+        <v>2.697426836737108</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489395</v>
+        <v>3.831819032489388</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.688068042415989</v>
+        <v>2.741590979415305</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.445434908350957</v>
+        <v>-4.44064108595737</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9095376547618588</v>
+        <v>0.9649781207186101</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.2724162650599281</v>
+        <v>-0.2523846965454722</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.524618283380032</v>
+        <v>2.590160161488022</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397804</v>
+        <v>3.836411672397798</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.686559660455917</v>
+        <v>2.740082597455234</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.36901286191903</v>
+        <v>-4.364219039525443</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9385980913745582</v>
+        <v>0.9940385573313095</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.2724162650599281</v>
+        <v>-0.2523846965454722</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.523109901419961</v>
+        <v>2.588651779527951</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316259</v>
+        <v>3.833513460316253</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.686422527891354</v>
+        <v>2.73994546489067</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.324639730280461</v>
+        <v>-4.319845907886874</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9562102114654218</v>
+        <v>1.011650677422173</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.2280431334213595</v>
+        <v>-0.2080115649069036</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.549596647838538</v>
+        <v>2.615138525946528</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105973</v>
+        <v>3.821562117105967</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.680816322029944</v>
+        <v>2.734339259029261</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.201805509393294</v>
+        <v>-4.197011686999707</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9997376939588793</v>
+        <v>1.055178159915631</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.2280431334213595</v>
+        <v>-0.2080115649069036</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.543990441977129</v>
+        <v>2.609532320085119</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190332</v>
+        <v>3.833011148190325</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.687198079057748</v>
+        <v>2.740721016057065</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.154149778832238</v>
+        <v>-4.149355956438651</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.025181743211106</v>
+        <v>1.080622209167857</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.1803874028603038</v>
+        <v>-0.160355834345848</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.578965637341566</v>
+        <v>2.644507515449556</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569624</v>
+        <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.692090452432473</v>
+        <v>2.74561338943179</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.053631620333483</v>
+        <v>-4.048837797939896</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.070281379985333</v>
+        <v>1.125721845942084</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.07986924436154924</v>
+        <v>-0.05983767584709343</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.644168905815544</v>
+        <v>2.709710783923534</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557299</v>
+        <v>3.828808877557293</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.678845124908345</v>
+        <v>2.732368061907662</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.114298210735873</v>
+        <v>-4.109504388342286</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.032769416300249</v>
+        <v>1.088209882257</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.1615675610800829</v>
+        <v>-0.1415359925656271</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.581904588260296</v>
+        <v>2.647446466368286</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932774</v>
+        <v>3.816837033932769</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.682942827518974</v>
+        <v>2.73646576451829</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.069459809127475</v>
+        <v>-4.064665986733887</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.054802479554237</v>
+        <v>1.110242945510988</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.1570241281352134</v>
+        <v>-0.1369925596207576</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.588728350637846</v>
+        <v>2.654270228745836</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917058</v>
+        <v>3.817932354917053</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.687103767150052</v>
+        <v>2.740626704149368</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.170218444884473</v>
+        <v>-4.165424622490885</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.018659964882516</v>
+        <v>1.074100430839267</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.2458496968622189</v>
+        <v>-0.225818128347763</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.539593949032721</v>
+        <v>2.605135827140711</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405967</v>
+        <v>3.826684745405962</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.692983369677889</v>
+        <v>2.746506306677206</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.126015607798572</v>
+        <v>-4.121221785404985</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.042220702244713</v>
+        <v>1.097661168201464</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.2016468597763184</v>
+        <v>-0.1816152912618626</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.571995253812098</v>
+        <v>2.637537131920088</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265652</v>
+        <v>3.838199629265647</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.691393370147137</v>
+        <v>2.744916307146453</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.162994635462015</v>
+        <v>-4.158200813068428</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.025839091648583</v>
+        <v>1.081279557605335</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.1646729579849879</v>
+        <v>-0.1446413894705321</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.592589595356144</v>
+        <v>2.658131473464134</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284887</v>
+        <v>3.863895080284881</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.742641135330176</v>
+        <v>2.796164072329493</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.183052714326855</v>
+        <v>-4.178258891933268</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.069063625285687</v>
+        <v>1.124504091242438</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.1646729579849879</v>
+        <v>-0.1446413894705321</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.643837360539184</v>
+        <v>2.709379238647174</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321029</v>
+        <v>3.865338681321024</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.741081839924429</v>
+        <v>2.794604776923746</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.143122041148965</v>
+        <v>-4.138328218755378</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.083476599151096</v>
+        <v>1.138917065107848</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.1247422848070975</v>
+        <v>-0.1047107162926417</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.666236469040171</v>
+        <v>2.731778347148161</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475146</v>
+        <v>3.864489842475141</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.736030068162699</v>
+        <v>2.789553005162016</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.092089948426437</v>
+        <v>-4.08729612603285</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.098837664478377</v>
+        <v>1.154278130435129</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.07371019208456958</v>
+        <v>-0.05367862357011377</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.691803952911958</v>
+        <v>2.757345831019948</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404862</v>
+        <v>3.842547360404857</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.753217472255404</v>
+        <v>2.806740409254721</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.026865767299232</v>
+        <v>-4.022071944905645</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.142114741021964</v>
+        <v>1.197555206978716</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.008486010957363954</v>
+        <v>0.01154555755709186</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.748125865680986</v>
+        <v>2.813667743788976</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882566</v>
+        <v>3.84006118688256</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.749178444554685</v>
+        <v>2.802701381554001</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.989438747228098</v>
+        <v>-3.984644924834511</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.153046521349698</v>
+        <v>1.208486987306449</v>
       </c>
       <c r="F1989" t="n">
-        <v>-0.003234472928182297</v>
+        <v>0.01679709558627351</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.747237760797776</v>
+        <v>2.812779638905766</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84516980899267</v>
+        <v>3.845169808992665</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.750435236885925</v>
+        <v>2.803958173885241</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.009550403262806</v>
+        <v>-4.00475658086922</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.146258651267055</v>
+        <v>1.201699117223807</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.0077928720692369</v>
+        <v>0.02782444058369271</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.755110960127467</v>
+        <v>2.820652838235457</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636296</v>
+        <v>3.828661445636291</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.910993007907136</v>
+        <v>2.964515944906452</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.955805588835601</v>
+        <v>-3.951011766442015</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.328314348059148</v>
+        <v>1.383754814015899</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.01785618150969887</v>
+        <v>0.03788775002415468</v>
       </c>
       <c r="G1991" t="n">
-        <v>2.921706716812955</v>
+        <v>2.987248594920945</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957634</v>
+        <v>3.813222820957629</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.031105917124953</v>
+        <v>3.084628854124269</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.932014020229459</v>
+        <v>-3.927220197835873</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.457943884719422</v>
+        <v>1.513384350676173</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.04164775011584115</v>
+        <v>0.06167931863029696</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.056094567194458</v>
+        <v>3.121636445302448</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.81423072799876</v>
+        <v>3.814230727998755</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.022813893138812</v>
+        <v>3.076336830138128</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.905929935965651</v>
+        <v>-3.901136113572065</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.460085494438804</v>
+        <v>1.515525960395555</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.04164775011584115</v>
+        <v>0.06167931863029696</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.047802543208317</v>
+        <v>3.113344421316307</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896934</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.021007088722591</v>
+        <v>3.074530025721908</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.775637405036041</v>
+        <v>-3.770843582642455</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.510395702394428</v>
+        <v>1.565836168351179</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.278183374643576</v>
+        <v>0.2982149431580318</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.187917113508737</v>
+        <v>3.253458991616727</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959863</v>
+        <v>3.796264143959859</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.038561494449383</v>
+        <v>3.092084431448699</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.766744943642758</v>
+        <v>-3.761951121249172</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.531507092678532</v>
+        <v>1.586947558635283</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.278183374643576</v>
+        <v>0.2982149431580318</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.205471519235529</v>
+        <v>3.271013397343518</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945373</v>
+        <v>3.794424941945367</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.030416541853967</v>
+        <v>3.083939478853283</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.935221060612636</v>
+        <v>-3.93042723821905</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.455971693295165</v>
+        <v>1.511412159251916</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.2502355389269952</v>
+        <v>0.270267107441451</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.180557865210164</v>
+        <v>3.246099743318154</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782715</v>
+        <v>3.795574066782709</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.011686239041829</v>
+        <v>3.065209176041145</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.237421531751052</v>
+        <v>-3.232627709357466</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.71636120202766</v>
+        <v>1.771801667984411</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.1798874795565845</v>
+        <v>0.1999190480710403</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.11961872677578</v>
+        <v>3.18516060488377</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632645</v>
+        <v>3.784671345632639</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.002350261538733</v>
+        <v>3.05587319853805</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.2147004280679</v>
+        <v>-3.209906605674314</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.716113665997826</v>
+        <v>1.771554131954577</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.1798874795565845</v>
+        <v>0.1999190480710403</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.110282749272684</v>
+        <v>3.175824627380674</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777682</v>
+        <v>3.783205696777677</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.161256387389902</v>
+        <v>3.214779324389219</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.212975384777856</v>
+        <v>-3.20818156238427</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.875709809165013</v>
+        <v>1.931150275121763</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.1816125228466282</v>
+        <v>0.201644091361084</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.27022390109788</v>
+        <v>3.335765779205869</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644421</v>
+        <v>3.779933725644415</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.198334209883549</v>
+        <v>3.251857146882865</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.367756391556111</v>
+        <v>-3.362962569162525</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.850875228947357</v>
+        <v>1.906315694904108</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.1482448487921521</v>
+        <v>0.1682764173066079</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.28728111915884</v>
+        <v>3.35282299726683</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799969</v>
+        <v>3.769443619799964</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.195009565873094</v>
+        <v>3.24853250287241</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.316321058171452</v>
+        <v>-3.311527235777866</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.868124718290766</v>
+        <v>1.923565184247517</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.1996801821768118</v>
+        <v>0.2197117506912676</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.314817675179181</v>
+        <v>3.380359553287171</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331124</v>
+        <v>3.766673496331119</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.205015719517835</v>
+        <v>3.258538656517152</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.289369833844964</v>
+        <v>-3.284576011451378</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.888911361666103</v>
+        <v>1.944351827622854</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.2145605282045309</v>
+        <v>0.2345920967189867</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.333752036440554</v>
+        <v>3.399293914548544</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784117</v>
+        <v>3.768052067784112</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.389118851662795</v>
+        <v>3.442641788662112</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.42532284190128</v>
+        <v>-3.420529019507694</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.018633290588536</v>
+        <v>2.074073756545287</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.2145605282045309</v>
+        <v>0.2345920967189867</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.517855168585514</v>
+        <v>3.583397046693504</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.74392550571443</v>
+        <v>3.743925505714425</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.381235546565788</v>
+        <v>3.434758483565105</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.447730959706152</v>
+        <v>-3.442937137312566</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.001786738369581</v>
+        <v>2.057227204326331</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.2145605282045309</v>
+        <v>0.2345920967189867</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.509971863488507</v>
+        <v>3.575513741596497</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155042</v>
+        <v>3.719118627155035</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.383289546115426</v>
+        <v>3.436812483114742</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.595736727185551</v>
+        <v>-3.590942904791965</v>
       </c>
       <c r="E2005" t="n">
-        <v>1.944638430927458</v>
+        <v>2.000078896884209</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.1278335193409895</v>
+        <v>0.1478650878554453</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.45998965772002</v>
+        <v>3.525531535828009</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161987</v>
+        <v>3.72945228516198</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.439543263837273</v>
+        <v>3.493066200836589</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.605177653074081</v>
+        <v>-3.600383830680495</v>
       </c>
       <c r="E2006" t="n">
-        <v>1.997115778293893</v>
+        <v>2.052556244250644</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.2502606368843809</v>
+        <v>0.2702922053988367</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.589699645967902</v>
+        <v>3.655241524075892</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321644</v>
+        <v>3.714941193321637</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.442434358382574</v>
+        <v>3.49595729538189</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.603890889534525</v>
+        <v>-3.599097067140939</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.000521578255016</v>
+        <v>2.055962044211768</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.2515474004239375</v>
+        <v>0.2715789689383933</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.593362798636937</v>
+        <v>3.658904676744926</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347712</v>
+        <v>3.727898186347706</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.440546171276349</v>
+        <v>3.494069108275665</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.605447943523816</v>
+        <v>-3.60065412113023</v>
       </c>
       <c r="E2008" t="n">
-        <v>1.998010569553075</v>
+        <v>2.053451035509826</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.2515474004239375</v>
+        <v>0.2715789689383933</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.591474611530712</v>
+        <v>3.657016489638702</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887756</v>
+        <v>3.71065410488775</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.435366400879211</v>
+        <v>3.488889337878528</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.612719829047281</v>
+        <v>-3.607926006653695</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.989922044946552</v>
+        <v>2.045362510903303</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.2442755149004727</v>
+        <v>0.2643070834149285</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.581931709819495</v>
+        <v>3.647473587927485</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343074</v>
+        <v>3.712897612343068</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.433800411089364</v>
+        <v>3.48732334808868</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.61087880998903</v>
+        <v>-3.606084987595444</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.989092462780004</v>
+        <v>2.044532928736755</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.2455437415719411</v>
+        <v>0.265575310086397</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.581126656032529</v>
+        <v>3.646668534140519</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647115</v>
+        <v>3.754911907647108</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.446873817955282</v>
+        <v>3.500396754954599</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.61778751548871</v>
+        <v>-3.612993693095124</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.999402387446051</v>
+        <v>2.054842853402802</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.2455437415719411</v>
+        <v>0.265575310086397</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.594200062898447</v>
+        <v>3.659741941006437</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763538</v>
+        <v>3.749896851763532</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.446873817955282</v>
+        <v>3.500396754954599</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.61934915830357</v>
+        <v>-3.815981132847049</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.998777730320107</v>
+        <v>1.973647877502032</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.2455437415719411</v>
+        <v>0.265575310086397</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.594200062898447</v>
+        <v>3.659741941006437</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.831785640062565</v>
+        <v>3.567820824833606</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.602751568594131</v>
+        <v>3.426250199803954</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.61934915830357</v>
+        <v>-3.815981132847049</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.998777730320107</v>
+        <v>1.973647877502032</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.2455437415719411</v>
+        <v>0.265575310086397</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.595815365580499</v>
+        <v>3.419313996790322</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240702.xlsx
+++ b/tame_output/ON/bt/strategyON_20240702.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -671,17 +671,17 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>50.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>72.8%</t>
+          <t>82.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,17 +819,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-33.6%</t>
+          <t>-21.1%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>58.9%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.2%</t>
+          <t>-72.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.2%</t>
+          <t>108.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.7%</t>
+          <t>122.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,12 +982,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.3%</t>
+          <t>-48.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.2%</t>
+          <t>-67.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>90.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>449.0%</t>
+          <t>452.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-12.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-543.2%</t>
+          <t>-506.5%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1140,22 +1140,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.5%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-37.8%</t>
+          <t>-36.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-24.8%</t>
+          <t>-29.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-37.2%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-178.9%</t>
+          <t>-156.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-19.2%</t>
+          <t>-19.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.2%</t>
+          <t>-33.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-12.7%</t>
+          <t>-12.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-40.0%</t>
+          <t>-30.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-171.4%</t>
+          <t>-171.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-197.4%</t>
+          <t>-196.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.2%</t>
+          <t>96.1%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.2%</t>
+          <t>-26.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-18.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-104.1%</t>
+          <t>-76.2%</t>
         </is>
       </c>
     </row>
@@ -43727,7 +43727,7 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045693</v>
+        <v>3.317575502045692</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.36737053999856</v>
+        <v>3.367370539998559</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082124</v>
+        <v>3.299560092082123</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757923</v>
+        <v>3.293490533757921</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760741</v>
+        <v>3.293766719760739</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706669</v>
+        <v>3.298730590706668</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911641</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213498</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416047</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130018</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178244</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.305316798207813</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310981</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006532</v>
+        <v>3.305849539006533</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309423</v>
+        <v>3.311086391309425</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970904</v>
+        <v>3.304715716970906</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330522</v>
+        <v>3.300815818330523</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191736</v>
+        <v>3.302618194191738</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108638</v>
+        <v>3.30502326510864</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.34137872309782</v>
+        <v>3.341378723097822</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094116</v>
+        <v>3.374439043094117</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199285</v>
+        <v>3.405960511199287</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969592</v>
+        <v>3.424633354969594</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923086</v>
+        <v>3.419979433923087</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297748</v>
+        <v>3.45810009129775</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317617</v>
+        <v>3.447750501317619</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.503515506737172</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539464</v>
+        <v>3.501052558539466</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937501</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141704</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.873404154998514</v>
+        <v>-9.703230192411484</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8093979940579059</v>
+        <v>-0.7413284090230938</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.310144017951603</v>
+        <v>-2.285159678283608</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.754233681484286</v>
+        <v>1.769224285285083</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.496851904729893</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.947737131258679</v>
+        <v>-9.777563168671648</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.834648630077536</v>
+        <v>-0.7665790450427235</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.454843541886275</v>
+        <v>-2.42985920221828</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.671896521607918</v>
+        <v>1.686887125408715</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440636</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.87426729959123</v>
+        <v>-9.704093337004199</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.7898889959171349</v>
+        <v>-0.7218194108823228</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.381373710218827</v>
+        <v>-2.356389370550832</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.731350122101808</v>
+        <v>1.746340725902605</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.490059241608602</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.04939171697777</v>
+        <v>-9.879217754390742</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8453835421242353</v>
+        <v>-0.7773139570894232</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.556498127605371</v>
+        <v>-2.531513787937376</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.640830692417399</v>
+        <v>1.655821296218196</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.28384381099226</v>
+        <v>-10.11366984840523</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9463835446316273</v>
+        <v>-0.8783139595968152</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.556498127605371</v>
+        <v>-2.531513787937376</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.633611527515803</v>
+        <v>1.6486021313166</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764398</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.38821854201871</v>
+        <v>-10.21804457943168</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.9948056278161821</v>
+        <v>-0.92673604278137</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.660872858631816</v>
+        <v>-2.635888518963821</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.564314498125959</v>
+        <v>1.579305101926756</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.44100469761904</v>
+        <v>-10.27083073503201</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.014804300217756</v>
+        <v>-0.9467347151829442</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.756548345214213</v>
+        <v>-2.731564005546218</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.508024996015078</v>
+        <v>1.523015599815875</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.4921016412974</v>
+        <v>3.492101641297401</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.56704149098733</v>
+        <v>-10.39686752840029</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.062525288935957</v>
+        <v>-0.9944557039011452</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.731296722404471</v>
+        <v>-2.706312382736476</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.525869698330037</v>
+        <v>1.540860302130834</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322545</v>
+        <v>3.573674025322546</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.51502597701851</v>
+        <v>-10.34485201443148</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.037728747662031</v>
+        <v>-0.9696591626272193</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.731296722404471</v>
+        <v>-2.706312382736476</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.529860034016438</v>
+        <v>1.544850637817235</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158923</v>
+        <v>3.600038265158924</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.65669781874263</v>
+        <v>-10.4865238561556</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.095872711250421</v>
+        <v>-1.027803126215609</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.731296722404471</v>
+        <v>-2.706312382736476</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.528384807117697</v>
+        <v>1.543375410918494</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940721</v>
+        <v>3.691571733940722</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.6071069743178</v>
+        <v>-10.43693301173077</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.060982963315615</v>
+        <v>-0.9929133782808033</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.681705877979637</v>
+        <v>-2.656721538311642</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.573192723937469</v>
+        <v>1.588183327738266</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770582</v>
+        <v>3.676841549770583</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.59429958131302</v>
+        <v>-10.42412561872599</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.068911139760389</v>
+        <v>-1.000841554725576</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.730561652988538</v>
+        <v>-2.705577313320543</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.530828125285446</v>
+        <v>1.545818729086243</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615285</v>
+        <v>3.685161381615287</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.36845442859361</v>
+        <v>-10.19828046600658</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.9689940056364157</v>
+        <v>-0.9009244206016036</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.688634977401374</v>
+        <v>-2.66365063773338</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.565563203673952</v>
+        <v>1.580553807474749</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812104</v>
+        <v>3.684843823812106</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.24387577225602</v>
+        <v>-10.07370180966899</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9180233985453197</v>
+        <v>-0.8499538135105085</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.688634977401374</v>
+        <v>-2.66365063773338</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.566702348230011</v>
+        <v>1.581692952030808</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646218</v>
+        <v>3.710935533646221</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.29677106030031</v>
+        <v>-10.12659709771328</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9365477396009263</v>
+        <v>-0.8684781545661151</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.683679631312928</v>
+        <v>-2.658695291644933</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.572309330045187</v>
+        <v>1.587299933845984</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.76895167461157</v>
+        <v>3.768951674611572</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.22463788501243</v>
+        <v>-10.0544639224254</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9019607652471375</v>
+        <v>-0.8338911802123263</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.683679631312928</v>
+        <v>-2.658695291644933</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.578043034283823</v>
+        <v>1.59303363808462</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955329</v>
+        <v>3.728577929955332</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.15327149240278</v>
+        <v>-9.983097529815749</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8831514705971442</v>
+        <v>-0.8150818855623325</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.61231323870328</v>
+        <v>-2.587328899035285</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.611125607455747</v>
+        <v>1.626116211256544</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232415</v>
+        <v>3.747702660232417</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.05981245841755</v>
+        <v>-9.889638495830525</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8556513383159614</v>
+        <v>-0.7875817532811502</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.61231323870328</v>
+        <v>-2.587328899035285</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.601242126142839</v>
+        <v>1.616232729943636</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436231</v>
+        <v>3.766317079436234</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.792570657549156</v>
+        <v>-9.622396694962127</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7505891784679766</v>
+        <v>-0.6825195934331649</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.61231323870328</v>
+        <v>-2.587328899035285</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.599407565643466</v>
+        <v>1.614398169444263</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311951</v>
+        <v>3.784684521311954</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.694663618872665</v>
+        <v>-9.524489656285636</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7117266779708409</v>
+        <v>-0.6436570929360292</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.544327488842724</v>
+        <v>-2.519343149174729</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.639898700586339</v>
+        <v>1.654889304387136</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097247</v>
+        <v>3.80082935409725</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.670710077896707</v>
+        <v>-9.500536115309679</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7014767554349643</v>
+        <v>-0.6334071704001527</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.520373947866766</v>
+        <v>-2.495389608198771</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.654939331317407</v>
+        <v>1.669929935118204</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017775</v>
+        <v>3.789311112017778</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.406650139573911</v>
+        <v>-9.236476176986882</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6091130962675977</v>
+        <v>-0.541043511232786</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.25631400954397</v>
+        <v>-2.231329669875975</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.800114978149332</v>
+        <v>1.815105581950129</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839728</v>
+        <v>3.83325274783973</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.699570516069073</v>
+        <v>-8.529396553482044</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3290682805259637</v>
+        <v>-0.2609986954911521</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.25631400954397</v>
+        <v>-2.231329669875975</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.797327944489031</v>
+        <v>1.812318548289828</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388732</v>
+        <v>3.839374447388735</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.659386217702883</v>
+        <v>-8.489212255115854</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3126509372916462</v>
+        <v>-0.2445813522568345</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.216129711177779</v>
+        <v>-2.191145371509784</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.821782147396587</v>
+        <v>1.836772751197384</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626478</v>
+        <v>3.856161751626481</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.495986346763519</v>
+        <v>-8.325812384176491</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2479241676951438</v>
+        <v>-0.1798545826603322</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.052729840238417</v>
+        <v>-2.027745500570422</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.919188891180962</v>
+        <v>1.934179494981759</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291814</v>
+        <v>3.787330429291817</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.26250512453392</v>
+        <v>-8.092331161946891</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1466072499654514</v>
+        <v>-0.07853766493064018</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.819248618008818</v>
+        <v>-1.794264278340823</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.067202053356573</v>
+        <v>2.08219265715737</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.80163712278579</v>
+        <v>3.801637122785793</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.028522268475006</v>
+        <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.108044911132819</v>
+        <v>-7.942664770939376</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.2150521202918685</v>
+        <v>-0.02156331884059304</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.706313558251827</v>
+        <v>-1.701360787098287</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.004734133523911</v>
+        <v>2.135042541589932</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.76318224839043</v>
+        <v>3.763182248390433</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.023889755222033</v>
+        <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.975769437501932</v>
+        <v>-7.81038929730849</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.166774444092487</v>
+        <v>0.02671435735878847</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.57403808462094</v>
+        <v>-1.569085313467401</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.07946690444947</v>
+        <v>2.209775312515491</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105955</v>
+        <v>3.784718794105957</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.02670481590967</v>
+        <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.82003110494219</v>
+        <v>-7.654650964748748</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1016640503809532</v>
+        <v>0.09182475107032184</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.418299752061198</v>
+        <v>-1.413346980907659</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.175724964672952</v>
+        <v>2.306033372738973</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.75388257196099</v>
+        <v>3.753882571960992</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.039611157133329</v>
+        <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.571031306258609</v>
+        <v>-7.405651166065167</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.01084221031613763</v>
+        <v>0.2043310117674131</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.418299752061198</v>
+        <v>-1.413346980907659</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.18863130589661</v>
+        <v>2.318939713962632</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607648</v>
+        <v>3.692931855607651</v>
       </c>
       <c r="C1908" t="n">
-        <v>2.91163522753411</v>
+        <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.676621296031714</v>
+        <v>-7.511241155838271</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.1593697151923226</v>
+        <v>0.03411908625895244</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.523889741834303</v>
+        <v>-1.518936970680764</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.997301382433529</v>
+        <v>2.127609790499551</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987906</v>
+        <v>3.77042258398791</v>
       </c>
       <c r="C1909" t="n">
-        <v>2.960179569411197</v>
+        <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.695356198150311</v>
+        <v>-7.529976057956868</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1183193341626749</v>
+        <v>0.07516946728860008</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.529485751494434</v>
+        <v>-1.524532980340895</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.042488118514536</v>
+        <v>2.172796526580558</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710815</v>
+        <v>3.760333686710818</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.840300646723029</v>
+        <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.547416156742711</v>
+        <v>-7.382036016549269</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1790222402878028</v>
+        <v>0.01446656116347222</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.509164835585876</v>
+        <v>-1.504212064432337</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.934801745371503</v>
+        <v>2.065110153437525</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409207</v>
+        <v>3.723566229409211</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.831586660469551</v>
+        <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.494446634488723</v>
+        <v>-7.32906649429528</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1665484176396856</v>
+        <v>0.02694038381158936</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.456195313331888</v>
+        <v>-1.451242542178349</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.957869472470418</v>
+        <v>2.08817788053644</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098111</v>
+        <v>3.729969716098115</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.824626048374458</v>
+        <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.450898227718032</v>
+        <v>-7.28551808752459</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1560896670265026</v>
+        <v>0.03739913442477238</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.456195313331888</v>
+        <v>-1.451242542178349</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.950908860375325</v>
+        <v>2.081217268441347</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.782922533493426</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.839088402755601</v>
+        <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.208749834264174</v>
+        <v>-7.043369694070732</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.04476795526381627</v>
+        <v>0.1487208461874587</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.456195313331888</v>
+        <v>-1.451242542178349</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.965371214756468</v>
+        <v>2.09567962282249</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722822</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.833620523214796</v>
+        <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.100490697141653</v>
+        <v>-6.93511055694821</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.006932179955612572</v>
+        <v>0.1865566214956624</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.456195313331888</v>
+        <v>-1.451242542178349</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.959903335215663</v>
+        <v>2.090211743281685</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792051</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.831118617225373</v>
+        <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.977199562324522</v>
+        <v>-6.811819422131079</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.03988236798181655</v>
+        <v>0.233371169433092</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.332904178514757</v>
+        <v>-1.327951407361218</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.031376110116518</v>
+        <v>2.16168451818254</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919908</v>
+        <v>3.812453678919913</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.838819595462698</v>
+        <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.956050363421078</v>
+        <v>-6.790670223227636</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.0560430257805189</v>
+        <v>0.2495318272317943</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.311754979611314</v>
+        <v>-1.306802208457775</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.05176660769591</v>
+        <v>2.182075015761932</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318094</v>
+        <v>3.748328408318099</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.834600303809748</v>
+        <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.712284921437634</v>
+        <v>-6.546904781244192</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1493299109209474</v>
+        <v>0.3428187123722228</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.311754979611314</v>
+        <v>-1.306802208457775</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.04754731604296</v>
+        <v>2.177855724108982</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057527</v>
+        <v>3.824311233057532</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.836724617729764</v>
+        <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.610522101160339</v>
+        <v>-6.445141960966897</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1921593529518812</v>
+        <v>0.3856481544031567</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.298535911218885</v>
+        <v>-1.293583140065346</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.057603070998434</v>
+        <v>2.187911479064455</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279192</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.829466692713467</v>
+        <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.360671707211265</v>
+        <v>-6.195291567017822</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2848415855152133</v>
+        <v>0.4783303869664888</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.298535911218885</v>
+        <v>-1.293583140065346</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.050345145982136</v>
+        <v>2.180653554048158</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011499</v>
+        <v>3.835957987011505</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.833065816234115</v>
+        <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.184779614743832</v>
+        <v>-6.01939947455039</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3587975460228354</v>
+        <v>0.5522863474741104</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.298535911218885</v>
+        <v>-1.293583140065346</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.053944269502785</v>
+        <v>2.184252677568806</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392994</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.846393322288669</v>
+        <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.013333151721368</v>
+        <v>-5.847953011527927</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4407036372863744</v>
+        <v>0.6341924387376494</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.127089448196422</v>
+        <v>-1.122136677042883</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.170139653370816</v>
+        <v>2.300448061436838</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.773765222632789</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.845413799904966</v>
+        <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.939043585983029</v>
+        <v>-5.773663445789587</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.469439941198007</v>
+        <v>0.662928742649282</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.052799882458083</v>
+        <v>-1.047847111304544</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.213733870430117</v>
+        <v>2.344042278496139</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883074</v>
+        <v>3.764617879883081</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.850108600959283</v>
+        <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.875407843749095</v>
+        <v>-5.710027703555653</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4995890391458984</v>
+        <v>0.6930778405971729</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.9891641402241481</v>
+        <v>-0.984211369070609</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.256610116824795</v>
+        <v>2.386918524890817</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074785</v>
+        <v>3.798814771074792</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.831302859743079</v>
+        <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.763981084423174</v>
+        <v>-5.598600944229733</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.525354001660062</v>
+        <v>0.718842803111337</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.9891641402241481</v>
+        <v>-0.984211369070609</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.23780437560859</v>
+        <v>2.368112783674612</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242296</v>
+        <v>3.797694884242303</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.833045936367956</v>
+        <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.523550587618314</v>
+        <v>-5.358170447424873</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6232692770068833</v>
+        <v>0.8167580784581583</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.7487336434192878</v>
+        <v>-0.7437808722657487</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.383805750316384</v>
+        <v>2.514114158382406</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367687</v>
+        <v>3.821593509367694</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.836975250202777</v>
+        <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.45130801944712</v>
+        <v>-5.285927879253678</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6560956181101814</v>
+        <v>0.8495844195614564</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.7487336434192878</v>
+        <v>-0.7437808722657487</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.387735064151204</v>
+        <v>2.518043472217226</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879967</v>
+        <v>3.822326997879975</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.837653834120117</v>
+        <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.398309697165732</v>
+        <v>-5.23292955697229</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6779735309400765</v>
+        <v>0.8714623323913515</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.693397384417349</v>
+        <v>-0.6884446132638099</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.421615403469707</v>
+        <v>2.551923811535729</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861662650234</v>
+        <v>3.848616626502347</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.83465190534011</v>
+        <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.289504811686005</v>
+        <v>-5.124124671492563</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.718493556351961</v>
+        <v>0.911982357803236</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.693397384417349</v>
+        <v>-0.6884446132638099</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.418613474689701</v>
+        <v>2.548921882755723</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675941</v>
+        <v>3.818668951675948</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.836230942350724</v>
+        <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.069484013648994</v>
+        <v>-4.904103873455552</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8080809125773794</v>
+        <v>1.001569714028654</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.5521775393493688</v>
+        <v>-0.5472247681958297</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.504924418741103</v>
+        <v>2.635232826807125</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539952</v>
+        <v>3.843274527539959</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.852125125152547</v>
+        <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.936616324585716</v>
+        <v>-4.771236184392275</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8771221710045136</v>
+        <v>1.070610972455789</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.5521775393493688</v>
+        <v>-0.5472247681958297</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.520818601542926</v>
+        <v>2.651127009608948</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496262</v>
+        <v>3.845047386496268</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.853270969592849</v>
+        <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.816443241221218</v>
+        <v>-4.651063101027776</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.926337248790615</v>
+        <v>1.11982605024189</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4320044559848698</v>
+        <v>-0.4270516848313307</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.594068296001928</v>
+        <v>2.72437670406795</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576999</v>
+        <v>3.791273551577005</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.863359072154289</v>
+        <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.67177109612148</v>
+        <v>-4.506390955928039</v>
       </c>
       <c r="E1932" t="n">
-        <v>0.9942942093919498</v>
+        <v>1.187783010843225</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.2873323108851324</v>
+        <v>-0.2823795397315933</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.69095968562321</v>
+        <v>2.821268093689232</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942104</v>
+        <v>3.73583922294211</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.849396563555715</v>
+        <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.731645923479173</v>
+        <v>-4.566265783285731</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9563817698502988</v>
+        <v>1.149870571301574</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.3472071382428245</v>
+        <v>-0.3422543670892854</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.64107228061002</v>
+        <v>2.771380688676042</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674516</v>
+        <v>3.762647477674522</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.871797056878281</v>
+        <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.644846425700164</v>
+        <v>-4.479466285506723</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.013502062284468</v>
+        <v>1.206990863735743</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.3472071382428245</v>
+        <v>-0.3422543670892854</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.663472773932587</v>
+        <v>2.793781181998608</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430696</v>
+        <v>3.729146398430701</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.871869458251693</v>
+        <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.64731613216197</v>
+        <v>-4.481935991968529</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.012586581073158</v>
+        <v>1.206075382524433</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3496768447046307</v>
+        <v>-0.3447240735510916</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.662063351428915</v>
+        <v>2.792371759494937</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003604</v>
+        <v>3.74322019600361</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.882876380726395</v>
+        <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.715686318485981</v>
+        <v>-4.550306178292539</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.9962454290182559</v>
+        <v>1.189734230469531</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3404011456684157</v>
+        <v>-0.3354483745148766</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.678635693325346</v>
+        <v>2.808944101391368</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508372</v>
+        <v>3.714179139508378</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.873313089358287</v>
+        <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.729474371333027</v>
+        <v>-4.564094231139586</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9811669165113284</v>
+        <v>1.174655717962603</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3404011456684157</v>
+        <v>-0.3354483745148766</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.669072401957237</v>
+        <v>2.799380810023259</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417706</v>
+        <v>3.710906731417713</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.698022654398673</v>
+        <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.760467530661733</v>
+        <v>-4.595087390468291</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.793479217820233</v>
+        <v>0.986968019271508</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3404011456684157</v>
+        <v>-0.3354483745148766</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.493781966997624</v>
+        <v>2.624090375063646</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205903</v>
+        <v>3.746042526205908</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.702589886390461</v>
+        <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.584993270869264</v>
+        <v>-4.419613130675822</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.8682361537290084</v>
+        <v>1.061724955180283</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.3404011456684157</v>
+        <v>-0.3354483745148766</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.498349198989412</v>
+        <v>2.628657607055434</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225448</v>
+        <v>3.765024323225453</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.678331915151668</v>
+        <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.695929523510513</v>
+        <v>-4.530549383317071</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.799603681433716</v>
+        <v>0.9930924828849907</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.3404011456684157</v>
+        <v>-0.3354483745148766</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.474091227750619</v>
+        <v>2.604399635816641</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111296</v>
+        <v>3.773210297111302</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.681463300371574</v>
+        <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.662265978038231</v>
+        <v>-4.496885837844789</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8162004848425344</v>
+        <v>1.009689286293809</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.3067376001961339</v>
+        <v>-0.3017848290425948</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.497420740253894</v>
+        <v>2.627729148319915</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264165</v>
+        <v>3.784343952264171</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.691635686803706</v>
+        <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.602413358834507</v>
+        <v>-4.437033218641066</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8503139189561559</v>
+        <v>1.043802720407431</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.3067376001961339</v>
+        <v>-0.3017848290425948</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.507593126686026</v>
+        <v>2.637901534752048</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742301</v>
+        <v>3.786949957742308</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.686581957377566</v>
+        <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.51616989580813</v>
+        <v>-4.350789755614688</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8797575747405673</v>
+        <v>1.073246376191842</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.3067376001961339</v>
+        <v>-0.3017848290425948</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.502539397259886</v>
+        <v>2.632847805325908</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316048</v>
+        <v>3.752027499316054</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.678357732822092</v>
+        <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.561476715207109</v>
+        <v>-4.396096575013668</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8534106224255009</v>
+        <v>1.046899423876776</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.3475477632053647</v>
+        <v>-0.3425949920518256</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.469829074898874</v>
+        <v>2.600137482964895</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803193</v>
+        <v>3.7535711658032</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.678909605855194</v>
+        <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.590509819909411</v>
+        <v>-4.425129679715969</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.842349253577682</v>
+        <v>1.035838055028957</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.3475477632053647</v>
+        <v>-0.3425949920518256</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.470380947931975</v>
+        <v>2.600689355997997</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333906008095</v>
+        <v>3.733390600809506</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.608182297746559</v>
+        <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.497699338458551</v>
+        <v>-4.332319198265109</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8087461380493917</v>
+        <v>1.002234939500666</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.2547372817545053</v>
+        <v>-0.2497845106009662</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.455339928693856</v>
+        <v>2.585648336759878</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560428</v>
+        <v>3.748285816560433</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.61005577367116</v>
+        <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.542088807787978</v>
+        <v>-4.376708667594537</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.7928638262422214</v>
+        <v>0.9863526276934964</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.299126751083933</v>
+        <v>-0.2941739799303939</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.4305797230208</v>
+        <v>2.560888131086822</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472746</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.605131482182883</v>
+        <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.429417589551728</v>
+        <v>-4.264037449358287</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8330080220484444</v>
+        <v>1.026496823499719</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.1864555328476828</v>
+        <v>-0.1815027616941437</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.493258162474274</v>
+        <v>2.623566570540295</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.74304760379854</v>
+        <v>3.743047603798545</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.61062277801355</v>
+        <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.317040588369055</v>
+        <v>-4.151660448175614</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.8834501183521808</v>
+        <v>1.076938919803456</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.1864555328476828</v>
+        <v>-0.1815027616941437</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.498749458304941</v>
+        <v>2.629057866370963</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498867</v>
+        <v>3.689597840498873</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.622119979782089</v>
+        <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.344820986270408</v>
+        <v>-4.179440846076966</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8838351609601789</v>
+        <v>1.077323962411454</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.2142359307490359</v>
+        <v>-0.2092831595954968</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.493578421332668</v>
+        <v>2.62388682939869</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705328</v>
+        <v>3.643069621705334</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.460475699782743</v>
+        <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.427822267295687</v>
+        <v>-4.262442127102245</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6889903685507206</v>
+        <v>0.8824791700019956</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2328068152762096</v>
+        <v>-0.2278540441226705</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.320791610617017</v>
+        <v>2.451100018683039</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729272</v>
+        <v>3.682716310729278</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.580625360501948</v>
+        <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.536436345739018</v>
+        <v>-4.371056205545576</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7656943978925939</v>
+        <v>0.9591831993438686</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2328068152762096</v>
+        <v>-0.2278540441226705</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.440941271336223</v>
+        <v>2.571249679402245</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190771</v>
+        <v>3.733012441190778</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.595138386604271</v>
+        <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.501027307490875</v>
+        <v>-4.335647167297433</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7943710392941739</v>
+        <v>0.9878598407454489</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2328068152762096</v>
+        <v>-0.2278540441226705</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.455454297438546</v>
+        <v>2.585762705504568</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913429</v>
+        <v>3.741174069913435</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.59255782794664</v>
+        <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.462643644932724</v>
+        <v>-4.297263504739282</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8071439456598031</v>
+        <v>1.000632747111078</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.1944231527180584</v>
+        <v>-0.1894703815645193</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.475903936315805</v>
+        <v>2.606212344381827</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532489</v>
+        <v>3.751147197532496</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.589286856791942</v>
+        <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.285527314897558</v>
+        <v>-4.120147174704116</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8747195065191713</v>
+        <v>1.068208307970446</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.1944231527180584</v>
+        <v>-0.1894703815645193</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.472632965161107</v>
+        <v>2.602941373227129</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793907</v>
+        <v>3.741328448793913</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.589970248553855</v>
+        <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.330619559731104</v>
+        <v>-4.165239419537662</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8573660003476662</v>
+        <v>1.050854801798941</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.2563191958874482</v>
+        <v>-0.2513664247339091</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.436178731021386</v>
+        <v>2.566487139087408</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.75072937701124</v>
+        <v>3.750729377011246</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.583757223860269</v>
+        <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.151244138492336</v>
+        <v>-3.985863998298894</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9229031441495876</v>
+        <v>1.116391945600863</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.09954243771672955</v>
+        <v>-0.09458966656319046</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.524031761230232</v>
+        <v>2.654340169296253</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982234</v>
+        <v>3.71699171898224</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.564564679191859</v>
+        <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.196258352012942</v>
+        <v>-4.0308782118195</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8857049140729352</v>
+        <v>1.07919371552421</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.1298913330313342</v>
+        <v>-0.1249385618777951</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.486629879373059</v>
+        <v>2.616938287439081</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509542</v>
+        <v>3.737026608509549</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.570256241530805</v>
+        <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.463262862285377</v>
+        <v>-4.297882722091935</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7845946723029069</v>
+        <v>0.9780834737541817</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.3242543710742827</v>
+        <v>-0.3193015999207436</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.375703618886235</v>
+        <v>2.506012026952257</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.70230945476082</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.569460163427306</v>
+        <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.564460643722549</v>
+        <v>-4.399080503529108</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7433194816245392</v>
+        <v>0.936808283075814</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3926631846196019</v>
+        <v>-0.3877104134660628</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.333862252655545</v>
+        <v>2.464170660721567</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815458</v>
+        <v>3.705571661815464</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.620583061980939</v>
+        <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.557949677108237</v>
+        <v>-4.392569536914795</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7970467668238974</v>
+        <v>0.9370126312758558</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3926631846196019</v>
+        <v>-0.3877104134660628</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.384985151209178</v>
+        <v>2.461770622275884</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378104</v>
+        <v>3.709510443378107</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.617107781189184</v>
+        <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.53891154940094</v>
+        <v>-4.373531409207498</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8011867371150612</v>
+        <v>0.9411526015670197</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4508467959507965</v>
+        <v>-0.4458940247972574</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.346599703618707</v>
+        <v>2.423385174685412</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131254</v>
+        <v>3.731064473131259</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.794689650127865</v>
+        <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.570038180551558</v>
+        <v>-4.404658040358116</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9663179535934945</v>
+        <v>1.106283818045453</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4508467959507965</v>
+        <v>-0.4458940247972574</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.524181572557387</v>
+        <v>2.600967043624093</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.72244736206787</v>
+        <v>3.722447362067875</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.795522979113998</v>
+        <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.583904941885476</v>
+        <v>-4.418524801692034</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9616045780460607</v>
+        <v>1.101570442498019</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4887047126846194</v>
+        <v>-0.4837519415310803</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.502300151503227</v>
+        <v>2.579085622569933</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789126</v>
+        <v>3.787425580789131</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.801531509510924</v>
+        <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.539100770345546</v>
+        <v>-4.373720630152104</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9855347770589586</v>
+        <v>1.125500641510917</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4887047126846194</v>
+        <v>-0.4837519415310803</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.508308681900153</v>
+        <v>2.585094152966859</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519913</v>
+        <v>3.781501250519918</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.880684157302946</v>
+        <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.391357800110543</v>
+        <v>-4.225977659917102</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.123784612944982</v>
+        <v>1.26375047739694</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.3208973554497362</v>
+        <v>-0.3159445842961972</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.688145744033105</v>
+        <v>2.76493121509981</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181175</v>
+        <v>3.80224592918118</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.883477778834427</v>
+        <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.493372482641765</v>
+        <v>-4.327992342448323</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.085772361463974</v>
+        <v>1.225738225915933</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.3208973554497362</v>
+        <v>-0.3159445842961972</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.690939365564586</v>
+        <v>2.767724836631291</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394735</v>
+        <v>3.80560898539474</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.884140127226086</v>
+        <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.48721977658898</v>
+        <v>-4.321839636395539</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.088895792276746</v>
+        <v>1.228861656728705</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.314744649396952</v>
+        <v>-0.3097918782434129</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.695293337587915</v>
+        <v>2.77207880865462</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890614</v>
+        <v>3.798239794890617</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.883220603966196</v>
+        <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.504029074739482</v>
+        <v>-4.338648934546041</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.081252549756656</v>
+        <v>1.221218414208614</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.3315539475474536</v>
+        <v>-0.3266011763939145</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.684288235437724</v>
+        <v>2.761073706504429</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798429</v>
+        <v>3.867362636798434</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.949556157763017</v>
+        <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.44173107596336</v>
+        <v>-4.276350935769918</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.172507303063925</v>
+        <v>1.312473167515884</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.3315539475474536</v>
+        <v>-0.3266011763939145</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.750623789234545</v>
+        <v>2.82740926030125</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992196</v>
+        <v>3.848729139992201</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.658137030152415</v>
+        <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.239940878298202</v>
+        <v>-4.07456073810476</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9618042545193868</v>
+        <v>1.101770118971345</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.1335357553782992</v>
+        <v>-0.1285829842247601</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.578015576925436</v>
+        <v>2.654801047992141</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852426</v>
+        <v>3.841444817852431</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.72842726247459</v>
+        <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.166562781209466</v>
+        <v>-4.001182641016024</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.061445725677056</v>
+        <v>1.201411590129015</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.06015765828956265</v>
+        <v>-0.05520488713602356</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.692332667500853</v>
+        <v>2.769118138567558</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.81906330031955</v>
+        <v>3.819063300319556</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.743054998590634</v>
+        <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.26430332583444</v>
+        <v>-4.098923185640999</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.03697724394311</v>
+        <v>1.176943108395069</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.07604693642254284</v>
+        <v>-0.07109416526900375</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.697426836737108</v>
+        <v>2.774212307803813</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489388</v>
+        <v>3.831819032489395</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.741590979415305</v>
+        <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.44064108595737</v>
+        <v>-4.275260945763928</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9649781207186101</v>
+        <v>1.104943985170569</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.2523846965454722</v>
+        <v>-0.2474319253919331</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.590160161488022</v>
+        <v>2.666945632554727</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397798</v>
+        <v>3.836411672397804</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.740082597455234</v>
+        <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.364219039525443</v>
+        <v>-4.198838899332001</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9940385573313095</v>
+        <v>1.134004421783268</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.2523846965454722</v>
+        <v>-0.2474319253919331</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.588651779527951</v>
+        <v>2.665437250594656</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316253</v>
+        <v>3.833513460316259</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.73994546489067</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.319845907886874</v>
+        <v>-4.154465767693432</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.011650677422173</v>
+        <v>1.151616541874132</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.2080115649069036</v>
+        <v>-0.2030587937533646</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.615138525946528</v>
+        <v>2.691923997013233</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105967</v>
+        <v>3.821562117105973</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.734339259029261</v>
+        <v>2.808153067403842</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.197011686999707</v>
+        <v>-4.031631546806265</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.055178159915631</v>
+        <v>1.195144024367589</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.2080115649069036</v>
+        <v>-0.2030587937533646</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.609532320085119</v>
+        <v>2.686317791151824</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190325</v>
+        <v>3.833011148190332</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.740721016057065</v>
+        <v>2.814534824431647</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.149355956438651</v>
+        <v>-3.983975816245209</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.080622209167857</v>
+        <v>1.220588073619816</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.160355834345848</v>
+        <v>-0.1554030631923089</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.644507515449556</v>
+        <v>2.721292986516262</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569618</v>
+        <v>3.822678210569624</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.74561338943179</v>
+        <v>2.819427197806371</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.048837797939896</v>
+        <v>-3.883457657746455</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.125721845942084</v>
+        <v>1.265687710394043</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.05983767584709343</v>
+        <v>-0.05488490469355434</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.709710783923534</v>
+        <v>2.786496254990239</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557293</v>
+        <v>3.828808877557299</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.732368061907662</v>
+        <v>2.806181870282244</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.109504388342286</v>
+        <v>-3.944124248148844</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.088209882257</v>
+        <v>1.228175746708959</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.1415359925656271</v>
+        <v>-0.136583221412088</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.647446466368286</v>
+        <v>2.724231937434991</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932769</v>
+        <v>3.816837033932774</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.73646576451829</v>
+        <v>2.810279572892872</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.064665986733887</v>
+        <v>-3.899285846540446</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.110242945510988</v>
+        <v>1.250208809962947</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.1369925596207576</v>
+        <v>-0.1320397884672185</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.654270228745836</v>
+        <v>2.731055699812541</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917053</v>
+        <v>3.817932354917058</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.740626704149368</v>
+        <v>2.81444051252395</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.165424622490885</v>
+        <v>-4.000044482297444</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.074100430839267</v>
+        <v>1.214066295291226</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.225818128347763</v>
+        <v>-0.220865357194224</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.605135827140711</v>
+        <v>2.681921298207416</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405962</v>
+        <v>3.826684745405967</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.746506306677206</v>
+        <v>2.820320115051787</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.121221785404985</v>
+        <v>-3.955841645211543</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.097661168201464</v>
+        <v>1.237627032653423</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.1816152912618626</v>
+        <v>-0.1766625201083235</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.637537131920088</v>
+        <v>2.714322602986794</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265647</v>
+        <v>3.838199629265652</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.744916307146453</v>
+        <v>2.818730115521035</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.158200813068428</v>
+        <v>-3.992820672874986</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.081279557605335</v>
+        <v>1.221245422057293</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.1446413894705321</v>
+        <v>-0.139688618316993</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.658131473464134</v>
+        <v>2.734916944530839</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284881</v>
+        <v>3.863895080284887</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.796164072329493</v>
+        <v>2.869977880704075</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.178258891933268</v>
+        <v>-4.012878751739827</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.124504091242438</v>
+        <v>1.264469955694397</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.1446413894705321</v>
+        <v>-0.139688618316993</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.709379238647174</v>
+        <v>2.786164709713879</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321024</v>
+        <v>3.865338681321029</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.794604776923746</v>
+        <v>2.868418585298328</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.138328218755378</v>
+        <v>-3.972948078561936</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.138917065107848</v>
+        <v>1.278882929559806</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.1047107162926417</v>
+        <v>-0.09975794513910263</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.731778347148161</v>
+        <v>2.808563818214866</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475141</v>
+        <v>3.864489842475146</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.789553005162016</v>
+        <v>2.863366813536598</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.08729612603285</v>
+        <v>-3.921915985839408</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.154278130435129</v>
+        <v>1.294243994887087</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.05367862357011377</v>
+        <v>-0.04872585241657468</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.757345831019948</v>
+        <v>2.834131302086653</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404857</v>
+        <v>3.842547360404862</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.806740409254721</v>
+        <v>2.880554217629303</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.022071944905645</v>
+        <v>-3.856691804712202</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.197555206978716</v>
+        <v>1.337521071430674</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.01154555755709186</v>
+        <v>0.01649832871063095</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.813667743788976</v>
+        <v>2.890453214855682</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.84006118688256</v>
+        <v>3.840061186882566</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.802701381554001</v>
+        <v>2.876515189928583</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.984644924834511</v>
+        <v>-3.819264784641069</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.208486987306449</v>
+        <v>1.348452851758408</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.01679709558627351</v>
+        <v>0.02174986673981261</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.812779638905766</v>
+        <v>2.889565109972471</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992665</v>
+        <v>3.84516980899267</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.803958173885241</v>
+        <v>2.877771982259823</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.00475658086922</v>
+        <v>-3.839376440675777</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.201699117223807</v>
+        <v>1.341664981675765</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.02782444058369271</v>
+        <v>0.0327772117372318</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.820652838235457</v>
+        <v>2.897438309302163</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636291</v>
+        <v>3.828661445636296</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.964515944906452</v>
+        <v>3.038329753281034</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.951011766442015</v>
+        <v>-3.785631626248572</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.383754814015899</v>
+        <v>1.523720678467858</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.03788775002415468</v>
+        <v>0.04284052117769377</v>
       </c>
       <c r="G1991" t="n">
-        <v>2.987248594920945</v>
+        <v>3.06403406598765</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957629</v>
+        <v>3.813222820957634</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.084628854124269</v>
+        <v>3.158442662498851</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.927220197835873</v>
+        <v>-3.76184005764243</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.513384350676173</v>
+        <v>1.653350215128132</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.06167931863029696</v>
+        <v>0.06663208978383606</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.121636445302448</v>
+        <v>3.198421916369153</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998755</v>
+        <v>3.81423072799876</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.076336830138128</v>
+        <v>3.15015063851271</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.901136113572065</v>
+        <v>-3.735755973378622</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.515525960395555</v>
+        <v>1.655491824847514</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.06167931863029696</v>
+        <v>0.06663208978383606</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.113344421316307</v>
+        <v>3.190129892383012</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896934</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.074530025721908</v>
+        <v>3.14834383409649</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.770843582642455</v>
+        <v>-3.605463442449012</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.565836168351179</v>
+        <v>1.705802032803138</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.2982149431580318</v>
+        <v>0.3031677143115709</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.253458991616727</v>
+        <v>3.330244462683432</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959859</v>
+        <v>3.796264143959863</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.092084431448699</v>
+        <v>3.165898239823281</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.761951121249172</v>
+        <v>-3.596570981055729</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.586947558635283</v>
+        <v>1.726913423087242</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.2982149431580318</v>
+        <v>0.3031677143115709</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.271013397343518</v>
+        <v>3.347798868410224</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945367</v>
+        <v>3.794424941945373</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.083939478853283</v>
+        <v>3.157753287227865</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.93042723821905</v>
+        <v>-3.765047098025607</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.511412159251916</v>
+        <v>1.651378023703875</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.270267107441451</v>
+        <v>0.2752198785949901</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.246099743318154</v>
+        <v>3.32288521438486</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782709</v>
+        <v>3.795574066782715</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.065209176041145</v>
+        <v>3.139022984415727</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.232627709357466</v>
+        <v>-3.067247569164024</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.771801667984411</v>
+        <v>1.91176753243637</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.1999190480710403</v>
+        <v>0.2048718192245794</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.18516060488377</v>
+        <v>3.261946075950475</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632639</v>
+        <v>3.784671345632645</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.05587319853805</v>
+        <v>3.129687006912631</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.209906605674314</v>
+        <v>-3.044526465480871</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.771554131954577</v>
+        <v>1.911519996406536</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.1999190480710403</v>
+        <v>0.2048718192245794</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.175824627380674</v>
+        <v>3.252610098447379</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777677</v>
+        <v>3.783205696777682</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.214779324389219</v>
+        <v>3.2885931327638</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.20818156238427</v>
+        <v>-3.042801422190827</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.931150275121763</v>
+        <v>2.071116139573722</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.201644091361084</v>
+        <v>0.2065968625146231</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.335765779205869</v>
+        <v>3.412551250272575</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644415</v>
+        <v>3.779933725644421</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.251857146882865</v>
+        <v>3.325670955257447</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.362962569162525</v>
+        <v>-3.197582428969082</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.906315694904108</v>
+        <v>2.046281559356067</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.1682764173066079</v>
+        <v>0.173229188460147</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.35282299726683</v>
+        <v>3.429608468333535</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799964</v>
+        <v>3.769443619799969</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.24853250287241</v>
+        <v>3.322346311246992</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.311527235777866</v>
+        <v>-3.146147095584423</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.923565184247517</v>
+        <v>2.063531048699476</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.2197117506912676</v>
+        <v>0.2246645218448067</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.380359553287171</v>
+        <v>3.457145024353876</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331119</v>
+        <v>3.766673496331124</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.258538656517152</v>
+        <v>3.332352464891734</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.284576011451378</v>
+        <v>-3.119195871257935</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.944351827622854</v>
+        <v>2.084317692074813</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.2345920967189867</v>
+        <v>0.2395448678725258</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.399293914548544</v>
+        <v>3.476079385615249</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784112</v>
+        <v>3.768052067784117</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.442641788662112</v>
+        <v>3.516455597036694</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.420529019507694</v>
+        <v>-3.255148879314251</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.074073756545287</v>
+        <v>2.214039620997246</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.2345920967189867</v>
+        <v>0.2395448678725258</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.583397046693504</v>
+        <v>3.660182517760209</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714425</v>
+        <v>3.74392550571443</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.434758483565105</v>
+        <v>3.508572291939687</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.442937137312566</v>
+        <v>-3.277556997119123</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.057227204326331</v>
+        <v>2.19719306877829</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.2345920967189867</v>
+        <v>0.2395448678725258</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.575513741596497</v>
+        <v>3.652299212663202</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155035</v>
+        <v>3.719118627155041</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.436812483114742</v>
+        <v>3.510626291489324</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.590942904791965</v>
+        <v>-3.425562764598522</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.000078896884209</v>
+        <v>2.140044761336168</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.1478650878554453</v>
+        <v>0.1528178590089844</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.525531535828009</v>
+        <v>3.602317006894715</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.72945228516198</v>
+        <v>3.729452285161986</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.493066200836589</v>
+        <v>3.566880009211171</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.600383830680495</v>
+        <v>-3.435003690487052</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.052556244250644</v>
+        <v>2.192522108702603</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.2702922053988367</v>
+        <v>0.2752449765523758</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.655241524075892</v>
+        <v>3.732026995142597</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321637</v>
+        <v>3.714941193321643</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.49595729538189</v>
+        <v>3.569771103756472</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.599097067140939</v>
+        <v>-3.433716926947496</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.055962044211768</v>
+        <v>2.195927908663727</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.2715789689383933</v>
+        <v>0.2765317400919324</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.658904676744926</v>
+        <v>3.735690147811632</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347706</v>
+        <v>3.727898186347711</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.494069108275665</v>
+        <v>3.567882916650247</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.60065412113023</v>
+        <v>-3.435273980936787</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.053451035509826</v>
+        <v>2.193416899961785</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.2715789689383933</v>
+        <v>0.2765317400919324</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.657016489638702</v>
+        <v>3.733801960705407</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.71065410488775</v>
+        <v>3.710654104887755</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.488889337878528</v>
+        <v>3.56270314625311</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.607926006653695</v>
+        <v>-3.442545866460252</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.045362510903303</v>
+        <v>2.185328375355262</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.2643070834149285</v>
+        <v>0.2692598545684676</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.647473587927485</v>
+        <v>3.72425905899419</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343068</v>
+        <v>3.712897612343073</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.48732334808868</v>
+        <v>3.561137156463262</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.606084987595444</v>
+        <v>-3.440704847402001</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.044532928736755</v>
+        <v>2.184498793188714</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.265575310086397</v>
+        <v>0.270528081239936</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.646668534140519</v>
+        <v>3.723454005207224</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647108</v>
+        <v>3.754911907647114</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.500396754954599</v>
+        <v>3.574210563329181</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.612993693095124</v>
+        <v>-3.447613552901681</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.054842853402802</v>
+        <v>2.194808717854761</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.265575310086397</v>
+        <v>0.270528081239936</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.659741941006437</v>
+        <v>3.736527412073142</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763532</v>
+        <v>3.749896851763536</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.500396754954599</v>
+        <v>3.574210563329181</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.815981132847049</v>
+        <v>-3.449175195716541</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.973647877502032</v>
+        <v>2.194184060728817</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.265575310086397</v>
+        <v>0.270528081239936</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.659741941006437</v>
+        <v>3.736527412073142</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.567820824833606</v>
+        <v>3.787316069270142</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.426250199803954</v>
+        <v>3.705409932039554</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.815981132847049</v>
+        <v>-3.449175195716541</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.973647877502032</v>
+        <v>2.194184060728817</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.265575310086397</v>
+        <v>0.270528081239936</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.419313996790322</v>
+        <v>3.698473729025922</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240702.xlsx
+++ b/tame_output/ON/bt/strategyON_20240702.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>61.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>55.0%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.2%</t>
+          <t>-72.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.5%</t>
+          <t>108.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.2%</t>
+          <t>94.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.9%</t>
+          <t>-49.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-67.5%</t>
+          <t>-67.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>452.2%</t>
+          <t>452.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-12.1%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-506.5%</t>
+          <t>-506.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-36.7%</t>
+          <t>-39.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-29.0%</t>
+          <t>-31.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-156.8%</t>
+          <t>-143.8%</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-4.8%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.0%</t>
+          <t>-31.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-12.1%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-30.5%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-171.8%</t>
+          <t>-178.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-196.9%</t>
+          <t>-196.5%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,12 +1456,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-26.4%</t>
+          <t>-28.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-76.2%</t>
+          <t>-59.0%</t>
         </is>
       </c>
     </row>
@@ -43681,7 +43681,7 @@
         <v>45294</v>
       </c>
       <c r="B1832" t="n">
-        <v>3.301413393085799</v>
+        <v>3.301413393085798</v>
       </c>
       <c r="C1832" t="n">
         <v>3.130069279090508</v>
@@ -43704,7 +43704,7 @@
         <v>45295</v>
       </c>
       <c r="B1833" t="n">
-        <v>3.311607601705545</v>
+        <v>3.311607601705544</v>
       </c>
       <c r="C1833" t="n">
         <v>3.12694133299222</v>
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.311888301355689</v>
+        <v>3.311888301355688</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279813</v>
+        <v>3.385382209279812</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511403</v>
+        <v>3.367379938511402</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998559</v>
+        <v>3.367370539998558</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082123</v>
+        <v>3.299560092082122</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757921</v>
+        <v>3.29349053375792</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760739</v>
+        <v>3.293766719760738</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296836</v>
+        <v>3.299918119296835</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201487</v>
+        <v>3.295507330201486</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153006</v>
+        <v>3.258791981153005</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537426</v>
+        <v>3.271168579537425</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382192</v>
+        <v>3.272760131382191</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074623</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911641</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213498</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416047</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.23598197738233</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347056</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130018</v>
+        <v>3.287377576130017</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207813</v>
+        <v>3.305316798207812</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309425</v>
+        <v>3.311086391309424</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970906</v>
+        <v>3.304715716970905</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191738</v>
+        <v>3.302618194191737</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.30502326510864</v>
+        <v>3.305023265108639</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097822</v>
+        <v>3.341378723097821</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094117</v>
+        <v>3.374439043094116</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199287</v>
+        <v>3.405960511199286</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969594</v>
+        <v>3.424633354969593</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923087</v>
+        <v>3.419979433923086</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.45810009129775</v>
+        <v>3.458100091297749</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317619</v>
+        <v>3.447750501317618</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737172</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341315</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539466</v>
+        <v>3.501052558539465</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937501</v>
+        <v>3.4924487119375</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141704</v>
+        <v>3.502790399141703</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729893</v>
+        <v>3.496851904729892</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440636</v>
+        <v>3.499971739440635</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764398</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390587</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297401</v>
+        <v>3.4921016412974</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322546</v>
+        <v>3.573674025322545</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158924</v>
+        <v>3.600038265158923</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940722</v>
+        <v>3.691571733940721</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770583</v>
+        <v>3.676841549770582</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615287</v>
+        <v>3.685161381615286</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646221</v>
+        <v>3.71093553364622</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611572</v>
+        <v>3.768951674611571</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955332</v>
+        <v>3.728577929955331</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436234</v>
+        <v>3.766317079436233</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311954</v>
+        <v>3.784684521311953</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.80082935409725</v>
+        <v>3.800829354097249</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017778</v>
+        <v>3.789311112017777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388735</v>
+        <v>3.839374447388733</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626481</v>
+        <v>3.856161751626479</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291817</v>
+        <v>3.787330429291815</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785793</v>
+        <v>3.801637122785792</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390433</v>
+        <v>3.763182248390431</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105957</v>
+        <v>3.784718794105955</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960992</v>
+        <v>3.753882571960991</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607651</v>
+        <v>3.692931855607649</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.77042258398791</v>
+        <v>3.770422583987908</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710818</v>
+        <v>3.760333686710816</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409211</v>
+        <v>3.723566229409209</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.32906649429528</v>
+        <v>-7.274530536164558</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.02694038381158936</v>
+        <v>0.04875476706387838</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.451242542178349</v>
+        <v>-1.396706584047627</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.08817788053644</v>
+        <v>2.120899455414873</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098115</v>
+        <v>3.729969716098113</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.28551808752459</v>
+        <v>-7.230982129393868</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.03739913442477238</v>
+        <v>0.0592135176770614</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.451242542178349</v>
+        <v>-1.396706584047627</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.081217268441347</v>
+        <v>2.11393884331978</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493426</v>
+        <v>3.782922533493424</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.043369694070732</v>
+        <v>-6.98883373594001</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1487208461874587</v>
+        <v>0.1705352294397477</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.451242542178349</v>
+        <v>-1.396706584047627</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.09567962282249</v>
+        <v>2.128401197700923</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722822</v>
+        <v>3.82855148672282</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.93511055694821</v>
+        <v>-6.880574598817488</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1865566214956624</v>
+        <v>0.2083710047479514</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.451242542178349</v>
+        <v>-1.396706584047627</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.090211743281685</v>
+        <v>2.122933318160118</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792051</v>
+        <v>3.828052928792049</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.811819422131079</v>
+        <v>-6.757283464000357</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.233371169433092</v>
+        <v>0.2551855526853806</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.327951407361218</v>
+        <v>-1.273415449230496</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.16168451818254</v>
+        <v>2.194406093060973</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919913</v>
+        <v>3.812453678919911</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.790670223227636</v>
+        <v>-6.736134265096914</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2495318272317943</v>
+        <v>0.2713462104840829</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.306802208457775</v>
+        <v>-1.252266250327053</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.182075015761932</v>
+        <v>2.214796590640365</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318099</v>
+        <v>3.748328408318097</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.546904781244192</v>
+        <v>-6.49236882311347</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3428187123722228</v>
+        <v>0.3646330956245114</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.306802208457775</v>
+        <v>-1.252266250327053</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.177855724108982</v>
+        <v>2.210577298987415</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057532</v>
+        <v>3.82431123305753</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.445141960966897</v>
+        <v>-6.390606002836175</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3856481544031567</v>
+        <v>0.4074625376554453</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.293583140065346</v>
+        <v>-1.239047181934624</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.187911479064455</v>
+        <v>2.220633053942889</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279192</v>
+        <v>3.82635497427919</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.195291567017822</v>
+        <v>-6.1407556088871</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4783303869664888</v>
+        <v>0.5001447702187773</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.293583140065346</v>
+        <v>-1.239047181934624</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.180653554048158</v>
+        <v>2.21337512892659</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011505</v>
+        <v>3.835957987011503</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.01939947455039</v>
+        <v>-5.964863516419667</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5522863474741104</v>
+        <v>0.5741007307263994</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.293583140065346</v>
+        <v>-1.239047181934624</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.184252677568806</v>
+        <v>2.21697425244724</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392994</v>
+        <v>3.780933911392992</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.847953011527927</v>
+        <v>-5.793417053397204</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6341924387376494</v>
+        <v>0.6560068219899384</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.122136677042883</v>
+        <v>-1.067600718912161</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.300448061436838</v>
+        <v>2.333169636315271</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632789</v>
+        <v>3.773765222632787</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.773663445789587</v>
+        <v>-5.719127487658865</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.662928742649282</v>
+        <v>0.684743125901571</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.047847111304544</v>
+        <v>-0.9933111531738217</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.344042278496139</v>
+        <v>2.376763853374571</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883081</v>
+        <v>3.76461787988308</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.710027703555653</v>
+        <v>-5.65549174542493</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6930778405971729</v>
+        <v>0.7148922238494624</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.984211369070609</v>
+        <v>-0.9296754109398871</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.386918524890817</v>
+        <v>2.41964009976925</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074792</v>
+        <v>3.79881477107479</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.598600944229733</v>
+        <v>-5.54406498609901</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.718842803111337</v>
+        <v>0.740657186363626</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.984211369070609</v>
+        <v>-0.9296754109398871</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.368112783674612</v>
+        <v>2.400834358553045</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242303</v>
+        <v>3.797694884242302</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.358170447424873</v>
+        <v>-5.30363448929415</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8167580784581583</v>
+        <v>0.8385724617104473</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.7437808722657487</v>
+        <v>-0.6892449141350269</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.514114158382406</v>
+        <v>2.546835733260839</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367694</v>
+        <v>3.821593509367692</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.285927879253678</v>
+        <v>-5.231391921122955</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8495844195614564</v>
+        <v>0.8713988028137454</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.7437808722657487</v>
+        <v>-0.6892449141350269</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.518043472217226</v>
+        <v>2.550765047095659</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879975</v>
+        <v>3.822326997879973</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.23292955697229</v>
+        <v>-5.178393598841567</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8714623323913515</v>
+        <v>0.8932767156436405</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.6884446132638099</v>
+        <v>-0.633908655133088</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.551923811535729</v>
+        <v>2.584645386414162</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502347</v>
+        <v>3.848616626502345</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.124124671492563</v>
+        <v>-5.06958871336184</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.911982357803236</v>
+        <v>0.933796741055525</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.6884446132638099</v>
+        <v>-0.633908655133088</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.548921882755723</v>
+        <v>2.581643457634156</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675948</v>
+        <v>3.818668951675947</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.904103873455552</v>
+        <v>-4.84956791532483</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.001569714028654</v>
+        <v>1.023384097280943</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.5472247681958297</v>
+        <v>-0.4926888100651078</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.635232826807125</v>
+        <v>2.667954401685558</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539959</v>
+        <v>3.843274527539958</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.771236184392275</v>
+        <v>-4.716700226261552</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.070610972455789</v>
+        <v>1.092425355708078</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.5472247681958297</v>
+        <v>-0.4926888100651078</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.651127009608948</v>
+        <v>2.683848584487381</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496268</v>
+        <v>3.845047386496266</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.651063101027776</v>
+        <v>-4.596527142897053</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.11982605024189</v>
+        <v>1.141640433494179</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4270516848313307</v>
+        <v>-0.3725157267006088</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.72437670406795</v>
+        <v>2.757098278946382</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577005</v>
+        <v>3.791273551577003</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.506390955928039</v>
+        <v>-4.451854997797316</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.187783010843225</v>
+        <v>1.209597394095514</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.2823795397315933</v>
+        <v>-0.2278435816008714</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.821268093689232</v>
+        <v>2.853989668567665</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.73583922294211</v>
+        <v>3.735839222942108</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.566265783285731</v>
+        <v>-4.511729825155008</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.149870571301574</v>
+        <v>1.171684954553863</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.3422543670892854</v>
+        <v>-0.2877184089585635</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.771380688676042</v>
+        <v>2.804102263554475</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674522</v>
+        <v>3.76264747767452</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.479466285506723</v>
+        <v>-4.424930327376</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.206990863735743</v>
+        <v>1.228805246988032</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.3422543670892854</v>
+        <v>-0.2877184089585635</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.793781181998608</v>
+        <v>2.826502756877042</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430701</v>
+        <v>3.729146398430699</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.481935991968529</v>
+        <v>-4.427400033837806</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.206075382524433</v>
+        <v>1.227889765776722</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3447240735510916</v>
+        <v>-0.2901881154203697</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.792371759494937</v>
+        <v>2.82509333437337</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.74322019600361</v>
+        <v>3.743220196003608</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.550306178292539</v>
+        <v>-4.495770220161816</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.189734230469531</v>
+        <v>1.21154861372182</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3354483745148766</v>
+        <v>-0.2809124163841548</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.808944101391368</v>
+        <v>2.841665676269801</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508378</v>
+        <v>3.714179139508376</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.564094231139586</v>
+        <v>-4.509558273008863</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.174655717962603</v>
+        <v>1.196470101214892</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3354483745148766</v>
+        <v>-0.2809124163841548</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.799380810023259</v>
+        <v>2.832102384901692</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417713</v>
+        <v>3.710906731417711</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.595087390468291</v>
+        <v>-4.540551432337568</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.986968019271508</v>
+        <v>1.008782402523797</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3354483745148766</v>
+        <v>-0.2809124163841548</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.624090375063646</v>
+        <v>2.656811949942079</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205908</v>
+        <v>3.746042526205906</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.419613130675822</v>
+        <v>-4.365077172545099</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.061724955180283</v>
+        <v>1.083539338432572</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.3354483745148766</v>
+        <v>-0.2809124163841548</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.628657607055434</v>
+        <v>2.661379181933867</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225453</v>
+        <v>3.765024323225451</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.530549383317071</v>
+        <v>-4.476013425186348</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9930924828849907</v>
+        <v>1.01490686613728</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.3354483745148766</v>
+        <v>-0.2809124163841548</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.604399635816641</v>
+        <v>2.637121210695074</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111302</v>
+        <v>3.7732102971113</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.496885837844789</v>
+        <v>-4.442349879714066</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.009689286293809</v>
+        <v>1.031503669546098</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.3017848290425948</v>
+        <v>-0.2472488709118729</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.627729148319915</v>
+        <v>2.660450723198349</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264171</v>
+        <v>3.78434395226417</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.437033218641066</v>
+        <v>-4.382497260510343</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.043802720407431</v>
+        <v>1.06561710365972</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.3017848290425948</v>
+        <v>-0.2472488709118729</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.637901534752048</v>
+        <v>2.670623109630481</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742308</v>
+        <v>3.786949957742306</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.350789755614688</v>
+        <v>-4.296253797483965</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.073246376191842</v>
+        <v>1.095060759444131</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.3017848290425948</v>
+        <v>-0.2472488709118729</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.632847805325908</v>
+        <v>2.665569380204341</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316054</v>
+        <v>3.752027499316053</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.396096575013668</v>
+        <v>-4.341560616882945</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.046899423876776</v>
+        <v>1.068713807129065</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.3425949920518256</v>
+        <v>-0.2880590339211037</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.600137482964895</v>
+        <v>2.632859057843328</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.7535711658032</v>
+        <v>3.753571165803198</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.425129679715969</v>
+        <v>-4.370593721585246</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.035838055028957</v>
+        <v>1.057652438281246</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.3425949920518256</v>
+        <v>-0.2880590339211037</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.600689355997997</v>
+        <v>2.63341093087643</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809506</v>
+        <v>3.733390600809504</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.332319198265109</v>
+        <v>-4.277783240134386</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.002234939500666</v>
+        <v>1.024049322752956</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.2497845106009662</v>
+        <v>-0.1952485524702444</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.585648336759878</v>
+        <v>2.618369911638311</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560433</v>
+        <v>3.748285816560431</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.376708667594537</v>
+        <v>-4.322172709463814</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9863526276934964</v>
+        <v>1.008167010945785</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.2941739799303939</v>
+        <v>-0.239638021799672</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.560888131086822</v>
+        <v>2.593609705965255</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472746</v>
+        <v>3.721077195472744</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.264037449358287</v>
+        <v>-4.209501491227564</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.026496823499719</v>
+        <v>1.048311206752008</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.1815027616941437</v>
+        <v>-0.1269668035634218</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.623566570540295</v>
+        <v>2.656288145418729</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798545</v>
+        <v>3.743047603798543</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.151660448175614</v>
+        <v>-4.097124490044891</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.076938919803456</v>
+        <v>1.098753303055745</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.1815027616941437</v>
+        <v>-0.1269668035634218</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.629057866370963</v>
+        <v>2.661779441249396</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498873</v>
+        <v>3.689597840498871</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.179440846076966</v>
+        <v>-4.124904887946244</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.077323962411454</v>
+        <v>1.099138345663743</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.2092831595954968</v>
+        <v>-0.1547472014647749</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.62388682939869</v>
+        <v>2.656608404277123</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705334</v>
+        <v>3.643069621705332</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.262442127102245</v>
+        <v>-4.207906168971522</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8824791700019956</v>
+        <v>0.9042935532542846</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2278540441226705</v>
+        <v>-0.1733180859919486</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.451100018683039</v>
+        <v>2.483821593561472</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729278</v>
+        <v>3.682716310729277</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.371056205545576</v>
+        <v>-4.316520247414854</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9591831993438686</v>
+        <v>0.9809975825961579</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2278540441226705</v>
+        <v>-0.1733180859919486</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.571249679402245</v>
+        <v>2.603971254280677</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190778</v>
+        <v>3.733012441190776</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.335647167297433</v>
+        <v>-4.281111209166711</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9878598407454489</v>
+        <v>1.009674223997738</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2278540441226705</v>
+        <v>-0.1733180859919486</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.585762705504568</v>
+        <v>2.618484280383</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913435</v>
+        <v>3.741174069913433</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.297263504739282</v>
+        <v>-4.24272754660856</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.000632747111078</v>
+        <v>1.022447130363367</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.1894703815645193</v>
+        <v>-0.1349344234337975</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.606212344381827</v>
+        <v>2.63893391926026</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532496</v>
+        <v>3.751147197532494</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.120147174704116</v>
+        <v>-4.065611216573394</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.068208307970446</v>
+        <v>1.090022691222735</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.1894703815645193</v>
+        <v>-0.1349344234337975</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.602941373227129</v>
+        <v>2.635662948105562</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793913</v>
+        <v>3.741328448793912</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.165239419537662</v>
+        <v>-4.110703461406939</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.050854801798941</v>
+        <v>1.07266918505123</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.2513664247339091</v>
+        <v>-0.1968304666031873</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.566487139087408</v>
+        <v>2.599208713965841</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011246</v>
+        <v>3.750729377011244</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.985863998298894</v>
+        <v>-3.931328040168172</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.116391945600863</v>
+        <v>1.138206328853152</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.09458966656319046</v>
+        <v>-0.04005370843246858</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.654340169296253</v>
+        <v>2.687061744174687</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898224</v>
+        <v>3.716991718982238</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.0308782118195</v>
+        <v>-3.976342253688778</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.07919371552421</v>
+        <v>1.101008098776499</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.1249385618777951</v>
+        <v>-0.07040260374707319</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.616938287439081</v>
+        <v>2.649659862317514</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509549</v>
+        <v>3.737026608509547</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.297882722091935</v>
+        <v>-4.243346763961213</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9780834737541817</v>
+        <v>0.9998978570064705</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.3193015999207436</v>
+        <v>-0.2647656417900218</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.506012026952257</v>
+        <v>2.53873360183069</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476082</v>
+        <v>3.702309454760818</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.399080503529108</v>
+        <v>-4.344544545398386</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.936808283075814</v>
+        <v>0.9586226663281028</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3877104134660628</v>
+        <v>-0.333174455335341</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.464170660721567</v>
+        <v>2.4968922356</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815464</v>
+        <v>3.705571661815462</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.392569536914795</v>
+        <v>-4.338033578784073</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9370126312758558</v>
+        <v>0.9588270145281446</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3877104134660628</v>
+        <v>-0.333174455335341</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.461770622275884</v>
+        <v>2.494492197154317</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378107</v>
+        <v>3.709510443378106</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.373531409207498</v>
+        <v>-4.318995451076776</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9411526015670197</v>
+        <v>0.9629669848193085</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4458940247972574</v>
+        <v>-0.3913580666665355</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.423385174685412</v>
+        <v>2.456106749563845</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131259</v>
+        <v>3.731064473131257</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.404658040358116</v>
+        <v>-4.350122082227394</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.106283818045453</v>
+        <v>1.128098201297742</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4458940247972574</v>
+        <v>-0.3913580666665355</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.600967043624093</v>
+        <v>2.633688618502526</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067875</v>
+        <v>3.722447362067873</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.418524801692034</v>
+        <v>-4.363988843561312</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.101570442498019</v>
+        <v>1.123384825750308</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4837519415310803</v>
+        <v>-0.4292159834003584</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.579085622569933</v>
+        <v>2.611807197448365</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789131</v>
+        <v>3.787425580789129</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.373720630152104</v>
+        <v>-4.319184672021382</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.125500641510917</v>
+        <v>1.147315024763206</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4837519415310803</v>
+        <v>-0.4292159834003584</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.585094152966859</v>
+        <v>2.617815727845291</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519918</v>
+        <v>3.781501250519916</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.225977659917102</v>
+        <v>-4.17144170178638</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.26375047739694</v>
+        <v>1.285564860649229</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.3159445842961972</v>
+        <v>-0.2614086261654753</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.76493121509981</v>
+        <v>2.797652789978243</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918118</v>
+        <v>3.802245929181178</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.327992342448323</v>
+        <v>-4.273456384317601</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.225738225915933</v>
+        <v>1.247552609168221</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.3159445842961972</v>
+        <v>-0.2614086261654753</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.767724836631291</v>
+        <v>2.800446411509724</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560898539474</v>
+        <v>3.805608985394739</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.321839636395539</v>
+        <v>-4.267303678264817</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.228861656728705</v>
+        <v>1.250676039980994</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.3097918782434129</v>
+        <v>-0.255255920112691</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.77207880865462</v>
+        <v>2.804800383533053</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890617</v>
+        <v>3.798239794890615</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.338648934546041</v>
+        <v>-4.284112976415319</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.221218414208614</v>
+        <v>1.243032797460903</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.3266011763939145</v>
+        <v>-0.2720652182631926</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.761073706504429</v>
+        <v>2.793795281382862</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798434</v>
+        <v>3.867362636798433</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.276350935769918</v>
+        <v>-4.221814977639196</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.312473167515884</v>
+        <v>1.334287550768173</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.3266011763939145</v>
+        <v>-0.2720652182631926</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.82740926030125</v>
+        <v>2.860130835179683</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992201</v>
+        <v>3.8487291399922</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.07456073810476</v>
+        <v>-4.020024779974039</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.101770118971345</v>
+        <v>1.123584502223634</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.1285829842247601</v>
+        <v>-0.07404702609403824</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.654801047992141</v>
+        <v>2.687522622870574</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852431</v>
+        <v>3.841444817852429</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.001182641016024</v>
+        <v>-3.946646682885302</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.201411590129015</v>
+        <v>1.223225973381304</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.05520488713602356</v>
+        <v>-0.0006689290053016883</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.769118138567558</v>
+        <v>2.801839713445991</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319556</v>
+        <v>3.819063300319553</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.098923185640999</v>
+        <v>-4.044387227510276</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.176943108395069</v>
+        <v>1.198757491647358</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.07109416526900375</v>
+        <v>-0.01655820713828188</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.774212307803813</v>
+        <v>2.806933882682247</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489395</v>
+        <v>3.831819032489392</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.275260945763928</v>
+        <v>-4.220724987633205</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.104943985170569</v>
+        <v>1.126758368422858</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.2474319253919331</v>
+        <v>-0.1928959672612113</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.666945632554727</v>
+        <v>2.699667207433161</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397804</v>
+        <v>3.836411672397801</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.198838899332001</v>
+        <v>-4.144302941201278</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.134004421783268</v>
+        <v>1.155818805035557</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.2474319253919331</v>
+        <v>-0.1928959672612113</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.665437250594656</v>
+        <v>2.698158825473089</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316259</v>
+        <v>3.833513460316256</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.154465767693432</v>
+        <v>-4.09992980956271</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.151616541874132</v>
+        <v>1.173430925126421</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.2030587937533646</v>
+        <v>-0.1485228356226427</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.691923997013233</v>
+        <v>2.724645571891667</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105973</v>
+        <v>3.82156211710597</v>
       </c>
       <c r="C1977" t="n">
         <v>2.808153067403842</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.031631546806265</v>
+        <v>-3.977095588675542</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.195144024367589</v>
+        <v>1.216958407619878</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.2030587937533646</v>
+        <v>-0.1485228356226427</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.686317791151824</v>
+        <v>2.719039366030257</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190332</v>
+        <v>3.833011148190328</v>
       </c>
       <c r="C1978" t="n">
         <v>2.814534824431647</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.983975816245209</v>
+        <v>-3.929439858114486</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.220588073619816</v>
+        <v>1.242402456872105</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.1554030631923089</v>
+        <v>-0.100867105061587</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.721292986516262</v>
+        <v>2.754014561394694</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569624</v>
+        <v>3.82267821056962</v>
       </c>
       <c r="C1979" t="n">
         <v>2.819427197806371</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.883457657746455</v>
+        <v>-3.828921699615732</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.265687710394043</v>
+        <v>1.287502093646332</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.05488490469355434</v>
+        <v>-0.0003489465628324639</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.786496254990239</v>
+        <v>2.819217829868672</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557299</v>
+        <v>3.828808877557296</v>
       </c>
       <c r="C1980" t="n">
         <v>2.806181870282244</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.944124248148844</v>
+        <v>-3.889588290018121</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.228175746708959</v>
+        <v>1.249990129961248</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.136583221412088</v>
+        <v>-0.08204726328136613</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.724231937434991</v>
+        <v>2.756953512313424</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932774</v>
+        <v>3.816837033932771</v>
       </c>
       <c r="C1981" t="n">
         <v>2.810279572892872</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.899285846540446</v>
+        <v>-3.844749888409723</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.250208809962947</v>
+        <v>1.272023193215236</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.1320397884672185</v>
+        <v>-0.07750383033649666</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.731055699812541</v>
+        <v>2.763777274690975</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917058</v>
+        <v>3.817932354917055</v>
       </c>
       <c r="C1982" t="n">
         <v>2.81444051252395</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.000044482297444</v>
+        <v>-3.945508524166721</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.214066295291226</v>
+        <v>1.235880678543514</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.220865357194224</v>
+        <v>-0.1663293990635021</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.681921298207416</v>
+        <v>2.714642873085849</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405967</v>
+        <v>3.826684745405964</v>
       </c>
       <c r="C1983" t="n">
         <v>2.820320115051787</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.955841645211543</v>
+        <v>-3.901305687080821</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.237627032653423</v>
+        <v>1.259441415905712</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.1766625201083235</v>
+        <v>-0.1221265619776016</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.714322602986794</v>
+        <v>2.747044177865227</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265652</v>
+        <v>3.838199629265649</v>
       </c>
       <c r="C1984" t="n">
         <v>2.818730115521035</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.992820672874986</v>
+        <v>-3.938284714744264</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.221245422057293</v>
+        <v>1.243059805309582</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.139688618316993</v>
+        <v>-0.0851526601862711</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.734916944530839</v>
+        <v>2.767638519409273</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284887</v>
+        <v>3.863895080284883</v>
       </c>
       <c r="C1985" t="n">
         <v>2.869977880704075</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.012878751739827</v>
+        <v>-3.958342793609104</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.264469955694397</v>
+        <v>1.286284338946686</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.139688618316993</v>
+        <v>-0.0851526601862711</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.786164709713879</v>
+        <v>2.818886284592312</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321029</v>
+        <v>3.865338681321026</v>
       </c>
       <c r="C1986" t="n">
         <v>2.868418585298328</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.972948078561936</v>
+        <v>-3.918412120431214</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.278882929559806</v>
+        <v>1.300697312812095</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.09975794513910263</v>
+        <v>-0.04522198700838076</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.808563818214866</v>
+        <v>2.841285393093299</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475146</v>
+        <v>3.864489842475143</v>
       </c>
       <c r="C1987" t="n">
         <v>2.863366813536598</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.921915985839408</v>
+        <v>-3.867380027708686</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.294243994887087</v>
+        <v>1.316058378139376</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.04872585241657468</v>
+        <v>0.005810105714147196</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.834131302086653</v>
+        <v>2.866852876965087</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404862</v>
+        <v>3.842547360404859</v>
       </c>
       <c r="C1988" t="n">
         <v>2.880554217629303</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.856691804712202</v>
+        <v>-3.80215584658148</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.337521071430674</v>
+        <v>1.359335454682963</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.01649832871063095</v>
+        <v>0.07103428684135282</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.890453214855682</v>
+        <v>2.923174789734114</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882566</v>
+        <v>3.840061186882562</v>
       </c>
       <c r="C1989" t="n">
         <v>2.876515189928583</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.819264784641069</v>
+        <v>-3.764728826510347</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.348452851758408</v>
+        <v>1.370267235010697</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.02174986673981261</v>
+        <v>0.07628582487053448</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.889565109972471</v>
+        <v>2.922286684850904</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84516980899267</v>
+        <v>3.845169808992667</v>
       </c>
       <c r="C1990" t="n">
         <v>2.877771982259823</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.839376440675777</v>
+        <v>-3.784840482545055</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.341664981675765</v>
+        <v>1.363479364928054</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.0327772117372318</v>
+        <v>0.08731316986795368</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.897438309302163</v>
+        <v>2.930159884180596</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636296</v>
+        <v>3.828661445636293</v>
       </c>
       <c r="C1991" t="n">
         <v>3.038329753281034</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.785631626248572</v>
+        <v>-3.73109566811785</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.523720678467858</v>
+        <v>1.545535061720147</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.04284052117769377</v>
+        <v>0.09737647930841564</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.06403406598765</v>
+        <v>3.096755640866084</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957634</v>
+        <v>3.81322282095763</v>
       </c>
       <c r="C1992" t="n">
         <v>3.158442662498851</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.76184005764243</v>
+        <v>-3.707304099511708</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.653350215128132</v>
+        <v>1.675164598380421</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.06663208978383606</v>
+        <v>0.1211680479145579</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.198421916369153</v>
+        <v>3.231143491247586</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.81423072799876</v>
+        <v>3.814230727998757</v>
       </c>
       <c r="C1993" t="n">
         <v>3.15015063851271</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.735755973378622</v>
+        <v>-3.6812200152479</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.655491824847514</v>
+        <v>1.677306208099803</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.06663208978383606</v>
+        <v>0.1211680479145579</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.190129892383012</v>
+        <v>3.222851467261445</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896934</v>
+        <v>3.80339781889693</v>
       </c>
       <c r="C1994" t="n">
         <v>3.14834383409649</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.605463442449012</v>
+        <v>-3.55092748431829</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.705802032803138</v>
+        <v>1.727616416055426</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.3031677143115709</v>
+        <v>0.3577036724422927</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.330244462683432</v>
+        <v>3.362966037561866</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959863</v>
+        <v>3.79626414395986</v>
       </c>
       <c r="C1995" t="n">
         <v>3.165898239823281</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.596570981055729</v>
+        <v>-3.542035022925007</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.726913423087242</v>
+        <v>1.748727806339531</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.3031677143115709</v>
+        <v>0.3577036724422927</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.347798868410224</v>
+        <v>3.380520443288657</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945373</v>
+        <v>3.794424941945369</v>
       </c>
       <c r="C1996" t="n">
         <v>3.157753287227865</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.765047098025607</v>
+        <v>-3.710511139894885</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.651378023703875</v>
+        <v>1.673192406956164</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.2752198785949901</v>
+        <v>0.329755836725712</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.32288521438486</v>
+        <v>3.355606789263292</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782715</v>
+        <v>3.795574066782711</v>
       </c>
       <c r="C1997" t="n">
         <v>3.139022984415727</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.067247569164024</v>
+        <v>-3.012711611033302</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.91176753243637</v>
+        <v>1.933581915688659</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.2048718192245794</v>
+        <v>0.2594077773553012</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.261946075950475</v>
+        <v>3.294667650828908</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632645</v>
+        <v>3.784671345632641</v>
       </c>
       <c r="C1998" t="n">
         <v>3.129687006912631</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.044526465480871</v>
+        <v>-2.989990507350149</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.911519996406536</v>
+        <v>1.933334379658825</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.2048718192245794</v>
+        <v>0.2594077773553012</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.252610098447379</v>
+        <v>3.285331673325813</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777682</v>
+        <v>3.783205696777679</v>
       </c>
       <c r="C1999" t="n">
         <v>3.2885931327638</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.042801422190827</v>
+        <v>-2.988265464060105</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.071116139573722</v>
+        <v>2.092930522826011</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.2065968625146231</v>
+        <v>0.261132820645345</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.412551250272575</v>
+        <v>3.445272825151008</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644421</v>
+        <v>3.779933725644417</v>
       </c>
       <c r="C2000" t="n">
         <v>3.325670955257447</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.197582428969082</v>
+        <v>-3.14304647083836</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.046281559356067</v>
+        <v>2.068095942608355</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.173229188460147</v>
+        <v>0.2277651465908689</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.429608468333535</v>
+        <v>3.462330043211969</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799969</v>
+        <v>3.769443619799965</v>
       </c>
       <c r="C2001" t="n">
         <v>3.322346311246992</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.146147095584423</v>
+        <v>-3.091611137453701</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.063531048699476</v>
+        <v>2.085345431951764</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.2246645218448067</v>
+        <v>0.2792004799755285</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.457145024353876</v>
+        <v>3.48986659923231</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331124</v>
+        <v>3.76667349633112</v>
       </c>
       <c r="C2002" t="n">
         <v>3.332352464891734</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.119195871257935</v>
+        <v>-3.064659913127213</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.084317692074813</v>
+        <v>2.106132075327102</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.2395448678725258</v>
+        <v>0.2940808260032477</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.476079385615249</v>
+        <v>3.508800960493683</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784117</v>
+        <v>3.768052067784113</v>
       </c>
       <c r="C2003" t="n">
         <v>3.516455597036694</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.255148879314251</v>
+        <v>-3.200612921183529</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.214039620997246</v>
+        <v>2.235854004249535</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.2395448678725258</v>
+        <v>0.2940808260032477</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.660182517760209</v>
+        <v>3.692904092638642</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.74392550571443</v>
+        <v>3.743925505714427</v>
       </c>
       <c r="C2004" t="n">
         <v>3.508572291939687</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.277556997119123</v>
+        <v>-3.223021038988401</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.19719306877829</v>
+        <v>2.219007452030579</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.2395448678725258</v>
+        <v>0.2940808260032477</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.652299212663202</v>
+        <v>3.685020787541636</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155041</v>
+        <v>3.719118627155037</v>
       </c>
       <c r="C2005" t="n">
         <v>3.510626291489324</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.425562764598522</v>
+        <v>-3.371026806467801</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.140044761336168</v>
+        <v>2.161859144588457</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.1528178590089844</v>
+        <v>0.2073538171397062</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.602317006894715</v>
+        <v>3.635038581773148</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161986</v>
+        <v>3.729452285161982</v>
       </c>
       <c r="C2006" t="n">
         <v>3.566880009211171</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.435003690487052</v>
+        <v>-3.380467732356331</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.192522108702603</v>
+        <v>2.214336491954892</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.2752449765523758</v>
+        <v>0.3297809346830977</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.732026995142597</v>
+        <v>3.76474857002103</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321643</v>
+        <v>3.714941193321639</v>
       </c>
       <c r="C2007" t="n">
         <v>3.569771103756472</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.433716926947496</v>
+        <v>-3.379180968816774</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.195927908663727</v>
+        <v>2.217742291916015</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.2765317400919324</v>
+        <v>0.3310676982226542</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.735690147811632</v>
+        <v>3.768411722690065</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347711</v>
+        <v>3.727898186347708</v>
       </c>
       <c r="C2008" t="n">
         <v>3.567882916650247</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.435273980936787</v>
+        <v>-3.380738022806066</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.193416899961785</v>
+        <v>2.215231283214074</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.2765317400919324</v>
+        <v>0.3310676982226542</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.733801960705407</v>
+        <v>3.76652353558384</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887755</v>
+        <v>3.710654104887752</v>
       </c>
       <c r="C2009" t="n">
         <v>3.56270314625311</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.442545866460252</v>
+        <v>-3.38800990832953</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.185328375355262</v>
+        <v>2.20714275860755</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.2692598545684676</v>
+        <v>0.3237958126991895</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.72425905899419</v>
+        <v>3.756980633872624</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343073</v>
+        <v>3.712897612343069</v>
       </c>
       <c r="C2010" t="n">
         <v>3.561137156463262</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.440704847402001</v>
+        <v>-3.386168889271279</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.184498793188714</v>
+        <v>2.206313176441003</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.270528081239936</v>
+        <v>0.3250640393706579</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.723454005207224</v>
+        <v>3.756175580085657</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647114</v>
+        <v>3.75491190764711</v>
       </c>
       <c r="C2011" t="n">
         <v>3.574210563329181</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.447613552901681</v>
+        <v>-3.393077594770959</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.194808717854761</v>
+        <v>2.216623101107049</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.270528081239936</v>
+        <v>0.3250640393706579</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.736527412073142</v>
+        <v>3.769248986951576</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763536</v>
+        <v>3.749896851763532</v>
       </c>
       <c r="C2012" t="n">
         <v>3.574210563329181</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.449175195716541</v>
+        <v>-3.394639237585819</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.194184060728817</v>
+        <v>2.215998443981106</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.270528081239936</v>
+        <v>0.3250640393706579</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.736527412073142</v>
+        <v>3.769248986951576</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.787316069270142</v>
+        <v>3.831072131322751</v>
       </c>
       <c r="C2013" t="n">
         <v>3.705409932039554</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.449175195716541</v>
+        <v>-3.452074347663385</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.194184060728817</v>
+        <v>2.324223768660453</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.270528081239936</v>
+        <v>0.2748498907125267</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.698473729025922</v>
+        <v>3.87031986646707</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240702.xlsx
+++ b/tame_output/ON/bt/strategyON_20240702.xlsx
@@ -600,12 +600,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>61.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.2%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>82.0%</t>
+          <t>77.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>45.6%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.3%</t>
+          <t>-73.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.6%</t>
+          <t>109.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.5%</t>
+          <t>123.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.3%</t>
+          <t>94.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -987,17 +987,17 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.1%</t>
+          <t>-49.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-67.4%</t>
+          <t>-68.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.1%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>452.3%</t>
+          <t>452.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-506.8%</t>
+          <t>-525.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,22 +1140,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-7.2%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-39.6%</t>
+          <t>-37.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-31.1%</t>
+          <t>-50.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>70.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-143.8%</t>
+          <t>-164.4%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-19.0%</t>
+          <t>-18.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.8%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-31.4%</t>
+          <t>-33.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-178.0%</t>
+          <t>-172.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-196.5%</t>
+          <t>-195.4%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.1%</t>
+          <t>96.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.5%</t>
+          <t>-26.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>-18.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-59.0%</t>
+          <t>-71.6%</t>
         </is>
       </c>
     </row>
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.311888301355688</v>
+        <v>3.311888301355689</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279812</v>
+        <v>3.385382209279813</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511402</v>
+        <v>3.367379938511403</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998558</v>
+        <v>3.367370539998559</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082122</v>
+        <v>3.299560092082123</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.29349053375792</v>
+        <v>3.293490533757921</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760738</v>
+        <v>3.293766719760739</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296835</v>
+        <v>3.299918119296836</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201486</v>
+        <v>3.295507330201487</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153005</v>
+        <v>3.258791981153006</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537425</v>
+        <v>3.271168579537426</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382191</v>
+        <v>3.272760131382192</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074623</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911641</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213498</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416047</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130017</v>
+        <v>3.287377576130018</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207812</v>
+        <v>3.305316798207813</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309424</v>
+        <v>3.311086391309425</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970905</v>
+        <v>3.304715716970906</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191737</v>
+        <v>3.302618194191738</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108639</v>
+        <v>3.30502326510864</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097821</v>
+        <v>3.341378723097822</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094116</v>
+        <v>3.374439043094117</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199286</v>
+        <v>3.405960511199287</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969593</v>
+        <v>3.424633354969594</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923086</v>
+        <v>3.419979433923087</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297749</v>
+        <v>3.45810009129775</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317618</v>
+        <v>3.447750501317619</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.503515506737172</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341315</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539465</v>
+        <v>3.501052558539466</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.4924487119375</v>
+        <v>3.492448711937501</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.703230192411484</v>
+        <v>-9.873404154998514</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.7413284090230938</v>
+        <v>-0.8093979940579059</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.285159678283608</v>
+        <v>-2.310144017951603</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.769224285285083</v>
+        <v>1.754233681484286</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729892</v>
+        <v>3.496851904729893</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.777563168671648</v>
+        <v>-9.947737131258679</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.7665790450427235</v>
+        <v>-0.834648630077536</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.42985920221828</v>
+        <v>-2.454843541886275</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.686887125408715</v>
+        <v>1.671896521607918</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440635</v>
+        <v>3.499971739440636</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.704093337004199</v>
+        <v>-9.87426729959123</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.7218194108823228</v>
+        <v>-0.7898889959171349</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.356389370550832</v>
+        <v>-2.381373710218827</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.746340725902605</v>
+        <v>1.731350122101808</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.879217754390742</v>
+        <v>-10.04939171697777</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.7773139570894232</v>
+        <v>-0.8453835421242353</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.531513787937376</v>
+        <v>-2.556498127605371</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.655821296218196</v>
+        <v>1.640830692417399</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.11366984840523</v>
+        <v>-10.28384381099226</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.8783139595968152</v>
+        <v>-0.9463835446316273</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.531513787937376</v>
+        <v>-2.556498127605371</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.6486021313166</v>
+        <v>1.633611527515803</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764398</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.21804457943168</v>
+        <v>-10.38821854201871</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.92673604278137</v>
+        <v>-0.9948056278161821</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.635888518963821</v>
+        <v>-2.660872858631816</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.579305101926756</v>
+        <v>1.564314498125959</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390587</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.27083073503201</v>
+        <v>-10.44100469761904</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.9467347151829442</v>
+        <v>-1.014804300217756</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.731564005546218</v>
+        <v>-2.756548345214213</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.523015599815875</v>
+        <v>1.508024996015078</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.4921016412974</v>
+        <v>3.492101641297401</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.39686752840029</v>
+        <v>-10.56704149098733</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.9944557039011452</v>
+        <v>-1.062525288935957</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.706312382736476</v>
+        <v>-2.731296722404471</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.540860302130834</v>
+        <v>1.525869698330037</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322545</v>
+        <v>3.573674025322546</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.34485201443148</v>
+        <v>-10.51502597701851</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.9696591626272193</v>
+        <v>-1.037728747662031</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.706312382736476</v>
+        <v>-2.731296722404471</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.544850637817235</v>
+        <v>1.529860034016438</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158923</v>
+        <v>3.600038265158924</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.4865238561556</v>
+        <v>-10.65669781874263</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.027803126215609</v>
+        <v>-1.095872711250421</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.706312382736476</v>
+        <v>-2.731296722404471</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.543375410918494</v>
+        <v>1.528384807117697</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940721</v>
+        <v>3.691571733940722</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.43693301173077</v>
+        <v>-10.6071069743178</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.9929133782808033</v>
+        <v>-1.060982963315615</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.656721538311642</v>
+        <v>-2.681705877979637</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.588183327738266</v>
+        <v>1.573192723937469</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770582</v>
+        <v>3.676841549770583</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.42412561872599</v>
+        <v>-10.59429958131302</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.000841554725576</v>
+        <v>-1.068911139760389</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.705577313320543</v>
+        <v>-2.730561652988538</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.545818729086243</v>
+        <v>1.530828125285446</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615286</v>
+        <v>3.685161381615287</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.19828046600658</v>
+        <v>-10.36845442859361</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.9009244206016036</v>
+        <v>-0.9689940056364157</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.66365063773338</v>
+        <v>-2.688634977401374</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.580553807474749</v>
+        <v>1.565563203673952</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.07370180966899</v>
+        <v>-10.24387577225602</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.8499538135105085</v>
+        <v>-0.9180233985453197</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.66365063773338</v>
+        <v>-2.688634977401374</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.581692952030808</v>
+        <v>1.566702348230011</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.71093553364622</v>
+        <v>3.710935533646221</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.12659709771328</v>
+        <v>-10.29677106030031</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.8684781545661151</v>
+        <v>-0.9365477396009263</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.658695291644933</v>
+        <v>-2.683679631312928</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.587299933845984</v>
+        <v>1.572309330045187</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611571</v>
+        <v>3.768951674611572</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.0544639224254</v>
+        <v>-10.22463788501243</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8338911802123263</v>
+        <v>-0.9019607652471375</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.658695291644933</v>
+        <v>-2.683679631312928</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.59303363808462</v>
+        <v>1.578043034283823</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955331</v>
+        <v>3.728577929955332</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.983097529815749</v>
+        <v>-10.15327149240278</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8150818855623325</v>
+        <v>-0.8831514705971442</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.587328899035285</v>
+        <v>-2.61231323870328</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.626116211256544</v>
+        <v>1.611125607455747</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.889638495830525</v>
+        <v>-10.05981245841755</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.7875817532811502</v>
+        <v>-0.8556513383159614</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.587328899035285</v>
+        <v>-2.61231323870328</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.616232729943636</v>
+        <v>1.601242126142839</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436233</v>
+        <v>3.766317079436234</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.622396694962127</v>
+        <v>-9.792570657549156</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6825195934331649</v>
+        <v>-0.7505891784679766</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.587328899035285</v>
+        <v>-2.61231323870328</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.614398169444263</v>
+        <v>1.599407565643466</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311953</v>
+        <v>3.784684521311954</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.524489656285636</v>
+        <v>-9.694663618872665</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6436570929360292</v>
+        <v>-0.7117266779708409</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.519343149174729</v>
+        <v>-2.544327488842724</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.654889304387136</v>
+        <v>1.639898700586339</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097249</v>
+        <v>3.80082935409725</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.500536115309679</v>
+        <v>-9.670710077896707</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6334071704001527</v>
+        <v>-0.7014767554349643</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.495389608198771</v>
+        <v>-2.520373947866766</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.669929935118204</v>
+        <v>1.654939331317407</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017777</v>
+        <v>3.789311112017778</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.236476176986882</v>
+        <v>-9.406650139573911</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.541043511232786</v>
+        <v>-0.6091130962675977</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.231329669875975</v>
+        <v>-2.25631400954397</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.815105581950129</v>
+        <v>1.800114978149332</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.529396553482044</v>
+        <v>-8.699570516069073</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2609986954911521</v>
+        <v>-0.3290682805259637</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.231329669875975</v>
+        <v>-2.25631400954397</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.812318548289828</v>
+        <v>1.797327944489031</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388733</v>
+        <v>3.839374447388735</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.489212255115854</v>
+        <v>-8.659386217702883</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2445813522568345</v>
+        <v>-0.3126509372916462</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.191145371509784</v>
+        <v>-2.216129711177779</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.836772751197384</v>
+        <v>1.821782147396587</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626479</v>
+        <v>3.856161751626481</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.325812384176491</v>
+        <v>-8.495986346763519</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.1798545826603322</v>
+        <v>-0.2479241676951438</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.027745500570422</v>
+        <v>-2.052729840238417</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.934179494981759</v>
+        <v>1.919188891180962</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291815</v>
+        <v>3.787330429291817</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.092331161946891</v>
+        <v>-8.26250512453392</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.07853766493064018</v>
+        <v>-0.1466072499654514</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.794264278340823</v>
+        <v>-1.819248618008818</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.08219265715737</v>
+        <v>2.067202053356573</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785792</v>
+        <v>3.801637122785793</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.942664770939376</v>
+        <v>-8.112838733526406</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.02156331884059304</v>
+        <v>-0.08963290387540512</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.701360787098287</v>
+        <v>-1.726345126766282</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.135042541589932</v>
+        <v>2.120051937789135</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390431</v>
+        <v>3.763182248390433</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.81038929730849</v>
+        <v>-7.980563259895519</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.02671435735878847</v>
+        <v>-0.04135522767602362</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.569085313467401</v>
+        <v>-1.594069653135396</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.209775312515491</v>
+        <v>2.194784708714694</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105955</v>
+        <v>3.784718794105957</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.654650964748748</v>
+        <v>-7.824824927335778</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.09182475107032184</v>
+        <v>0.0237551660355102</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.413346980907659</v>
+        <v>-1.438331320575654</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.306033372738973</v>
+        <v>2.291042768938176</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960991</v>
+        <v>3.753882571960992</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.405651166065167</v>
+        <v>-7.575825128652196</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.2043310117674131</v>
+        <v>0.136261426732601</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.413346980907659</v>
+        <v>-1.438331320575654</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.318939713962632</v>
+        <v>2.303949110161835</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607649</v>
+        <v>3.692931855607651</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.511241155838271</v>
+        <v>-7.681415118425301</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.03411908625895244</v>
+        <v>-0.03395049877585921</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.518936970680764</v>
+        <v>-1.543921310348759</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.127609790499551</v>
+        <v>2.112619186698754</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987908</v>
+        <v>3.77042258398791</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.529976057956868</v>
+        <v>-7.700150020543898</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.07516946728860008</v>
+        <v>0.007099882253788437</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.524532980340895</v>
+        <v>-1.54951732000889</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.172796526580558</v>
+        <v>2.157805922779761</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710816</v>
+        <v>3.760333686710817</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.382036016549269</v>
+        <v>-7.552209979136299</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.01446656116347222</v>
+        <v>-0.05360302387133942</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.504212064432337</v>
+        <v>-1.529196404100332</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.065110153437525</v>
+        <v>2.050119549636728</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409209</v>
+        <v>3.72356622940921</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.274530536164558</v>
+        <v>-7.49924045688231</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.04875476706387838</v>
+        <v>-0.04112920122322228</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.396706584047627</v>
+        <v>-1.476226881846344</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.120899455414873</v>
+        <v>2.073187276735643</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098113</v>
+        <v>3.729969716098115</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.230982129393868</v>
+        <v>-7.45569205011162</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.0592135176770614</v>
+        <v>-0.03067045061003926</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.396706584047627</v>
+        <v>-1.476226881846344</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.11393884331978</v>
+        <v>2.06622666464055</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493424</v>
+        <v>3.782922533493426</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.98883373594001</v>
+        <v>-7.213543656657762</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1705352294397477</v>
+        <v>0.08065126115264709</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.396706584047627</v>
+        <v>-1.476226881846344</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.128401197700923</v>
+        <v>2.080689019021693</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.82855148672282</v>
+        <v>3.828551486722822</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.880574598817488</v>
+        <v>-7.10528451953524</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.2083710047479514</v>
+        <v>0.1184870364608508</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.396706584047627</v>
+        <v>-1.476226881846344</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.122933318160118</v>
+        <v>2.075221139480888</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792049</v>
+        <v>3.828052928792051</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.757283464000357</v>
+        <v>-6.981993384718109</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2551855526853806</v>
+        <v>0.1653015843982799</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.273415449230496</v>
+        <v>-1.352935747029213</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.194406093060973</v>
+        <v>2.146693914381743</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919911</v>
+        <v>3.812453678919913</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.736134265096914</v>
+        <v>-6.960844185814666</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2713462104840829</v>
+        <v>0.1814622421969823</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.252266250327053</v>
+        <v>-1.33178654812577</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.214796590640365</v>
+        <v>2.167084411961135</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318097</v>
+        <v>3.748328408318099</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.49236882311347</v>
+        <v>-6.717078743831221</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3646330956245114</v>
+        <v>0.2747491273374107</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.252266250327053</v>
+        <v>-1.33178654812577</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.210577298987415</v>
+        <v>2.162865120308185</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.82431123305753</v>
+        <v>3.824311233057532</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.390606002836175</v>
+        <v>-6.615315923553927</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.4074625376554453</v>
+        <v>0.3175785693683446</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.239047181934624</v>
+        <v>-1.318567479733341</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.220633053942889</v>
+        <v>2.172920875263658</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.82635497427919</v>
+        <v>3.826354974279192</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.1407556088871</v>
+        <v>-6.365465529604852</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.5001447702187773</v>
+        <v>0.4102608019316767</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.239047181934624</v>
+        <v>-1.318567479733341</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.21337512892659</v>
+        <v>2.165662950247361</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011503</v>
+        <v>3.835957987011505</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.964863516419667</v>
+        <v>-6.189573437137419</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5741007307263994</v>
+        <v>0.4842167624392988</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.239047181934624</v>
+        <v>-1.318567479733341</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.21697425244724</v>
+        <v>2.169262073768009</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392992</v>
+        <v>3.780933911392994</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.793417053397204</v>
+        <v>-6.018126974114955</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6560068219899384</v>
+        <v>0.5661228537028378</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.067600718912161</v>
+        <v>-1.147121016710878</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.333169636315271</v>
+        <v>2.285457457636041</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632787</v>
+        <v>3.773765222632789</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.719127487658865</v>
+        <v>-5.943837408376616</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.684743125901571</v>
+        <v>0.5948591576144704</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.9933111531738217</v>
+        <v>-1.072831450972539</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.376763853374571</v>
+        <v>2.329051674695342</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.76461787988308</v>
+        <v>3.764617879883081</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.65549174542493</v>
+        <v>-5.880201666142682</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7148922238494624</v>
+        <v>0.6250082555623617</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.9296754109398871</v>
+        <v>-1.009195708738604</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.41964009976925</v>
+        <v>2.37192792109002</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107479</v>
+        <v>3.798814771074792</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.54406498609901</v>
+        <v>-5.768774906816762</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.740657186363626</v>
+        <v>0.6507732180765253</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.9296754109398871</v>
+        <v>-1.009195708738604</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.400834358553045</v>
+        <v>2.353122179873815</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242302</v>
+        <v>3.797694884242303</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.30363448929415</v>
+        <v>-5.528344410011901</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8385724617104473</v>
+        <v>0.7486884934233466</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.6892449141350269</v>
+        <v>-0.7687652119337436</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.546835733260839</v>
+        <v>2.499123554581609</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367692</v>
+        <v>3.821593509367694</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.231391921122955</v>
+        <v>-5.456101841840707</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8713988028137454</v>
+        <v>0.7815148345266447</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.6892449141350269</v>
+        <v>-0.7687652119337436</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.550765047095659</v>
+        <v>2.503052868416429</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879973</v>
+        <v>3.822326997879975</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.178393598841567</v>
+        <v>-5.403103519559319</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8932767156436405</v>
+        <v>0.8033927473565399</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.633908655133088</v>
+        <v>-0.7134289529318047</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.584645386414162</v>
+        <v>2.536933207734932</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502345</v>
+        <v>3.848616626502347</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.06958871336184</v>
+        <v>-5.294298634079592</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.933796741055525</v>
+        <v>0.8439127727684244</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.633908655133088</v>
+        <v>-0.7134289529318047</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.581643457634156</v>
+        <v>2.533931278954926</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675947</v>
+        <v>3.818668951675948</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.84956791532483</v>
+        <v>-5.074277836042581</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.023384097280943</v>
+        <v>0.9335001289938427</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4926888100651078</v>
+        <v>-0.5722091078638245</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.667954401685558</v>
+        <v>2.620242223006328</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539958</v>
+        <v>3.843274527539959</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.716700226261552</v>
+        <v>-4.941410146979304</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.092425355708078</v>
+        <v>1.002541387420977</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4926888100651078</v>
+        <v>-0.5722091078638245</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.683848584487381</v>
+        <v>2.636136405808151</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496266</v>
+        <v>3.845047386496267</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.596527142897053</v>
+        <v>-4.821237063614805</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.141640433494179</v>
+        <v>1.051756465207078</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.3725157267006088</v>
+        <v>-0.4520360244993256</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.757098278946382</v>
+        <v>2.709386100267153</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577003</v>
+        <v>3.791273551577004</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.451854997797316</v>
+        <v>-4.676564918515068</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.209597394095514</v>
+        <v>1.119713425808413</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.2278435816008714</v>
+        <v>-0.3073638793995881</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.853989668567665</v>
+        <v>2.806277489888435</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942108</v>
+        <v>3.735839222942109</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.511729825155008</v>
+        <v>-4.73643974587276</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.171684954553863</v>
+        <v>1.081800986266762</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.2877184089585635</v>
+        <v>-0.3672387067572803</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.804102263554475</v>
+        <v>2.756390084875245</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.76264747767452</v>
+        <v>3.762647477674521</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.424930327376</v>
+        <v>-4.649640248093752</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.228805246988032</v>
+        <v>1.138921278700932</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.2877184089585635</v>
+        <v>-0.3672387067572803</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.826502756877042</v>
+        <v>2.778790578197811</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430699</v>
+        <v>3.7291463984307</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.427400033837806</v>
+        <v>-4.652109954555558</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.227889765776722</v>
+        <v>1.138005797489621</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.2901881154203697</v>
+        <v>-0.3697084132190864</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.82509333437337</v>
+        <v>2.77738115569414</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003608</v>
+        <v>3.743220196003609</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.495770220161816</v>
+        <v>-4.720480140879568</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.21154861372182</v>
+        <v>1.121664645434719</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.2809124163841548</v>
+        <v>-0.3604327141828715</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.841665676269801</v>
+        <v>2.793953497590571</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508376</v>
+        <v>3.714179139508377</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.509558273008863</v>
+        <v>-4.734268193726614</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.196470101214892</v>
+        <v>1.106586132927792</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.2809124163841548</v>
+        <v>-0.3604327141828715</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.832102384901692</v>
+        <v>2.784390206222462</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417711</v>
+        <v>3.710906731417712</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.540551432337568</v>
+        <v>-4.76526135305532</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.008782402523797</v>
+        <v>0.9188984342366964</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.2809124163841548</v>
+        <v>-0.3604327141828715</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.656811949942079</v>
+        <v>2.609099771262849</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205906</v>
+        <v>3.746042526205908</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.365077172545099</v>
+        <v>-4.589787093262851</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.083539338432572</v>
+        <v>0.9936553701454718</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.2809124163841548</v>
+        <v>-0.3604327141828715</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.661379181933867</v>
+        <v>2.613667003254637</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225451</v>
+        <v>3.765024323225453</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.476013425186348</v>
+        <v>-4.7007233459041</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.01490686613728</v>
+        <v>0.9250228978501793</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.2809124163841548</v>
+        <v>-0.3604327141828715</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.637121210695074</v>
+        <v>2.589409032015844</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.7732102971113</v>
+        <v>3.773210297111302</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.442349879714066</v>
+        <v>-4.667059800431818</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.031503669546098</v>
+        <v>0.9416197012589977</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.2472488709118729</v>
+        <v>-0.3267691687105896</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.660450723198349</v>
+        <v>2.612738544519118</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.78434395226417</v>
+        <v>3.784343952264171</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.382497260510343</v>
+        <v>-4.57113057475906</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.06561710365972</v>
+        <v>0.990163777960233</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.2472488709118729</v>
+        <v>-0.3267691687105896</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.670623109630481</v>
+        <v>2.622910930951251</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742306</v>
+        <v>3.786949957742308</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.296253797483965</v>
+        <v>-4.484887111732682</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.095060759444131</v>
+        <v>1.019607433744645</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.2472488709118729</v>
+        <v>-0.3267691687105896</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.665569380204341</v>
+        <v>2.617857201525111</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316053</v>
+        <v>3.752027499316054</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.341560616882945</v>
+        <v>-4.530193931131662</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.068713807129065</v>
+        <v>0.9932604814295782</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2880590339211037</v>
+        <v>-0.3675793317198204</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.632859057843328</v>
+        <v>2.585146879164098</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803198</v>
+        <v>3.7535711658032</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.370593721585246</v>
+        <v>-4.559227035833963</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.057652438281246</v>
+        <v>0.9821991125817593</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2880590339211037</v>
+        <v>-0.3675793317198204</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.63341093087643</v>
+        <v>2.5856987521972</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809504</v>
+        <v>3.733390600809506</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.277783240134386</v>
+        <v>-4.466416554383104</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.024049322752956</v>
+        <v>0.9485959970534688</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1952485524702444</v>
+        <v>-0.2747688502689611</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.618369911638311</v>
+        <v>2.570657732959081</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560431</v>
+        <v>3.748285816560433</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.322172709463814</v>
+        <v>-4.510806023712531</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.008167010945785</v>
+        <v>0.9327136852462985</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.239638021799672</v>
+        <v>-0.3191583195983888</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.593609705965255</v>
+        <v>2.545897527286025</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472744</v>
+        <v>3.721077195472746</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.209501491227564</v>
+        <v>-4.398134805476281</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.048311206752008</v>
+        <v>0.9728578810525217</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.1269668035634218</v>
+        <v>-0.2064871013621385</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.656288145418729</v>
+        <v>2.608575966739498</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798543</v>
+        <v>3.743047603798545</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.097124490044891</v>
+        <v>-4.285757804293608</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.098753303055745</v>
+        <v>1.023299977356258</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.1269668035634218</v>
+        <v>-0.2064871013621385</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.661779441249396</v>
+        <v>2.614067262570166</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498871</v>
+        <v>3.689597840498873</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.124904887946244</v>
+        <v>-4.313538202194961</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.099138345663743</v>
+        <v>1.023685019964256</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1547472014647749</v>
+        <v>-0.2342674992634916</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.656608404277123</v>
+        <v>2.608896225597893</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705332</v>
+        <v>3.643069621705334</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.207906168971522</v>
+        <v>-4.39653948322024</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9042935532542846</v>
+        <v>0.8288402275547977</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1733180859919486</v>
+        <v>-0.2528383837906654</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.483821593561472</v>
+        <v>2.436109414882242</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729277</v>
+        <v>3.682716310729278</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.316520247414854</v>
+        <v>-4.505153561663571</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9809975825961579</v>
+        <v>0.905544256896671</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1733180859919486</v>
+        <v>-0.2528383837906654</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.603971254280677</v>
+        <v>2.556259075601448</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190776</v>
+        <v>3.733012441190778</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.281111209166711</v>
+        <v>-4.469744523415428</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.009674223997738</v>
+        <v>0.9342208982982512</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1733180859919486</v>
+        <v>-0.2528383837906654</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.618484280383</v>
+        <v>2.570772101703771</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913433</v>
+        <v>3.741174069913435</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.24272754660856</v>
+        <v>-4.431360860857277</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.022447130363367</v>
+        <v>0.9469938046638802</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.1349344234337975</v>
+        <v>-0.2144547212325142</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.63893391926026</v>
+        <v>2.59122174058103</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532494</v>
+        <v>3.751147197532496</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.065611216573394</v>
+        <v>-4.254244530822111</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.090022691222735</v>
+        <v>1.014569365523249</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.1349344234337975</v>
+        <v>-0.2144547212325142</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.635662948105562</v>
+        <v>2.587950769426332</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793912</v>
+        <v>3.741328448793913</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.110703461406939</v>
+        <v>-4.299336775655656</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.07266918505123</v>
+        <v>0.9972158593517433</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1968304666031873</v>
+        <v>-0.276350764401904</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.599208713965841</v>
+        <v>2.551496535286611</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011244</v>
+        <v>3.750729377011246</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.931328040168172</v>
+        <v>-4.119961354416889</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.138206328853152</v>
+        <v>1.062753003153665</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.04005370843246858</v>
+        <v>-0.1195740062311853</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.687061744174687</v>
+        <v>2.639349565495456</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982238</v>
+        <v>3.71699171898224</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.976342253688778</v>
+        <v>-4.164975567937494</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.101008098776499</v>
+        <v>1.025554773077012</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.07040260374707319</v>
+        <v>-0.1499229015457899</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.649659862317514</v>
+        <v>2.601947683638284</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509547</v>
+        <v>3.737026608509549</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.243346763961213</v>
+        <v>-4.431980078209929</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9998978570064705</v>
+        <v>0.924444531306984</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2647656417900218</v>
+        <v>-0.3442859395887385</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.53873360183069</v>
+        <v>2.49102142315146</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760818</v>
+        <v>3.70230945476082</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.344544545398386</v>
+        <v>-4.533177859647102</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9586226663281028</v>
+        <v>0.8831693406286163</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.333174455335341</v>
+        <v>-0.4126947531340577</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.4968922356</v>
+        <v>2.44918005692077</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815462</v>
+        <v>3.705571661815464</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.338033578784073</v>
+        <v>-4.52666689303279</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9588270145281446</v>
+        <v>0.8833736888286581</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.333174455335341</v>
+        <v>-0.4126947531340577</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.494492197154317</v>
+        <v>2.446780018475087</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378106</v>
+        <v>3.709510443378107</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.318995451076776</v>
+        <v>-4.507628765325492</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9629669848193085</v>
+        <v>0.8875136591198221</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3913580666665355</v>
+        <v>-0.4708783644652522</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.456106749563845</v>
+        <v>2.408394570884615</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131257</v>
+        <v>3.731064473131259</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.350122082227394</v>
+        <v>-4.538755396476111</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.128098201297742</v>
+        <v>1.052644875598255</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3913580666665355</v>
+        <v>-0.4708783644652522</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.633688618502526</v>
+        <v>2.585976439823296</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067873</v>
+        <v>3.722447362067875</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.363988843561312</v>
+        <v>-4.552622157810029</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.123384825750308</v>
+        <v>1.047931500050822</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4292159834003584</v>
+        <v>-0.5087362811990752</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.611807197448365</v>
+        <v>2.564095018769136</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789129</v>
+        <v>3.787425580789131</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.319184672021382</v>
+        <v>-4.507817986270099</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.147315024763206</v>
+        <v>1.07186169906372</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4292159834003584</v>
+        <v>-0.5087362811990752</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.617815727845291</v>
+        <v>2.570103549166062</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519916</v>
+        <v>3.781501250519918</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.17144170178638</v>
+        <v>-4.360075016035096</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.285564860649229</v>
+        <v>1.210111534949742</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2614086261654753</v>
+        <v>-0.3409289239641921</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.797652789978243</v>
+        <v>2.749940611299013</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181178</v>
+        <v>3.80224592918118</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.273456384317601</v>
+        <v>-4.462089698566317</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.247552609168221</v>
+        <v>1.172099283468735</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2614086261654753</v>
+        <v>-0.3409289239641921</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.800446411509724</v>
+        <v>2.752734232830494</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394739</v>
+        <v>3.80560898539474</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.267303678264817</v>
+        <v>-4.455936992513533</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.250676039980994</v>
+        <v>1.175222714281507</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.255255920112691</v>
+        <v>-0.3347762179114078</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.804800383533053</v>
+        <v>2.757088204853823</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890615</v>
+        <v>3.798239794890617</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.284112976415319</v>
+        <v>-4.472746290664035</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.243032797460903</v>
+        <v>1.167579471761417</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.2720652182631926</v>
+        <v>-0.3515855160619094</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.793795281382862</v>
+        <v>2.746083102703632</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798433</v>
+        <v>3.867362636798434</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.221814977639196</v>
+        <v>-4.410448291887913</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.334287550768173</v>
+        <v>1.258834225068686</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.2720652182631926</v>
+        <v>-0.3515855160619094</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.860130835179683</v>
+        <v>2.812418656500453</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.8487291399922</v>
+        <v>3.848729139992201</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.020024779974039</v>
+        <v>-4.208658094222755</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.123584502223634</v>
+        <v>1.048131176524147</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.07404702609403824</v>
+        <v>-0.153567323892755</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.687522622870574</v>
+        <v>2.639810444191344</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852429</v>
+        <v>3.841444817852431</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.946646682885302</v>
+        <v>-4.135279997134019</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.223225973381304</v>
+        <v>1.147772647681817</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.0006689290053016883</v>
+        <v>-0.08018922680401847</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.801839713445991</v>
+        <v>2.754127534766761</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319553</v>
+        <v>3.819063300319556</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.044387227510276</v>
+        <v>-4.233020541758993</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.198757491647358</v>
+        <v>1.123304165947871</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.01655820713828188</v>
+        <v>-0.09607850493699865</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.806933882682247</v>
+        <v>2.759221704003016</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489392</v>
+        <v>3.831819032489395</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.220724987633205</v>
+        <v>-4.409358301881922</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.126758368422858</v>
+        <v>1.051305042723371</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.1928959672612113</v>
+        <v>-0.2724162650599281</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.699667207433161</v>
+        <v>2.65195502875393</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397801</v>
+        <v>3.836411672397804</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.144302941201278</v>
+        <v>-4.332936255449995</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.155818805035557</v>
+        <v>1.08036547933607</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.1928959672612113</v>
+        <v>-0.2724162650599281</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.698158825473089</v>
+        <v>2.650446646793859</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316256</v>
+        <v>3.833513460316259</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.09992980956271</v>
+        <v>-4.288563123811427</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.173430925126421</v>
+        <v>1.097977599426934</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.1485228356226427</v>
+        <v>-0.2280431334213595</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.724645571891667</v>
+        <v>2.676933393212436</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.82156211710597</v>
+        <v>3.821562117105973</v>
       </c>
       <c r="C1977" t="n">
         <v>2.808153067403842</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.977095588675542</v>
+        <v>-4.165728902924259</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.216958407619878</v>
+        <v>1.141505081920391</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.1485228356226427</v>
+        <v>-0.2280431334213595</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.719039366030257</v>
+        <v>2.671327187351027</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190328</v>
+        <v>3.833011148190331</v>
       </c>
       <c r="C1978" t="n">
         <v>2.814534824431647</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.929439858114486</v>
+        <v>-4.077837976526363</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.242402456872105</v>
+        <v>1.183043209507354</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.100867105061587</v>
+        <v>-0.1401522070234625</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.754014561394694</v>
+        <v>2.730443500217569</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.82267821056962</v>
+        <v>3.822678210569624</v>
       </c>
       <c r="C1979" t="n">
         <v>2.819427197806371</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.828921699615732</v>
+        <v>-3.977319818027608</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.287502093646332</v>
+        <v>1.228142846281581</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.0003489465628324639</v>
+        <v>-0.03963404852470792</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.819217829868672</v>
+        <v>2.795646768691547</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557296</v>
+        <v>3.828808877557299</v>
       </c>
       <c r="C1980" t="n">
         <v>2.806181870282244</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.889588290018121</v>
+        <v>-4.037986408429997</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.249990129961248</v>
+        <v>1.190630882596497</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.08204726328136613</v>
+        <v>-0.1213323652432416</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.756953512313424</v>
+        <v>2.733382451136299</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932771</v>
+        <v>3.816837033932774</v>
       </c>
       <c r="C1981" t="n">
         <v>2.810279572892872</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.844749888409723</v>
+        <v>-3.993148006821599</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.272023193215236</v>
+        <v>1.212663945850485</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.07750383033649666</v>
+        <v>-0.1167889322983721</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.763777274690975</v>
+        <v>2.740206213513849</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917055</v>
+        <v>3.817932354917058</v>
       </c>
       <c r="C1982" t="n">
         <v>2.81444051252395</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.945508524166721</v>
+        <v>-4.093906642578598</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.235880678543514</v>
+        <v>1.176521431178764</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.1663293990635021</v>
+        <v>-0.2056145010253775</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.714642873085849</v>
+        <v>2.691071811908724</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405964</v>
+        <v>3.826684745405967</v>
       </c>
       <c r="C1983" t="n">
         <v>2.820320115051787</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.901305687080821</v>
+        <v>-4.049703805492697</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.259441415905712</v>
+        <v>1.200082168540961</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.1221265619776016</v>
+        <v>-0.1614116639394771</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.747044177865227</v>
+        <v>2.723473116688101</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265649</v>
+        <v>3.838199629265652</v>
       </c>
       <c r="C1984" t="n">
         <v>2.818730115521035</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.938284714744264</v>
+        <v>-4.086682833156141</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.243059805309582</v>
+        <v>1.183700557944831</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.0851526601862711</v>
+        <v>-0.1244377621481466</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.767638519409273</v>
+        <v>2.744067458232147</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284883</v>
+        <v>3.863895080284887</v>
       </c>
       <c r="C1985" t="n">
         <v>2.869977880704075</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.958342793609104</v>
+        <v>-4.106740912020982</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.286284338946686</v>
+        <v>1.226925091581935</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.0851526601862711</v>
+        <v>-0.1244377621481466</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.818886284592312</v>
+        <v>2.795315223415187</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321026</v>
+        <v>3.865338681321029</v>
       </c>
       <c r="C1986" t="n">
         <v>2.868418585298328</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.918412120431214</v>
+        <v>-4.066810238843091</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.300697312812095</v>
+        <v>1.241338065447344</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.04522198700838076</v>
+        <v>-0.08450708897025622</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.841285393093299</v>
+        <v>2.817714331916174</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475143</v>
+        <v>3.864489842475146</v>
       </c>
       <c r="C1987" t="n">
         <v>2.863366813536598</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.867380027708686</v>
+        <v>-4.015778146120564</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.316058378139376</v>
+        <v>1.256699130774625</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.005810105714147196</v>
+        <v>-0.03347499624772826</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.866852876965087</v>
+        <v>2.843281815787961</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404859</v>
+        <v>3.842547360404862</v>
       </c>
       <c r="C1988" t="n">
         <v>2.880554217629303</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.80215584658148</v>
+        <v>-3.950553964993358</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.359335454682963</v>
+        <v>1.299976207318212</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.07103428684135282</v>
+        <v>0.03174918487947737</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.923174789734114</v>
+        <v>2.899603728556989</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882562</v>
+        <v>3.840061186882566</v>
       </c>
       <c r="C1989" t="n">
         <v>2.876515189928583</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.764728826510347</v>
+        <v>-3.913126944922225</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.370267235010697</v>
+        <v>1.310907987645946</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.07628582487053448</v>
+        <v>0.03700072290865902</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.922286684850904</v>
+        <v>2.898715623673779</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992667</v>
+        <v>3.84516980899267</v>
       </c>
       <c r="C1990" t="n">
         <v>2.877771982259823</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.784840482545055</v>
+        <v>-3.933238600956933</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.363479364928054</v>
+        <v>1.304120117563303</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.08731316986795368</v>
+        <v>0.04802806790607822</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.930159884180596</v>
+        <v>2.90658882300347</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636293</v>
+        <v>3.828661445636296</v>
       </c>
       <c r="C1991" t="n">
         <v>3.038329753281034</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.73109566811785</v>
+        <v>-3.879493786529728</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.545535061720147</v>
+        <v>1.486175814355396</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.09737647930841564</v>
+        <v>0.05809137734654019</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.096755640866084</v>
+        <v>3.073184579688959</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.81322282095763</v>
+        <v>3.813222820957634</v>
       </c>
       <c r="C1992" t="n">
         <v>3.158442662498851</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.707304099511708</v>
+        <v>-3.855702217923586</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.675164598380421</v>
+        <v>1.61580535101567</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.1211680479145579</v>
+        <v>0.08188294595268247</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.231143491247586</v>
+        <v>3.207572430070461</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998757</v>
+        <v>3.81423072799876</v>
       </c>
       <c r="C1993" t="n">
         <v>3.15015063851271</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.6812200152479</v>
+        <v>-3.829618133659778</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.677306208099803</v>
+        <v>1.617946960735052</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.1211680479145579</v>
+        <v>0.08188294595268247</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.222851467261445</v>
+        <v>3.19928040608432</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.80339781889693</v>
+        <v>3.803397818896934</v>
       </c>
       <c r="C1994" t="n">
         <v>3.14834383409649</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.55092748431829</v>
+        <v>-3.699325602730168</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.727616416055426</v>
+        <v>1.668257168690675</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.3577036724422927</v>
+        <v>0.3184185704804173</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.362966037561866</v>
+        <v>3.339394976384741</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.79626414395986</v>
+        <v>3.796264143959863</v>
       </c>
       <c r="C1995" t="n">
         <v>3.165898239823281</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.542035022925007</v>
+        <v>-3.690433141336885</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.748727806339531</v>
+        <v>1.68936855897478</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.3577036724422927</v>
+        <v>0.3184185704804173</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.380520443288657</v>
+        <v>3.356949382111532</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945369</v>
+        <v>3.794424941945373</v>
       </c>
       <c r="C1996" t="n">
         <v>3.157753287227865</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.710511139894885</v>
+        <v>-3.858909258306763</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.673192406956164</v>
+        <v>1.613833159591413</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.329755836725712</v>
+        <v>0.2904707347638365</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.355606789263292</v>
+        <v>3.332035728086167</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782711</v>
+        <v>3.795574066782715</v>
       </c>
       <c r="C1997" t="n">
         <v>3.139022984415727</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.012711611033302</v>
+        <v>-3.16110972944518</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.933581915688659</v>
+        <v>1.874222668323908</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.2594077773553012</v>
+        <v>0.2201226753934258</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.294667650828908</v>
+        <v>3.271096589651783</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632641</v>
+        <v>3.784671345632645</v>
       </c>
       <c r="C1998" t="n">
         <v>3.129687006912631</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.989990507350149</v>
+        <v>-3.138388625762027</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.933334379658825</v>
+        <v>1.873975132294073</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.2594077773553012</v>
+        <v>0.2201226753934258</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.285331673325813</v>
+        <v>3.261760612148687</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777679</v>
+        <v>3.783205696777682</v>
       </c>
       <c r="C1999" t="n">
         <v>3.2885931327638</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.988265464060105</v>
+        <v>-3.136663582471983</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.092930522826011</v>
+        <v>2.03357127546126</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.261132820645345</v>
+        <v>0.2218477186834695</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.445272825151008</v>
+        <v>3.421701763973882</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644417</v>
+        <v>3.779933725644421</v>
       </c>
       <c r="C2000" t="n">
         <v>3.325670955257447</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.14304647083836</v>
+        <v>-3.291444589250238</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.068095942608355</v>
+        <v>2.008736695243605</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.2277651465908689</v>
+        <v>0.1884800446289934</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.462330043211969</v>
+        <v>3.438758982034843</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799965</v>
+        <v>3.769443619799969</v>
       </c>
       <c r="C2001" t="n">
         <v>3.322346311246992</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.091611137453701</v>
+        <v>-3.240009255865579</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.085345431951764</v>
+        <v>2.025986184587014</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.2792004799755285</v>
+        <v>0.2399153780136531</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.48986659923231</v>
+        <v>3.466295538055184</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.76667349633112</v>
+        <v>3.766673496331124</v>
       </c>
       <c r="C2002" t="n">
         <v>3.332352464891734</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.064659913127213</v>
+        <v>-3.213058031539091</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.106132075327102</v>
+        <v>2.04677282796235</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.2940808260032477</v>
+        <v>0.2547957240413722</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.508800960493683</v>
+        <v>3.485229899316557</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784113</v>
+        <v>3.768052067784117</v>
       </c>
       <c r="C2003" t="n">
         <v>3.516455597036694</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.200612921183529</v>
+        <v>-3.349011039595407</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.235854004249535</v>
+        <v>2.176494756884783</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.2940808260032477</v>
+        <v>0.2547957240413722</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.692904092638642</v>
+        <v>3.669333031461517</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714427</v>
+        <v>3.74392550571443</v>
       </c>
       <c r="C2004" t="n">
         <v>3.508572291939687</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.223021038988401</v>
+        <v>-3.371419157400279</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.219007452030579</v>
+        <v>2.159648204665828</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.2940808260032477</v>
+        <v>0.2547957240413722</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.685020787541636</v>
+        <v>3.66144972636451</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155037</v>
+        <v>3.719118627155041</v>
       </c>
       <c r="C2005" t="n">
         <v>3.510626291489324</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.371026806467801</v>
+        <v>-3.519424924879679</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.161859144588457</v>
+        <v>2.102499897223705</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.2073538171397062</v>
+        <v>0.1680687151778308</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.635038581773148</v>
+        <v>3.611467520596023</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161982</v>
+        <v>3.729452285161986</v>
       </c>
       <c r="C2006" t="n">
         <v>3.566880009211171</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.380467732356331</v>
+        <v>-3.528865850768208</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.214336491954892</v>
+        <v>2.154977244590141</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.3297809346830977</v>
+        <v>0.2904958327212222</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.76474857002103</v>
+        <v>3.741177508843905</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321639</v>
+        <v>3.714941193321643</v>
       </c>
       <c r="C2007" t="n">
         <v>3.569771103756472</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.379180968816774</v>
+        <v>-3.527579087228652</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.217742291916015</v>
+        <v>2.158383044551264</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.3310676982226542</v>
+        <v>0.2917825962607788</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.768411722690065</v>
+        <v>3.744840661512939</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347708</v>
+        <v>3.727898186347711</v>
       </c>
       <c r="C2008" t="n">
         <v>3.567882916650247</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.380738022806066</v>
+        <v>-3.529136141217943</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.215231283214074</v>
+        <v>2.155872035849323</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.3310676982226542</v>
+        <v>0.2917825962607788</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.76652353558384</v>
+        <v>3.742952474406715</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887752</v>
+        <v>3.710654104887755</v>
       </c>
       <c r="C2009" t="n">
         <v>3.56270314625311</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.38800990832953</v>
+        <v>-3.536408026741408</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.20714275860755</v>
+        <v>2.147783511242799</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.3237958126991895</v>
+        <v>0.284510710737314</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.756980633872624</v>
+        <v>3.733409572695498</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343069</v>
+        <v>3.712897612343073</v>
       </c>
       <c r="C2010" t="n">
         <v>3.561137156463262</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.386168889271279</v>
+        <v>-3.534567007683157</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.206313176441003</v>
+        <v>2.146953929076252</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.3250640393706579</v>
+        <v>0.2857789374087825</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.756175580085657</v>
+        <v>3.732604518908532</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.75491190764711</v>
+        <v>3.754911907647114</v>
       </c>
       <c r="C2011" t="n">
         <v>3.574210563329181</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.393077594770959</v>
+        <v>-3.541475713182837</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.216623101107049</v>
+        <v>2.157263853742299</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.3250640393706579</v>
+        <v>0.2857789374087825</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.769248986951576</v>
+        <v>3.74567792577445</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763532</v>
+        <v>3.749896851763536</v>
       </c>
       <c r="C2012" t="n">
         <v>3.574210563329181</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.394639237585819</v>
+        <v>-3.587299590940459</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.215998443981106</v>
+        <v>2.13893430263925</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.3250640393706579</v>
+        <v>0.2857789374087825</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.769248986951576</v>
+        <v>3.74567792577445</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.831072131322751</v>
+        <v>3.822924352496842</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.705409932039554</v>
+        <v>3.572734604456183</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.452074347663385</v>
+        <v>-3.634780800924797</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.324223768660453</v>
+        <v>2.118465859772516</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.2748498907125267</v>
+        <v>0.2857789374087825</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.87031986646707</v>
+        <v>3.744201966901452</v>
       </c>
     </row>
   </sheetData>
